--- a/biodym_mfa_tool/data/02_output/results_scientific.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific.xlsx
@@ -10134,16 +10134,16 @@
         <v>2025</v>
       </c>
       <c r="C470">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D470">
         <v>0</v>
       </c>
       <c r="E470">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F470">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -10154,16 +10154,16 @@
         <v>2026</v>
       </c>
       <c r="C471">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D471">
         <v>0</v>
       </c>
       <c r="E471">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F471">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="472" spans="1:6">
@@ -10174,16 +10174,16 @@
         <v>2027</v>
       </c>
       <c r="C472">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D472">
         <v>0</v>
       </c>
       <c r="E472">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F472">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="473" spans="1:6">
@@ -10194,16 +10194,16 @@
         <v>2028</v>
       </c>
       <c r="C473">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D473">
         <v>0</v>
       </c>
       <c r="E473">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F473">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="474" spans="1:6">
@@ -10214,16 +10214,16 @@
         <v>2029</v>
       </c>
       <c r="C474">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D474">
         <v>0</v>
       </c>
       <c r="E474">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F474">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="475" spans="1:6">
@@ -10234,16 +10234,16 @@
         <v>2030</v>
       </c>
       <c r="C475">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D475">
         <v>0</v>
       </c>
       <c r="E475">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F475">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="476" spans="1:6">
@@ -10254,16 +10254,16 @@
         <v>2031</v>
       </c>
       <c r="C476">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D476">
         <v>0</v>
       </c>
       <c r="E476">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F476">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="477" spans="1:6">
@@ -10274,16 +10274,16 @@
         <v>2032</v>
       </c>
       <c r="C477">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D477">
         <v>0</v>
       </c>
       <c r="E477">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F477">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="478" spans="1:6">
@@ -10294,16 +10294,16 @@
         <v>2033</v>
       </c>
       <c r="C478">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D478">
         <v>0</v>
       </c>
       <c r="E478">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F478">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="479" spans="1:6">
@@ -10314,16 +10314,16 @@
         <v>2034</v>
       </c>
       <c r="C479">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D479">
         <v>0</v>
       </c>
       <c r="E479">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F479">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="480" spans="1:6">
@@ -10334,16 +10334,16 @@
         <v>2035</v>
       </c>
       <c r="C480">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D480">
         <v>0</v>
       </c>
       <c r="E480">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F480">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="481" spans="1:6">
@@ -10354,16 +10354,16 @@
         <v>2036</v>
       </c>
       <c r="C481">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D481">
         <v>0</v>
       </c>
       <c r="E481">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F481">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="482" spans="1:6">
@@ -10374,16 +10374,16 @@
         <v>2037</v>
       </c>
       <c r="C482">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D482">
         <v>0</v>
       </c>
       <c r="E482">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F482">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -10394,16 +10394,16 @@
         <v>2038</v>
       </c>
       <c r="C483">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D483">
         <v>0</v>
       </c>
       <c r="E483">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F483">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="484" spans="1:6">
@@ -10414,16 +10414,16 @@
         <v>2039</v>
       </c>
       <c r="C484">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D484">
         <v>0</v>
       </c>
       <c r="E484">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F484">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="485" spans="1:6">
@@ -10434,16 +10434,16 @@
         <v>2040</v>
       </c>
       <c r="C485">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D485">
         <v>0</v>
       </c>
       <c r="E485">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F485">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="486" spans="1:6">
@@ -10454,16 +10454,16 @@
         <v>2041</v>
       </c>
       <c r="C486">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D486">
         <v>0</v>
       </c>
       <c r="E486">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F486">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="487" spans="1:6">
@@ -10474,16 +10474,16 @@
         <v>2042</v>
       </c>
       <c r="C487">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D487">
         <v>0</v>
       </c>
       <c r="E487">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F487">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="488" spans="1:6">
@@ -10494,16 +10494,16 @@
         <v>2043</v>
       </c>
       <c r="C488">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D488">
         <v>0</v>
       </c>
       <c r="E488">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F488">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="489" spans="1:6">
@@ -10514,16 +10514,16 @@
         <v>2044</v>
       </c>
       <c r="C489">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D489">
         <v>0</v>
       </c>
       <c r="E489">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F489">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="490" spans="1:6">
@@ -10534,16 +10534,16 @@
         <v>2045</v>
       </c>
       <c r="C490">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D490">
         <v>0</v>
       </c>
       <c r="E490">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F490">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="491" spans="1:6">
@@ -10554,16 +10554,16 @@
         <v>2046</v>
       </c>
       <c r="C491">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D491">
         <v>0</v>
       </c>
       <c r="E491">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F491">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="492" spans="1:6">
@@ -10574,16 +10574,16 @@
         <v>2047</v>
       </c>
       <c r="C492">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D492">
         <v>0</v>
       </c>
       <c r="E492">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F492">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="493" spans="1:6">
@@ -10594,16 +10594,16 @@
         <v>2048</v>
       </c>
       <c r="C493">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D493">
         <v>0</v>
       </c>
       <c r="E493">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F493">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="494" spans="1:6">
@@ -10614,16 +10614,16 @@
         <v>2049</v>
       </c>
       <c r="C494">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D494">
         <v>0</v>
       </c>
       <c r="E494">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F494">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="495" spans="1:6">
@@ -10634,16 +10634,16 @@
         <v>2050</v>
       </c>
       <c r="C495">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D495">
         <v>0</v>
       </c>
       <c r="E495">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F495">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -10684,16 +10684,16 @@
         <v>2025</v>
       </c>
       <c r="C2">
-        <v>973.149325461347</v>
+        <v>-25.85067453865305</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>973.149325461347</v>
+        <v>-25.85067453865305</v>
       </c>
       <c r="F2">
-        <v>436.5746627306735</v>
+        <v>-62.92533726932653</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -10704,16 +10704,16 @@
         <v>2026</v>
       </c>
       <c r="C3">
-        <v>971.0172866979176</v>
+        <v>-27.98271330208243</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>971.0172866979176</v>
+        <v>-27.98271330208243</v>
       </c>
       <c r="F3">
-        <v>430.5086433489588</v>
+        <v>-68.99135665104122</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -10724,16 +10724,16 @@
         <v>2027</v>
       </c>
       <c r="C4">
-        <v>968.929149084719</v>
+        <v>-30.07085091528093</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>968.929149084719</v>
+        <v>-30.07085091528093</v>
       </c>
       <c r="F4">
-        <v>424.4645745423595</v>
+        <v>-75.03542545764046</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -10744,16 +10744,16 @@
         <v>2028</v>
       </c>
       <c r="C5">
-        <v>966.8848835252036</v>
+        <v>-32.11511647479648</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>966.8848835252036</v>
+        <v>-32.11511647479648</v>
       </c>
       <c r="F5">
-        <v>418.4424417626018</v>
+        <v>-81.05755823739824</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -10764,16 +10764,16 @@
         <v>2029</v>
       </c>
       <c r="C6">
-        <v>964.8848375625003</v>
+        <v>-34.11516243749971</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>964.8848375625003</v>
+        <v>-34.11516243749971</v>
       </c>
       <c r="F6">
-        <v>412.4424187812501</v>
+        <v>-87.05758121874985</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -10784,16 +10784,16 @@
         <v>2030</v>
       </c>
       <c r="C7">
-        <v>962.9298689891305</v>
+        <v>-36.07013101086957</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>962.9298689891305</v>
+        <v>-36.07013101086957</v>
       </c>
       <c r="F7">
-        <v>406.4649344945652</v>
+        <v>-93.03506550543479</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -10804,16 +10804,16 @@
         <v>2031</v>
       </c>
       <c r="C8">
-        <v>961.588427009136</v>
+        <v>-37.41157299086406</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>961.588427009136</v>
+        <v>-37.41157299086406</v>
       </c>
       <c r="F8">
-        <v>400.794213504568</v>
+        <v>-98.70578649543202</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -10824,16 +10824,16 @@
         <v>2032</v>
       </c>
       <c r="C9">
-        <v>960.5145493682924</v>
+        <v>-38.48545063170755</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>960.5145493682924</v>
+        <v>-38.48545063170755</v>
       </c>
       <c r="F9">
-        <v>395.2572746841462</v>
+        <v>-104.2427253158538</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -10844,16 +10844,16 @@
         <v>2033</v>
       </c>
       <c r="C10">
-        <v>959.7641849322604</v>
+        <v>-39.23581506773959</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>959.7641849322604</v>
+        <v>-39.23581506773959</v>
       </c>
       <c r="F10">
-        <v>389.8820924661302</v>
+        <v>-109.6179075338698</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -10864,16 +10864,16 @@
         <v>2034</v>
       </c>
       <c r="C11">
-        <v>959.5504162086359</v>
+        <v>-39.44958379136418</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>959.5504162086359</v>
+        <v>-39.44958379136418</v>
       </c>
       <c r="F11">
-        <v>384.7752081043179</v>
+        <v>-114.7247918956821</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -10884,16 +10884,16 @@
         <v>2035</v>
       </c>
       <c r="C12">
-        <v>960.1035926431023</v>
+        <v>-38.89640735689778</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>960.1035926431023</v>
+        <v>-38.89640735689778</v>
       </c>
       <c r="F12">
-        <v>380.0517963215511</v>
+        <v>-119.4482036784489</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -10904,16 +10904,16 @@
         <v>2036</v>
       </c>
       <c r="C13">
-        <v>1010.541376870601</v>
+        <v>11.54137687060118</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>1010.541376870601</v>
+        <v>11.54137687060118</v>
       </c>
       <c r="F13">
-        <v>500.2706884353006</v>
+        <v>0.7706884353005918</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -10924,16 +10924,16 @@
         <v>2037</v>
       </c>
       <c r="C14">
-        <v>959.9646713644893</v>
+        <v>-39.03532863551061</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>959.9646713644893</v>
+        <v>-39.03532863551061</v>
       </c>
       <c r="F14">
-        <v>369.9823356822446</v>
+        <v>-129.5176643177553</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -10944,16 +10944,16 @@
         <v>2038</v>
       </c>
       <c r="C15">
-        <v>961.3715437506896</v>
+        <v>-37.6284562493104</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>961.3715437506896</v>
+        <v>-37.6284562493104</v>
       </c>
       <c r="F15">
-        <v>365.6857718753448</v>
+        <v>-133.8142281246552</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -10964,16 +10964,16 @@
         <v>2039</v>
       </c>
       <c r="C16">
-        <v>963.276239675921</v>
+        <v>-35.72376032407891</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>963.276239675921</v>
+        <v>-35.72376032407891</v>
       </c>
       <c r="F16">
-        <v>361.6381198379605</v>
+        <v>-137.8618801620395</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -10984,16 +10984,16 @@
         <v>2040</v>
       </c>
       <c r="C17">
-        <v>965.6819510498524</v>
+        <v>-33.31804895014756</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>965.6819510498524</v>
+        <v>-33.31804895014756</v>
       </c>
       <c r="F17">
-        <v>357.8409755249262</v>
+        <v>-141.6590244750738</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -11004,16 +11004,16 @@
         <v>2041</v>
       </c>
       <c r="C18">
-        <v>967.5567596307756</v>
+        <v>-31.44324036922433</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>967.5567596307756</v>
+        <v>-31.44324036922433</v>
       </c>
       <c r="F18">
-        <v>353.7783798153878</v>
+        <v>-145.7216201846122</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -11024,16 +11024,16 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>969.4305527380152</v>
+        <v>-29.56944726198486</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>969.4305527380152</v>
+        <v>-29.56944726198486</v>
       </c>
       <c r="F19">
-        <v>349.7152763690076</v>
+        <v>-149.7847236309924</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -11044,16 +11044,16 @@
         <v>2043</v>
       </c>
       <c r="C20">
-        <v>971.2857579094186</v>
+        <v>-27.71424209058131</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>971.2857579094186</v>
+        <v>-27.71424209058131</v>
       </c>
       <c r="F20">
-        <v>345.6428789547093</v>
+        <v>-153.8571210452907</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -11064,16 +11064,16 @@
         <v>2044</v>
       </c>
       <c r="C21">
-        <v>973.0919891015064</v>
+        <v>-25.90801089849344</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>973.0919891015064</v>
+        <v>-25.90801089849344</v>
       </c>
       <c r="F21">
-        <v>341.5459945507532</v>
+        <v>-157.9540054492467</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -11084,16 +11084,16 @@
         <v>2045</v>
       </c>
       <c r="C22">
-        <v>974.6838522213998</v>
+        <v>-24.31614777860023</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>974.6838522213998</v>
+        <v>-24.31614777860023</v>
       </c>
       <c r="F22">
-        <v>337.3419261106999</v>
+        <v>-162.1580738893001</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -11104,16 +11104,16 @@
         <v>2046</v>
       </c>
       <c r="C23">
-        <v>976.0560586016468</v>
+        <v>-22.94394139835327</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>976.0560586016468</v>
+        <v>-22.94394139835327</v>
       </c>
       <c r="F23">
-        <v>333.0280293008234</v>
+        <v>-166.4719706991766</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -11124,16 +11124,16 @@
         <v>2047</v>
       </c>
       <c r="C24">
-        <v>977.8343509511526</v>
+        <v>-21.16564904884734</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>977.8343509511526</v>
+        <v>-21.16564904884734</v>
       </c>
       <c r="F24">
-        <v>328.9171754755763</v>
+        <v>-170.5828245244237</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -11144,16 +11144,16 @@
         <v>2048</v>
       </c>
       <c r="C25">
-        <v>979.9876980579843</v>
+        <v>-19.01230194201565</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>979.9876980579843</v>
+        <v>-19.01230194201565</v>
       </c>
       <c r="F25">
-        <v>324.9938490289921</v>
+        <v>-174.5061509710078</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -11164,16 +11164,16 @@
         <v>2049</v>
       </c>
       <c r="C26">
-        <v>981.851354754675</v>
+        <v>-17.14864524532493</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>981.851354754675</v>
+        <v>-17.14864524532493</v>
       </c>
       <c r="F26">
-        <v>320.9256773773375</v>
+        <v>-178.5743226226625</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -11184,16 +11184,16 @@
         <v>2050</v>
       </c>
       <c r="C27">
-        <v>983.4762840634182</v>
+        <v>-15.52371593658182</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>983.4762840634182</v>
+        <v>-15.52371593658182</v>
       </c>
       <c r="F27">
-        <v>316.7381420317091</v>
+        <v>-182.7618579682909</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -11224,16 +11224,16 @@
         <v>2026</v>
       </c>
       <c r="C29">
-        <v>973.149325461347</v>
+        <v>-25.85067453865305</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>973.149325461347</v>
+        <v>-25.85067453865305</v>
       </c>
       <c r="F29">
-        <v>436.5746627306735</v>
+        <v>-62.92533726932653</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -11244,16 +11244,16 @@
         <v>2027</v>
       </c>
       <c r="C30">
-        <v>1944.166612159265</v>
+        <v>-53.83338784073548</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>1944.166612159265</v>
+        <v>-53.83338784073548</v>
       </c>
       <c r="F30">
-        <v>867.0833060796323</v>
+        <v>-131.9166939203677</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -11264,16 +11264,16 @@
         <v>2028</v>
       </c>
       <c r="C31">
-        <v>2913.095761243983</v>
+        <v>-83.90423875601641</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>2913.095761243983</v>
+        <v>-83.90423875601641</v>
       </c>
       <c r="F31">
-        <v>1291.547880621992</v>
+        <v>-206.9521193780082</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -11284,16 +11284,16 @@
         <v>2029</v>
       </c>
       <c r="C32">
-        <v>3879.980644769187</v>
+        <v>-116.0193552308129</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>3879.980644769187</v>
+        <v>-116.0193552308129</v>
       </c>
       <c r="F32">
-        <v>1709.990322384594</v>
+        <v>-288.0096776154064</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -11304,16 +11304,16 @@
         <v>2030</v>
       </c>
       <c r="C33">
-        <v>4844.865482331687</v>
+        <v>-150.1345176683126</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>4844.865482331687</v>
+        <v>-150.1345176683126</v>
       </c>
       <c r="F33">
-        <v>2122.432741165844</v>
+        <v>-375.0672588341563</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -11324,16 +11324,16 @@
         <v>2031</v>
       </c>
       <c r="C34">
-        <v>5807.795351320818</v>
+        <v>-186.2046486791822</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>5807.795351320818</v>
+        <v>-186.2046486791822</v>
       </c>
       <c r="F34">
-        <v>2528.897675660409</v>
+        <v>-468.1023243395911</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -11344,16 +11344,16 @@
         <v>2032</v>
       </c>
       <c r="C35">
-        <v>6769.383778329953</v>
+        <v>-223.6162216700462</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>6769.383778329953</v>
+        <v>-223.6162216700462</v>
       </c>
       <c r="F35">
-        <v>2929.691889164977</v>
+        <v>-566.8081108350231</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -11364,16 +11364,16 @@
         <v>2033</v>
       </c>
       <c r="C36">
-        <v>7729.898327698245</v>
+        <v>-262.1016723017538</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>7729.898327698245</v>
+        <v>-262.1016723017538</v>
       </c>
       <c r="F36">
-        <v>3324.949163849123</v>
+        <v>-671.0508361508769</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -11384,16 +11384,16 @@
         <v>2034</v>
       </c>
       <c r="C37">
-        <v>8689.662512630506</v>
+        <v>-301.3374873694934</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>8689.662512630506</v>
+        <v>-301.3374873694934</v>
       </c>
       <c r="F37">
-        <v>3714.831256315253</v>
+        <v>-780.6687436847467</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -11404,16 +11404,16 @@
         <v>2035</v>
       </c>
       <c r="C38">
-        <v>9649.212928839142</v>
+        <v>-340.7870711608575</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>9649.212928839142</v>
+        <v>-340.7870711608575</v>
       </c>
       <c r="F38">
-        <v>4099.606464419571</v>
+        <v>-895.3935355804288</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -11424,16 +11424,16 @@
         <v>2036</v>
       </c>
       <c r="C39">
-        <v>10609.31652148224</v>
+        <v>-379.6834785177553</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>10609.31652148224</v>
+        <v>-379.6834785177553</v>
       </c>
       <c r="F39">
-        <v>4479.658260741122</v>
+        <v>-1014.841739258878</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -11444,16 +11444,16 @@
         <v>2037</v>
       </c>
       <c r="C40">
-        <v>11619.85789835285</v>
+        <v>-368.1421016471541</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>11619.85789835285</v>
+        <v>-368.1421016471541</v>
       </c>
       <c r="F40">
-        <v>4979.928949176423</v>
+        <v>-1014.071050823577</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -11464,16 +11464,16 @@
         <v>2038</v>
       </c>
       <c r="C41">
-        <v>12579.82256971733</v>
+        <v>-407.1774302826647</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>12579.82256971733</v>
+        <v>-407.1774302826647</v>
       </c>
       <c r="F41">
-        <v>5349.911284858667</v>
+        <v>-1143.588715141332</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -11484,16 +11484,16 @@
         <v>2039</v>
       </c>
       <c r="C42">
-        <v>13541.19411346802</v>
+        <v>-444.8058865319751</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>13541.19411346802</v>
+        <v>-444.8058865319751</v>
       </c>
       <c r="F42">
-        <v>5715.597056734012</v>
+        <v>-1277.402943265988</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -11504,16 +11504,16 @@
         <v>2040</v>
       </c>
       <c r="C43">
-        <v>14504.47035314394</v>
+        <v>-480.5296468560541</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>14504.47035314394</v>
+        <v>-480.5296468560541</v>
       </c>
       <c r="F43">
-        <v>6077.235176571972</v>
+        <v>-1415.264823428027</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -11524,16 +11524,16 @@
         <v>2041</v>
       </c>
       <c r="C44">
-        <v>15470.1523041938</v>
+        <v>-513.8476958062016</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>15470.1523041938</v>
+        <v>-513.8476958062016</v>
       </c>
       <c r="F44">
-        <v>6435.076152096898</v>
+        <v>-1556.923847903101</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -11544,16 +11544,16 @@
         <v>2042</v>
       </c>
       <c r="C45">
-        <v>16437.70906382457</v>
+        <v>-545.2909361754259</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>16437.70906382457</v>
+        <v>-545.2909361754259</v>
       </c>
       <c r="F45">
-        <v>6788.854531912286</v>
+        <v>-1702.645468087713</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -11564,16 +11564,16 @@
         <v>2043</v>
       </c>
       <c r="C46">
-        <v>17407.13961656259</v>
+        <v>-574.8603834374107</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>17407.13961656259</v>
+        <v>-574.8603834374107</v>
       </c>
       <c r="F46">
-        <v>7138.569808281293</v>
+        <v>-1852.430191718705</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -11584,16 +11584,16 @@
         <v>2044</v>
       </c>
       <c r="C47">
-        <v>18378.42537447201</v>
+        <v>-602.5746255279921</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>18378.42537447201</v>
+        <v>-602.5746255279921</v>
       </c>
       <c r="F47">
-        <v>7484.212687236002</v>
+        <v>-2006.287312763996</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -11604,16 +11604,16 @@
         <v>2045</v>
       </c>
       <c r="C48">
-        <v>19351.51736357352</v>
+        <v>-628.4826364264856</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>19351.51736357352</v>
+        <v>-628.4826364264856</v>
       </c>
       <c r="F48">
-        <v>7825.758681786756</v>
+        <v>-2164.241318213243</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -11624,16 +11624,16 @@
         <v>2046</v>
       </c>
       <c r="C49">
-        <v>20326.20121579491</v>
+        <v>-652.7987842050858</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>20326.20121579491</v>
+        <v>-652.7987842050858</v>
       </c>
       <c r="F49">
-        <v>8163.100607897456</v>
+        <v>-2326.399392102543</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -11644,16 +11644,16 @@
         <v>2047</v>
       </c>
       <c r="C50">
-        <v>21302.25727439656</v>
+        <v>-675.7427256034391</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>21302.25727439656</v>
+        <v>-675.7427256034391</v>
       </c>
       <c r="F50">
-        <v>8496.128637198279</v>
+        <v>-2492.87136280172</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -11664,16 +11664,16 @@
         <v>2048</v>
       </c>
       <c r="C51">
-        <v>22280.09162534772</v>
+        <v>-696.9083746522865</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>22280.09162534772</v>
+        <v>-696.9083746522865</v>
       </c>
       <c r="F51">
-        <v>8825.045812673856</v>
+        <v>-2663.454187326144</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -11684,16 +11684,16 @@
         <v>2049</v>
       </c>
       <c r="C52">
-        <v>23260.0793234057</v>
+        <v>-715.9206765943022</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>23260.0793234057</v>
+        <v>-715.9206765943022</v>
       </c>
       <c r="F52">
-        <v>9150.039661702847</v>
+        <v>-2837.960338297151</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -11704,16 +11704,16 @@
         <v>2050</v>
       </c>
       <c r="C53">
-        <v>24241.93067816037</v>
+        <v>-733.0693218396272</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>24241.93067816037</v>
+        <v>-733.0693218396272</v>
       </c>
       <c r="F53">
-        <v>9470.965339080185</v>
+        <v>-3016.534660919814</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -13804,16 +13804,16 @@
         <v>2025</v>
       </c>
       <c r="C158">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D158">
         <v>0</v>
       </c>
       <c r="E158">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F158">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="159" spans="1:6">
@@ -13824,16 +13824,16 @@
         <v>2026</v>
       </c>
       <c r="C159">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D159">
         <v>0</v>
       </c>
       <c r="E159">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F159">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="160" spans="1:6">
@@ -13844,16 +13844,16 @@
         <v>2027</v>
       </c>
       <c r="C160">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D160">
         <v>0</v>
       </c>
       <c r="E160">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F160">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="161" spans="1:6">
@@ -13864,16 +13864,16 @@
         <v>2028</v>
       </c>
       <c r="C161">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D161">
         <v>0</v>
       </c>
       <c r="E161">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F161">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="162" spans="1:6">
@@ -13884,16 +13884,16 @@
         <v>2029</v>
       </c>
       <c r="C162">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D162">
         <v>0</v>
       </c>
       <c r="E162">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F162">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="163" spans="1:6">
@@ -13904,16 +13904,16 @@
         <v>2030</v>
       </c>
       <c r="C163">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D163">
         <v>0</v>
       </c>
       <c r="E163">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F163">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="164" spans="1:6">
@@ -13924,16 +13924,16 @@
         <v>2031</v>
       </c>
       <c r="C164">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D164">
         <v>0</v>
       </c>
       <c r="E164">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F164">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="165" spans="1:6">
@@ -13944,16 +13944,16 @@
         <v>2032</v>
       </c>
       <c r="C165">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D165">
         <v>0</v>
       </c>
       <c r="E165">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F165">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="166" spans="1:6">
@@ -13964,16 +13964,16 @@
         <v>2033</v>
       </c>
       <c r="C166">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D166">
         <v>0</v>
       </c>
       <c r="E166">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F166">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="167" spans="1:6">
@@ -13984,16 +13984,16 @@
         <v>2034</v>
       </c>
       <c r="C167">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D167">
         <v>0</v>
       </c>
       <c r="E167">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F167">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="168" spans="1:6">
@@ -14004,16 +14004,16 @@
         <v>2035</v>
       </c>
       <c r="C168">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D168">
         <v>0</v>
       </c>
       <c r="E168">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F168">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="169" spans="1:6">
@@ -14024,16 +14024,16 @@
         <v>2036</v>
       </c>
       <c r="C169">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D169">
         <v>0</v>
       </c>
       <c r="E169">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F169">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="170" spans="1:6">
@@ -14044,16 +14044,16 @@
         <v>2037</v>
       </c>
       <c r="C170">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D170">
         <v>0</v>
       </c>
       <c r="E170">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F170">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="171" spans="1:6">
@@ -14064,16 +14064,16 @@
         <v>2038</v>
       </c>
       <c r="C171">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D171">
         <v>0</v>
       </c>
       <c r="E171">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F171">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="172" spans="1:6">
@@ -14084,16 +14084,16 @@
         <v>2039</v>
       </c>
       <c r="C172">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D172">
         <v>0</v>
       </c>
       <c r="E172">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F172">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="173" spans="1:6">
@@ -14104,16 +14104,16 @@
         <v>2040</v>
       </c>
       <c r="C173">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D173">
         <v>0</v>
       </c>
       <c r="E173">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F173">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="174" spans="1:6">
@@ -14124,16 +14124,16 @@
         <v>2041</v>
       </c>
       <c r="C174">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D174">
         <v>0</v>
       </c>
       <c r="E174">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F174">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="175" spans="1:6">
@@ -14144,16 +14144,16 @@
         <v>2042</v>
       </c>
       <c r="C175">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D175">
         <v>0</v>
       </c>
       <c r="E175">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F175">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="176" spans="1:6">
@@ -14164,16 +14164,16 @@
         <v>2043</v>
       </c>
       <c r="C176">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D176">
         <v>0</v>
       </c>
       <c r="E176">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F176">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="177" spans="1:6">
@@ -14184,16 +14184,16 @@
         <v>2044</v>
       </c>
       <c r="C177">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D177">
         <v>0</v>
       </c>
       <c r="E177">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F177">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="178" spans="1:6">
@@ -14204,16 +14204,16 @@
         <v>2045</v>
       </c>
       <c r="C178">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D178">
         <v>0</v>
       </c>
       <c r="E178">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F178">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="179" spans="1:6">
@@ -14224,16 +14224,16 @@
         <v>2046</v>
       </c>
       <c r="C179">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D179">
         <v>0</v>
       </c>
       <c r="E179">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F179">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="180" spans="1:6">
@@ -14244,16 +14244,16 @@
         <v>2047</v>
       </c>
       <c r="C180">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D180">
         <v>0</v>
       </c>
       <c r="E180">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F180">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="181" spans="1:6">
@@ -14264,16 +14264,16 @@
         <v>2048</v>
       </c>
       <c r="C181">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D181">
         <v>0</v>
       </c>
       <c r="E181">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F181">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="182" spans="1:6">
@@ -14284,16 +14284,16 @@
         <v>2049</v>
       </c>
       <c r="C182">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D182">
         <v>0</v>
       </c>
       <c r="E182">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F182">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="183" spans="1:6">
@@ -14304,16 +14304,16 @@
         <v>2050</v>
       </c>
       <c r="C183">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D183">
         <v>0</v>
       </c>
       <c r="E183">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F183">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="184" spans="1:6">
@@ -14324,16 +14324,16 @@
         <v>2025</v>
       </c>
       <c r="C184">
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="D184">
         <v>0</v>
       </c>
       <c r="E184">
-        <v>10000</v>
+        <v>10</v>
       </c>
       <c r="F184">
-        <v>5000</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:6">
@@ -14344,16 +14344,16 @@
         <v>2026</v>
       </c>
       <c r="C185">
-        <v>9000</v>
+        <v>9</v>
       </c>
       <c r="D185">
         <v>0</v>
       </c>
       <c r="E185">
-        <v>9000</v>
+        <v>9</v>
       </c>
       <c r="F185">
-        <v>4500</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="186" spans="1:6">
@@ -14364,16 +14364,16 @@
         <v>2027</v>
       </c>
       <c r="C186">
-        <v>8000</v>
+        <v>8</v>
       </c>
       <c r="D186">
         <v>0</v>
       </c>
       <c r="E186">
-        <v>8000</v>
+        <v>8</v>
       </c>
       <c r="F186">
-        <v>4000</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187" spans="1:6">
@@ -14384,16 +14384,16 @@
         <v>2028</v>
       </c>
       <c r="C187">
-        <v>7000</v>
+        <v>7</v>
       </c>
       <c r="D187">
         <v>0</v>
       </c>
       <c r="E187">
-        <v>7000</v>
+        <v>7</v>
       </c>
       <c r="F187">
-        <v>3500</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="188" spans="1:6">
@@ -14404,16 +14404,16 @@
         <v>2029</v>
       </c>
       <c r="C188">
-        <v>6000</v>
+        <v>6</v>
       </c>
       <c r="D188">
         <v>0</v>
       </c>
       <c r="E188">
-        <v>6000</v>
+        <v>6</v>
       </c>
       <c r="F188">
-        <v>3000</v>
+        <v>3</v>
       </c>
     </row>
     <row r="189" spans="1:6">
@@ -14424,16 +14424,16 @@
         <v>2030</v>
       </c>
       <c r="C189">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="D189">
         <v>0</v>
       </c>
       <c r="E189">
-        <v>5000</v>
+        <v>5</v>
       </c>
       <c r="F189">
-        <v>2500</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="190" spans="1:6">
@@ -14444,16 +14444,16 @@
         <v>2031</v>
       </c>
       <c r="C190">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="D190">
         <v>0</v>
       </c>
       <c r="E190">
-        <v>4000</v>
+        <v>4</v>
       </c>
       <c r="F190">
-        <v>2000</v>
+        <v>2</v>
       </c>
     </row>
     <row r="191" spans="1:6">
@@ -14464,16 +14464,16 @@
         <v>2032</v>
       </c>
       <c r="C191">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="D191">
         <v>0</v>
       </c>
       <c r="E191">
-        <v>3000</v>
+        <v>3</v>
       </c>
       <c r="F191">
-        <v>1500</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="192" spans="1:6">
@@ -14484,16 +14484,16 @@
         <v>2033</v>
       </c>
       <c r="C192">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="D192">
         <v>0</v>
       </c>
       <c r="E192">
-        <v>2000</v>
+        <v>2</v>
       </c>
       <c r="F192">
-        <v>1000</v>
+        <v>1</v>
       </c>
     </row>
     <row r="193" spans="1:6">
@@ -14504,16 +14504,16 @@
         <v>2034</v>
       </c>
       <c r="C193">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="D193">
         <v>0</v>
       </c>
       <c r="E193">
-        <v>1000</v>
+        <v>1</v>
       </c>
       <c r="F193">
-        <v>500</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="194" spans="1:6">
@@ -14544,16 +14544,16 @@
         <v>2036</v>
       </c>
       <c r="C195">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="D195">
         <v>0</v>
       </c>
       <c r="E195">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
       <c r="F195">
-        <v>-500</v>
+        <v>-0.5</v>
       </c>
     </row>
     <row r="196" spans="1:6">
@@ -14564,16 +14564,16 @@
         <v>2037</v>
       </c>
       <c r="C196">
-        <v>-2000</v>
+        <v>-2</v>
       </c>
       <c r="D196">
         <v>0</v>
       </c>
       <c r="E196">
-        <v>-2000</v>
+        <v>-2</v>
       </c>
       <c r="F196">
-        <v>-1000</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="197" spans="1:6">
@@ -14584,16 +14584,16 @@
         <v>2038</v>
       </c>
       <c r="C197">
-        <v>-3000</v>
+        <v>-3</v>
       </c>
       <c r="D197">
         <v>0</v>
       </c>
       <c r="E197">
-        <v>-3000</v>
+        <v>-3</v>
       </c>
       <c r="F197">
-        <v>-1500</v>
+        <v>-1.5</v>
       </c>
     </row>
     <row r="198" spans="1:6">
@@ -14604,16 +14604,16 @@
         <v>2039</v>
       </c>
       <c r="C198">
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="D198">
         <v>0</v>
       </c>
       <c r="E198">
-        <v>-4000</v>
+        <v>-4</v>
       </c>
       <c r="F198">
-        <v>-2000</v>
+        <v>-2</v>
       </c>
     </row>
     <row r="199" spans="1:6">
@@ -14624,16 +14624,16 @@
         <v>2040</v>
       </c>
       <c r="C199">
-        <v>-5000</v>
+        <v>-5</v>
       </c>
       <c r="D199">
         <v>0</v>
       </c>
       <c r="E199">
-        <v>-5000</v>
+        <v>-5</v>
       </c>
       <c r="F199">
-        <v>-2500</v>
+        <v>-2.5</v>
       </c>
     </row>
     <row r="200" spans="1:6">
@@ -14644,16 +14644,16 @@
         <v>2041</v>
       </c>
       <c r="C200">
-        <v>-6000</v>
+        <v>-6</v>
       </c>
       <c r="D200">
         <v>0</v>
       </c>
       <c r="E200">
-        <v>-6000</v>
+        <v>-6</v>
       </c>
       <c r="F200">
-        <v>-3000</v>
+        <v>-3</v>
       </c>
     </row>
     <row r="201" spans="1:6">
@@ -14664,16 +14664,16 @@
         <v>2042</v>
       </c>
       <c r="C201">
-        <v>-7000</v>
+        <v>-7</v>
       </c>
       <c r="D201">
         <v>0</v>
       </c>
       <c r="E201">
-        <v>-7000</v>
+        <v>-7</v>
       </c>
       <c r="F201">
-        <v>-3500</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="202" spans="1:6">
@@ -14684,16 +14684,16 @@
         <v>2043</v>
       </c>
       <c r="C202">
-        <v>-8000</v>
+        <v>-8</v>
       </c>
       <c r="D202">
         <v>0</v>
       </c>
       <c r="E202">
-        <v>-8000</v>
+        <v>-8</v>
       </c>
       <c r="F202">
-        <v>-4000</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="203" spans="1:6">
@@ -14704,16 +14704,16 @@
         <v>2044</v>
       </c>
       <c r="C203">
-        <v>-9000</v>
+        <v>-9</v>
       </c>
       <c r="D203">
         <v>0</v>
       </c>
       <c r="E203">
-        <v>-9000</v>
+        <v>-9</v>
       </c>
       <c r="F203">
-        <v>-4500</v>
+        <v>-4.5</v>
       </c>
     </row>
     <row r="204" spans="1:6">
@@ -14724,16 +14724,16 @@
         <v>2045</v>
       </c>
       <c r="C204">
-        <v>-10000</v>
+        <v>-10</v>
       </c>
       <c r="D204">
         <v>0</v>
       </c>
       <c r="E204">
-        <v>-10000</v>
+        <v>-10</v>
       </c>
       <c r="F204">
-        <v>-5000</v>
+        <v>-5</v>
       </c>
     </row>
     <row r="205" spans="1:6">
@@ -14744,16 +14744,16 @@
         <v>2046</v>
       </c>
       <c r="C205">
-        <v>-11000</v>
+        <v>-11</v>
       </c>
       <c r="D205">
         <v>0</v>
       </c>
       <c r="E205">
-        <v>-11000</v>
+        <v>-11</v>
       </c>
       <c r="F205">
-        <v>-5500</v>
+        <v>-5.5</v>
       </c>
     </row>
     <row r="206" spans="1:6">
@@ -14764,16 +14764,16 @@
         <v>2047</v>
       </c>
       <c r="C206">
-        <v>-12000</v>
+        <v>-12</v>
       </c>
       <c r="D206">
         <v>0</v>
       </c>
       <c r="E206">
-        <v>-12000</v>
+        <v>-12</v>
       </c>
       <c r="F206">
-        <v>-6000</v>
+        <v>-6</v>
       </c>
     </row>
     <row r="207" spans="1:6">
@@ -14784,16 +14784,16 @@
         <v>2048</v>
       </c>
       <c r="C207">
-        <v>-13000</v>
+        <v>-13</v>
       </c>
       <c r="D207">
         <v>0</v>
       </c>
       <c r="E207">
-        <v>-13000</v>
+        <v>-13</v>
       </c>
       <c r="F207">
-        <v>-6500</v>
+        <v>-6.5</v>
       </c>
     </row>
     <row r="208" spans="1:6">
@@ -14804,16 +14804,16 @@
         <v>2049</v>
       </c>
       <c r="C208">
-        <v>-14000</v>
+        <v>-14</v>
       </c>
       <c r="D208">
         <v>0</v>
       </c>
       <c r="E208">
-        <v>-14000</v>
+        <v>-14</v>
       </c>
       <c r="F208">
-        <v>-7000</v>
+        <v>-7</v>
       </c>
     </row>
     <row r="209" spans="1:6">
@@ -14824,16 +14824,16 @@
         <v>2050</v>
       </c>
       <c r="C209">
-        <v>-15000</v>
+        <v>-15</v>
       </c>
       <c r="D209">
         <v>0</v>
       </c>
       <c r="E209">
-        <v>-15000</v>
+        <v>-15</v>
       </c>
       <c r="F209">
-        <v>-7500</v>
+        <v>-7.5</v>
       </c>
     </row>
     <row r="210" spans="1:6">

--- a/biodym_mfa_tool/data/02_output/results_scientific.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="932" uniqueCount="126">
   <si>
     <t>Flow</t>
   </si>
@@ -91,6 +91,9 @@
     <t>F_10_01</t>
   </si>
   <si>
+    <t>F_09_11</t>
+  </si>
+  <si>
     <t>F_9_0_stock</t>
   </si>
   <si>
@@ -125,6 +128,12 @@
   </si>
   <si>
     <t>S_10</t>
+  </si>
+  <si>
+    <t>dS_11</t>
+  </si>
+  <si>
+    <t>S_11</t>
   </si>
   <si>
     <t>Parameter</t>
@@ -350,6 +359,9 @@
   </si>
   <si>
     <t>CC_F_10_01</t>
+  </si>
+  <si>
+    <t>CC_F_09_11</t>
   </si>
   <si>
     <t>[0.4  0.4  0.4  0.4  0.4  0.4  0.37 0.34 0.31 0.28 0.25 0.22 0.19 0.16
@@ -743,7 +755,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F495"/>
+  <dimension ref="A1:F521"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
@@ -10134,16 +10146,16 @@
         <v>2025</v>
       </c>
       <c r="C470">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D470">
         <v>0</v>
       </c>
       <c r="E470">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F470">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471" spans="1:6">
@@ -10154,16 +10166,16 @@
         <v>2026</v>
       </c>
       <c r="C471">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D471">
         <v>0</v>
       </c>
       <c r="E471">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F471">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472" spans="1:6">
@@ -10174,16 +10186,16 @@
         <v>2027</v>
       </c>
       <c r="C472">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D472">
         <v>0</v>
       </c>
       <c r="E472">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F472">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473" spans="1:6">
@@ -10194,16 +10206,16 @@
         <v>2028</v>
       </c>
       <c r="C473">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D473">
         <v>0</v>
       </c>
       <c r="E473">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F473">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="474" spans="1:6">
@@ -10214,16 +10226,16 @@
         <v>2029</v>
       </c>
       <c r="C474">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D474">
         <v>0</v>
       </c>
       <c r="E474">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F474">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475" spans="1:6">
@@ -10234,16 +10246,16 @@
         <v>2030</v>
       </c>
       <c r="C475">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D475">
         <v>0</v>
       </c>
       <c r="E475">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F475">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="476" spans="1:6">
@@ -10254,16 +10266,16 @@
         <v>2031</v>
       </c>
       <c r="C476">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D476">
         <v>0</v>
       </c>
       <c r="E476">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F476">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477" spans="1:6">
@@ -10274,16 +10286,16 @@
         <v>2032</v>
       </c>
       <c r="C477">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D477">
         <v>0</v>
       </c>
       <c r="E477">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F477">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="478" spans="1:6">
@@ -10294,16 +10306,16 @@
         <v>2033</v>
       </c>
       <c r="C478">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D478">
         <v>0</v>
       </c>
       <c r="E478">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F478">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="479" spans="1:6">
@@ -10314,16 +10326,16 @@
         <v>2034</v>
       </c>
       <c r="C479">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D479">
         <v>0</v>
       </c>
       <c r="E479">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F479">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480" spans="1:6">
@@ -10334,16 +10346,16 @@
         <v>2035</v>
       </c>
       <c r="C480">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D480">
         <v>0</v>
       </c>
       <c r="E480">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F480">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="481" spans="1:6">
@@ -10354,16 +10366,16 @@
         <v>2036</v>
       </c>
       <c r="C481">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D481">
         <v>0</v>
       </c>
       <c r="E481">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F481">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482" spans="1:6">
@@ -10374,16 +10386,16 @@
         <v>2037</v>
       </c>
       <c r="C482">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D482">
         <v>0</v>
       </c>
       <c r="E482">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F482">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483" spans="1:6">
@@ -10394,16 +10406,16 @@
         <v>2038</v>
       </c>
       <c r="C483">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D483">
         <v>0</v>
       </c>
       <c r="E483">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F483">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="484" spans="1:6">
@@ -10414,16 +10426,16 @@
         <v>2039</v>
       </c>
       <c r="C484">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D484">
         <v>0</v>
       </c>
       <c r="E484">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F484">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="485" spans="1:6">
@@ -10434,16 +10446,16 @@
         <v>2040</v>
       </c>
       <c r="C485">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D485">
         <v>0</v>
       </c>
       <c r="E485">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F485">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="486" spans="1:6">
@@ -10454,16 +10466,16 @@
         <v>2041</v>
       </c>
       <c r="C486">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D486">
         <v>0</v>
       </c>
       <c r="E486">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F486">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487" spans="1:6">
@@ -10474,16 +10486,16 @@
         <v>2042</v>
       </c>
       <c r="C487">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D487">
         <v>0</v>
       </c>
       <c r="E487">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F487">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488" spans="1:6">
@@ -10494,16 +10506,16 @@
         <v>2043</v>
       </c>
       <c r="C488">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D488">
         <v>0</v>
       </c>
       <c r="E488">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F488">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="489" spans="1:6">
@@ -10514,16 +10526,16 @@
         <v>2044</v>
       </c>
       <c r="C489">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D489">
         <v>0</v>
       </c>
       <c r="E489">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F489">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="490" spans="1:6">
@@ -10534,16 +10546,16 @@
         <v>2045</v>
       </c>
       <c r="C490">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D490">
         <v>0</v>
       </c>
       <c r="E490">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F490">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="491" spans="1:6">
@@ -10554,16 +10566,16 @@
         <v>2046</v>
       </c>
       <c r="C491">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D491">
         <v>0</v>
       </c>
       <c r="E491">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F491">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="492" spans="1:6">
@@ -10574,16 +10586,16 @@
         <v>2047</v>
       </c>
       <c r="C492">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D492">
         <v>0</v>
       </c>
       <c r="E492">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F492">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="493" spans="1:6">
@@ -10594,16 +10606,16 @@
         <v>2048</v>
       </c>
       <c r="C493">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D493">
         <v>0</v>
       </c>
       <c r="E493">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F493">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494" spans="1:6">
@@ -10614,16 +10626,16 @@
         <v>2049</v>
       </c>
       <c r="C494">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D494">
         <v>0</v>
       </c>
       <c r="E494">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F494">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="495" spans="1:6">
@@ -10634,15 +10646,535 @@
         <v>2050</v>
       </c>
       <c r="C495">
+        <v>0</v>
+      </c>
+      <c r="D495">
+        <v>0</v>
+      </c>
+      <c r="E495">
+        <v>0</v>
+      </c>
+      <c r="F495">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="496" spans="1:6">
+      <c r="A496" t="s">
+        <v>25</v>
+      </c>
+      <c r="B496">
+        <v>2025</v>
+      </c>
+      <c r="C496">
         <v>1</v>
       </c>
-      <c r="D495">
-        <v>0</v>
-      </c>
-      <c r="E495">
+      <c r="D496">
+        <v>0</v>
+      </c>
+      <c r="E496">
         <v>1</v>
       </c>
-      <c r="F495">
+      <c r="F496">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="497" spans="1:6">
+      <c r="A497" t="s">
+        <v>25</v>
+      </c>
+      <c r="B497">
+        <v>2026</v>
+      </c>
+      <c r="C497">
+        <v>1</v>
+      </c>
+      <c r="D497">
+        <v>0</v>
+      </c>
+      <c r="E497">
+        <v>1</v>
+      </c>
+      <c r="F497">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="498" spans="1:6">
+      <c r="A498" t="s">
+        <v>25</v>
+      </c>
+      <c r="B498">
+        <v>2027</v>
+      </c>
+      <c r="C498">
+        <v>1</v>
+      </c>
+      <c r="D498">
+        <v>0</v>
+      </c>
+      <c r="E498">
+        <v>1</v>
+      </c>
+      <c r="F498">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="499" spans="1:6">
+      <c r="A499" t="s">
+        <v>25</v>
+      </c>
+      <c r="B499">
+        <v>2028</v>
+      </c>
+      <c r="C499">
+        <v>1</v>
+      </c>
+      <c r="D499">
+        <v>0</v>
+      </c>
+      <c r="E499">
+        <v>1</v>
+      </c>
+      <c r="F499">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="500" spans="1:6">
+      <c r="A500" t="s">
+        <v>25</v>
+      </c>
+      <c r="B500">
+        <v>2029</v>
+      </c>
+      <c r="C500">
+        <v>1</v>
+      </c>
+      <c r="D500">
+        <v>0</v>
+      </c>
+      <c r="E500">
+        <v>1</v>
+      </c>
+      <c r="F500">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="501" spans="1:6">
+      <c r="A501" t="s">
+        <v>25</v>
+      </c>
+      <c r="B501">
+        <v>2030</v>
+      </c>
+      <c r="C501">
+        <v>1</v>
+      </c>
+      <c r="D501">
+        <v>0</v>
+      </c>
+      <c r="E501">
+        <v>1</v>
+      </c>
+      <c r="F501">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="502" spans="1:6">
+      <c r="A502" t="s">
+        <v>25</v>
+      </c>
+      <c r="B502">
+        <v>2031</v>
+      </c>
+      <c r="C502">
+        <v>1</v>
+      </c>
+      <c r="D502">
+        <v>0</v>
+      </c>
+      <c r="E502">
+        <v>1</v>
+      </c>
+      <c r="F502">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="503" spans="1:6">
+      <c r="A503" t="s">
+        <v>25</v>
+      </c>
+      <c r="B503">
+        <v>2032</v>
+      </c>
+      <c r="C503">
+        <v>1</v>
+      </c>
+      <c r="D503">
+        <v>0</v>
+      </c>
+      <c r="E503">
+        <v>1</v>
+      </c>
+      <c r="F503">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="504" spans="1:6">
+      <c r="A504" t="s">
+        <v>25</v>
+      </c>
+      <c r="B504">
+        <v>2033</v>
+      </c>
+      <c r="C504">
+        <v>1</v>
+      </c>
+      <c r="D504">
+        <v>0</v>
+      </c>
+      <c r="E504">
+        <v>1</v>
+      </c>
+      <c r="F504">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="505" spans="1:6">
+      <c r="A505" t="s">
+        <v>25</v>
+      </c>
+      <c r="B505">
+        <v>2034</v>
+      </c>
+      <c r="C505">
+        <v>1</v>
+      </c>
+      <c r="D505">
+        <v>0</v>
+      </c>
+      <c r="E505">
+        <v>1</v>
+      </c>
+      <c r="F505">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="506" spans="1:6">
+      <c r="A506" t="s">
+        <v>25</v>
+      </c>
+      <c r="B506">
+        <v>2035</v>
+      </c>
+      <c r="C506">
+        <v>1</v>
+      </c>
+      <c r="D506">
+        <v>0</v>
+      </c>
+      <c r="E506">
+        <v>1</v>
+      </c>
+      <c r="F506">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="507" spans="1:6">
+      <c r="A507" t="s">
+        <v>25</v>
+      </c>
+      <c r="B507">
+        <v>2036</v>
+      </c>
+      <c r="C507">
+        <v>1</v>
+      </c>
+      <c r="D507">
+        <v>0</v>
+      </c>
+      <c r="E507">
+        <v>1</v>
+      </c>
+      <c r="F507">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="508" spans="1:6">
+      <c r="A508" t="s">
+        <v>25</v>
+      </c>
+      <c r="B508">
+        <v>2037</v>
+      </c>
+      <c r="C508">
+        <v>1</v>
+      </c>
+      <c r="D508">
+        <v>0</v>
+      </c>
+      <c r="E508">
+        <v>1</v>
+      </c>
+      <c r="F508">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="509" spans="1:6">
+      <c r="A509" t="s">
+        <v>25</v>
+      </c>
+      <c r="B509">
+        <v>2038</v>
+      </c>
+      <c r="C509">
+        <v>1</v>
+      </c>
+      <c r="D509">
+        <v>0</v>
+      </c>
+      <c r="E509">
+        <v>1</v>
+      </c>
+      <c r="F509">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="510" spans="1:6">
+      <c r="A510" t="s">
+        <v>25</v>
+      </c>
+      <c r="B510">
+        <v>2039</v>
+      </c>
+      <c r="C510">
+        <v>1</v>
+      </c>
+      <c r="D510">
+        <v>0</v>
+      </c>
+      <c r="E510">
+        <v>1</v>
+      </c>
+      <c r="F510">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="511" spans="1:6">
+      <c r="A511" t="s">
+        <v>25</v>
+      </c>
+      <c r="B511">
+        <v>2040</v>
+      </c>
+      <c r="C511">
+        <v>1</v>
+      </c>
+      <c r="D511">
+        <v>0</v>
+      </c>
+      <c r="E511">
+        <v>1</v>
+      </c>
+      <c r="F511">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="512" spans="1:6">
+      <c r="A512" t="s">
+        <v>25</v>
+      </c>
+      <c r="B512">
+        <v>2041</v>
+      </c>
+      <c r="C512">
+        <v>1</v>
+      </c>
+      <c r="D512">
+        <v>0</v>
+      </c>
+      <c r="E512">
+        <v>1</v>
+      </c>
+      <c r="F512">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="513" spans="1:6">
+      <c r="A513" t="s">
+        <v>25</v>
+      </c>
+      <c r="B513">
+        <v>2042</v>
+      </c>
+      <c r="C513">
+        <v>1</v>
+      </c>
+      <c r="D513">
+        <v>0</v>
+      </c>
+      <c r="E513">
+        <v>1</v>
+      </c>
+      <c r="F513">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="514" spans="1:6">
+      <c r="A514" t="s">
+        <v>25</v>
+      </c>
+      <c r="B514">
+        <v>2043</v>
+      </c>
+      <c r="C514">
+        <v>1</v>
+      </c>
+      <c r="D514">
+        <v>0</v>
+      </c>
+      <c r="E514">
+        <v>1</v>
+      </c>
+      <c r="F514">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="515" spans="1:6">
+      <c r="A515" t="s">
+        <v>25</v>
+      </c>
+      <c r="B515">
+        <v>2044</v>
+      </c>
+      <c r="C515">
+        <v>1</v>
+      </c>
+      <c r="D515">
+        <v>0</v>
+      </c>
+      <c r="E515">
+        <v>1</v>
+      </c>
+      <c r="F515">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="516" spans="1:6">
+      <c r="A516" t="s">
+        <v>25</v>
+      </c>
+      <c r="B516">
+        <v>2045</v>
+      </c>
+      <c r="C516">
+        <v>1</v>
+      </c>
+      <c r="D516">
+        <v>0</v>
+      </c>
+      <c r="E516">
+        <v>1</v>
+      </c>
+      <c r="F516">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="517" spans="1:6">
+      <c r="A517" t="s">
+        <v>25</v>
+      </c>
+      <c r="B517">
+        <v>2046</v>
+      </c>
+      <c r="C517">
+        <v>1</v>
+      </c>
+      <c r="D517">
+        <v>0</v>
+      </c>
+      <c r="E517">
+        <v>1</v>
+      </c>
+      <c r="F517">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="518" spans="1:6">
+      <c r="A518" t="s">
+        <v>25</v>
+      </c>
+      <c r="B518">
+        <v>2047</v>
+      </c>
+      <c r="C518">
+        <v>1</v>
+      </c>
+      <c r="D518">
+        <v>0</v>
+      </c>
+      <c r="E518">
+        <v>1</v>
+      </c>
+      <c r="F518">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="519" spans="1:6">
+      <c r="A519" t="s">
+        <v>25</v>
+      </c>
+      <c r="B519">
+        <v>2048</v>
+      </c>
+      <c r="C519">
+        <v>1</v>
+      </c>
+      <c r="D519">
+        <v>0</v>
+      </c>
+      <c r="E519">
+        <v>1</v>
+      </c>
+      <c r="F519">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="520" spans="1:6">
+      <c r="A520" t="s">
+        <v>25</v>
+      </c>
+      <c r="B520">
+        <v>2049</v>
+      </c>
+      <c r="C520">
+        <v>1</v>
+      </c>
+      <c r="D520">
+        <v>0</v>
+      </c>
+      <c r="E520">
+        <v>1</v>
+      </c>
+      <c r="F520">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="521" spans="1:6">
+      <c r="A521" t="s">
+        <v>25</v>
+      </c>
+      <c r="B521">
+        <v>2050</v>
+      </c>
+      <c r="C521">
+        <v>1</v>
+      </c>
+      <c r="D521">
+        <v>0</v>
+      </c>
+      <c r="E521">
+        <v>1</v>
+      </c>
+      <c r="F521">
         <v>0.5</v>
       </c>
     </row>
@@ -10653,12 +11185,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F261"/>
+  <dimension ref="A1:F313"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -10678,7 +11210,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B2">
         <v>2025</v>
@@ -10698,7 +11230,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B3">
         <v>2026</v>
@@ -10718,7 +11250,7 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B4">
         <v>2027</v>
@@ -10738,7 +11270,7 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B5">
         <v>2028</v>
@@ -10758,7 +11290,7 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B6">
         <v>2029</v>
@@ -10778,7 +11310,7 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B7">
         <v>2030</v>
@@ -10798,7 +11330,7 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B8">
         <v>2031</v>
@@ -10818,7 +11350,7 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B9">
         <v>2032</v>
@@ -10838,7 +11370,7 @@
     </row>
     <row r="10" spans="1:6">
       <c r="A10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B10">
         <v>2033</v>
@@ -10858,7 +11390,7 @@
     </row>
     <row r="11" spans="1:6">
       <c r="A11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B11">
         <v>2034</v>
@@ -10878,7 +11410,7 @@
     </row>
     <row r="12" spans="1:6">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B12">
         <v>2035</v>
@@ -10898,7 +11430,7 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B13">
         <v>2036</v>
@@ -10918,7 +11450,7 @@
     </row>
     <row r="14" spans="1:6">
       <c r="A14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14">
         <v>2037</v>
@@ -10938,7 +11470,7 @@
     </row>
     <row r="15" spans="1:6">
       <c r="A15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B15">
         <v>2038</v>
@@ -10958,7 +11490,7 @@
     </row>
     <row r="16" spans="1:6">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B16">
         <v>2039</v>
@@ -10978,7 +11510,7 @@
     </row>
     <row r="17" spans="1:6">
       <c r="A17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B17">
         <v>2040</v>
@@ -10998,7 +11530,7 @@
     </row>
     <row r="18" spans="1:6">
       <c r="A18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B18">
         <v>2041</v>
@@ -11018,7 +11550,7 @@
     </row>
     <row r="19" spans="1:6">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B19">
         <v>2042</v>
@@ -11038,7 +11570,7 @@
     </row>
     <row r="20" spans="1:6">
       <c r="A20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B20">
         <v>2043</v>
@@ -11058,7 +11590,7 @@
     </row>
     <row r="21" spans="1:6">
       <c r="A21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B21">
         <v>2044</v>
@@ -11078,7 +11610,7 @@
     </row>
     <row r="22" spans="1:6">
       <c r="A22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B22">
         <v>2045</v>
@@ -11098,7 +11630,7 @@
     </row>
     <row r="23" spans="1:6">
       <c r="A23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B23">
         <v>2046</v>
@@ -11118,7 +11650,7 @@
     </row>
     <row r="24" spans="1:6">
       <c r="A24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B24">
         <v>2047</v>
@@ -11138,7 +11670,7 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B25">
         <v>2048</v>
@@ -11158,7 +11690,7 @@
     </row>
     <row r="26" spans="1:6">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B26">
         <v>2049</v>
@@ -11178,7 +11710,7 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B27">
         <v>2050</v>
@@ -11198,7 +11730,7 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B28">
         <v>2025</v>
@@ -11218,7 +11750,7 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B29">
         <v>2026</v>
@@ -11238,7 +11770,7 @@
     </row>
     <row r="30" spans="1:6">
       <c r="A30" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B30">
         <v>2027</v>
@@ -11258,7 +11790,7 @@
     </row>
     <row r="31" spans="1:6">
       <c r="A31" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B31">
         <v>2028</v>
@@ -11278,7 +11810,7 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B32">
         <v>2029</v>
@@ -11298,7 +11830,7 @@
     </row>
     <row r="33" spans="1:6">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B33">
         <v>2030</v>
@@ -11318,7 +11850,7 @@
     </row>
     <row r="34" spans="1:6">
       <c r="A34" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B34">
         <v>2031</v>
@@ -11338,7 +11870,7 @@
     </row>
     <row r="35" spans="1:6">
       <c r="A35" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B35">
         <v>2032</v>
@@ -11358,7 +11890,7 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B36">
         <v>2033</v>
@@ -11378,7 +11910,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B37">
         <v>2034</v>
@@ -11398,7 +11930,7 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B38">
         <v>2035</v>
@@ -11418,7 +11950,7 @@
     </row>
     <row r="39" spans="1:6">
       <c r="A39" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B39">
         <v>2036</v>
@@ -11438,7 +11970,7 @@
     </row>
     <row r="40" spans="1:6">
       <c r="A40" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B40">
         <v>2037</v>
@@ -11458,7 +11990,7 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B41">
         <v>2038</v>
@@ -11478,7 +12010,7 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B42">
         <v>2039</v>
@@ -11498,7 +12030,7 @@
     </row>
     <row r="43" spans="1:6">
       <c r="A43" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B43">
         <v>2040</v>
@@ -11518,7 +12050,7 @@
     </row>
     <row r="44" spans="1:6">
       <c r="A44" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B44">
         <v>2041</v>
@@ -11538,7 +12070,7 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B45">
         <v>2042</v>
@@ -11558,7 +12090,7 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B46">
         <v>2043</v>
@@ -11578,7 +12110,7 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B47">
         <v>2044</v>
@@ -11598,7 +12130,7 @@
     </row>
     <row r="48" spans="1:6">
       <c r="A48" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B48">
         <v>2045</v>
@@ -11618,7 +12150,7 @@
     </row>
     <row r="49" spans="1:6">
       <c r="A49" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B49">
         <v>2046</v>
@@ -11638,7 +12170,7 @@
     </row>
     <row r="50" spans="1:6">
       <c r="A50" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B50">
         <v>2047</v>
@@ -11658,7 +12190,7 @@
     </row>
     <row r="51" spans="1:6">
       <c r="A51" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B51">
         <v>2048</v>
@@ -11678,7 +12210,7 @@
     </row>
     <row r="52" spans="1:6">
       <c r="A52" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B52">
         <v>2049</v>
@@ -11698,7 +12230,7 @@
     </row>
     <row r="53" spans="1:6">
       <c r="A53" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B53">
         <v>2050</v>
@@ -11718,7 +12250,7 @@
     </row>
     <row r="54" spans="1:6">
       <c r="A54" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B54">
         <v>2025</v>
@@ -11738,7 +12270,7 @@
     </row>
     <row r="55" spans="1:6">
       <c r="A55" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B55">
         <v>2026</v>
@@ -11758,7 +12290,7 @@
     </row>
     <row r="56" spans="1:6">
       <c r="A56" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B56">
         <v>2027</v>
@@ -11778,7 +12310,7 @@
     </row>
     <row r="57" spans="1:6">
       <c r="A57" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B57">
         <v>2028</v>
@@ -11798,7 +12330,7 @@
     </row>
     <row r="58" spans="1:6">
       <c r="A58" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B58">
         <v>2029</v>
@@ -11818,7 +12350,7 @@
     </row>
     <row r="59" spans="1:6">
       <c r="A59" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B59">
         <v>2030</v>
@@ -11838,7 +12370,7 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B60">
         <v>2031</v>
@@ -11858,7 +12390,7 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B61">
         <v>2032</v>
@@ -11878,7 +12410,7 @@
     </row>
     <row r="62" spans="1:6">
       <c r="A62" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B62">
         <v>2033</v>
@@ -11898,7 +12430,7 @@
     </row>
     <row r="63" spans="1:6">
       <c r="A63" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B63">
         <v>2034</v>
@@ -11918,7 +12450,7 @@
     </row>
     <row r="64" spans="1:6">
       <c r="A64" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B64">
         <v>2035</v>
@@ -11938,7 +12470,7 @@
     </row>
     <row r="65" spans="1:6">
       <c r="A65" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B65">
         <v>2036</v>
@@ -11958,7 +12490,7 @@
     </row>
     <row r="66" spans="1:6">
       <c r="A66" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B66">
         <v>2037</v>
@@ -11978,7 +12510,7 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B67">
         <v>2038</v>
@@ -11998,7 +12530,7 @@
     </row>
     <row r="68" spans="1:6">
       <c r="A68" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B68">
         <v>2039</v>
@@ -12018,7 +12550,7 @@
     </row>
     <row r="69" spans="1:6">
       <c r="A69" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B69">
         <v>2040</v>
@@ -12038,7 +12570,7 @@
     </row>
     <row r="70" spans="1:6">
       <c r="A70" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B70">
         <v>2041</v>
@@ -12058,7 +12590,7 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B71">
         <v>2042</v>
@@ -12078,7 +12610,7 @@
     </row>
     <row r="72" spans="1:6">
       <c r="A72" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B72">
         <v>2043</v>
@@ -12098,7 +12630,7 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B73">
         <v>2044</v>
@@ -12118,7 +12650,7 @@
     </row>
     <row r="74" spans="1:6">
       <c r="A74" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B74">
         <v>2045</v>
@@ -12138,7 +12670,7 @@
     </row>
     <row r="75" spans="1:6">
       <c r="A75" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B75">
         <v>2046</v>
@@ -12158,7 +12690,7 @@
     </row>
     <row r="76" spans="1:6">
       <c r="A76" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B76">
         <v>2047</v>
@@ -12178,7 +12710,7 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B77">
         <v>2048</v>
@@ -12198,7 +12730,7 @@
     </row>
     <row r="78" spans="1:6">
       <c r="A78" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B78">
         <v>2049</v>
@@ -12218,7 +12750,7 @@
     </row>
     <row r="79" spans="1:6">
       <c r="A79" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B79">
         <v>2050</v>
@@ -12238,7 +12770,7 @@
     </row>
     <row r="80" spans="1:6">
       <c r="A80" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B80">
         <v>2025</v>
@@ -12258,7 +12790,7 @@
     </row>
     <row r="81" spans="1:6">
       <c r="A81" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B81">
         <v>2026</v>
@@ -12278,7 +12810,7 @@
     </row>
     <row r="82" spans="1:6">
       <c r="A82" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B82">
         <v>2027</v>
@@ -12298,7 +12830,7 @@
     </row>
     <row r="83" spans="1:6">
       <c r="A83" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B83">
         <v>2028</v>
@@ -12318,7 +12850,7 @@
     </row>
     <row r="84" spans="1:6">
       <c r="A84" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B84">
         <v>2029</v>
@@ -12338,7 +12870,7 @@
     </row>
     <row r="85" spans="1:6">
       <c r="A85" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B85">
         <v>2030</v>
@@ -12358,7 +12890,7 @@
     </row>
     <row r="86" spans="1:6">
       <c r="A86" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B86">
         <v>2031</v>
@@ -12378,7 +12910,7 @@
     </row>
     <row r="87" spans="1:6">
       <c r="A87" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B87">
         <v>2032</v>
@@ -12398,7 +12930,7 @@
     </row>
     <row r="88" spans="1:6">
       <c r="A88" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B88">
         <v>2033</v>
@@ -12418,7 +12950,7 @@
     </row>
     <row r="89" spans="1:6">
       <c r="A89" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B89">
         <v>2034</v>
@@ -12438,7 +12970,7 @@
     </row>
     <row r="90" spans="1:6">
       <c r="A90" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B90">
         <v>2035</v>
@@ -12458,7 +12990,7 @@
     </row>
     <row r="91" spans="1:6">
       <c r="A91" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B91">
         <v>2036</v>
@@ -12478,7 +13010,7 @@
     </row>
     <row r="92" spans="1:6">
       <c r="A92" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B92">
         <v>2037</v>
@@ -12498,7 +13030,7 @@
     </row>
     <row r="93" spans="1:6">
       <c r="A93" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B93">
         <v>2038</v>
@@ -12518,7 +13050,7 @@
     </row>
     <row r="94" spans="1:6">
       <c r="A94" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B94">
         <v>2039</v>
@@ -12538,7 +13070,7 @@
     </row>
     <row r="95" spans="1:6">
       <c r="A95" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B95">
         <v>2040</v>
@@ -12558,7 +13090,7 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B96">
         <v>2041</v>
@@ -12578,7 +13110,7 @@
     </row>
     <row r="97" spans="1:6">
       <c r="A97" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B97">
         <v>2042</v>
@@ -12598,7 +13130,7 @@
     </row>
     <row r="98" spans="1:6">
       <c r="A98" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B98">
         <v>2043</v>
@@ -12618,7 +13150,7 @@
     </row>
     <row r="99" spans="1:6">
       <c r="A99" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B99">
         <v>2044</v>
@@ -12638,7 +13170,7 @@
     </row>
     <row r="100" spans="1:6">
       <c r="A100" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B100">
         <v>2045</v>
@@ -12658,7 +13190,7 @@
     </row>
     <row r="101" spans="1:6">
       <c r="A101" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B101">
         <v>2046</v>
@@ -12678,7 +13210,7 @@
     </row>
     <row r="102" spans="1:6">
       <c r="A102" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B102">
         <v>2047</v>
@@ -12698,7 +13230,7 @@
     </row>
     <row r="103" spans="1:6">
       <c r="A103" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B103">
         <v>2048</v>
@@ -12718,7 +13250,7 @@
     </row>
     <row r="104" spans="1:6">
       <c r="A104" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B104">
         <v>2049</v>
@@ -12738,7 +13270,7 @@
     </row>
     <row r="105" spans="1:6">
       <c r="A105" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B105">
         <v>2050</v>
@@ -12758,7 +13290,7 @@
     </row>
     <row r="106" spans="1:6">
       <c r="A106" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B106">
         <v>2025</v>
@@ -12778,7 +13310,7 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B107">
         <v>2026</v>
@@ -12798,7 +13330,7 @@
     </row>
     <row r="108" spans="1:6">
       <c r="A108" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B108">
         <v>2027</v>
@@ -12818,7 +13350,7 @@
     </row>
     <row r="109" spans="1:6">
       <c r="A109" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B109">
         <v>2028</v>
@@ -12838,7 +13370,7 @@
     </row>
     <row r="110" spans="1:6">
       <c r="A110" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B110">
         <v>2029</v>
@@ -12858,7 +13390,7 @@
     </row>
     <row r="111" spans="1:6">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B111">
         <v>2030</v>
@@ -12878,7 +13410,7 @@
     </row>
     <row r="112" spans="1:6">
       <c r="A112" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B112">
         <v>2031</v>
@@ -12898,7 +13430,7 @@
     </row>
     <row r="113" spans="1:6">
       <c r="A113" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B113">
         <v>2032</v>
@@ -12918,7 +13450,7 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B114">
         <v>2033</v>
@@ -12938,7 +13470,7 @@
     </row>
     <row r="115" spans="1:6">
       <c r="A115" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B115">
         <v>2034</v>
@@ -12958,7 +13490,7 @@
     </row>
     <row r="116" spans="1:6">
       <c r="A116" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B116">
         <v>2035</v>
@@ -12978,7 +13510,7 @@
     </row>
     <row r="117" spans="1:6">
       <c r="A117" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B117">
         <v>2036</v>
@@ -12998,7 +13530,7 @@
     </row>
     <row r="118" spans="1:6">
       <c r="A118" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B118">
         <v>2037</v>
@@ -13018,7 +13550,7 @@
     </row>
     <row r="119" spans="1:6">
       <c r="A119" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B119">
         <v>2038</v>
@@ -13038,7 +13570,7 @@
     </row>
     <row r="120" spans="1:6">
       <c r="A120" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B120">
         <v>2039</v>
@@ -13058,7 +13590,7 @@
     </row>
     <row r="121" spans="1:6">
       <c r="A121" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B121">
         <v>2040</v>
@@ -13078,7 +13610,7 @@
     </row>
     <row r="122" spans="1:6">
       <c r="A122" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B122">
         <v>2041</v>
@@ -13098,7 +13630,7 @@
     </row>
     <row r="123" spans="1:6">
       <c r="A123" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B123">
         <v>2042</v>
@@ -13118,7 +13650,7 @@
     </row>
     <row r="124" spans="1:6">
       <c r="A124" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B124">
         <v>2043</v>
@@ -13138,7 +13670,7 @@
     </row>
     <row r="125" spans="1:6">
       <c r="A125" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B125">
         <v>2044</v>
@@ -13158,7 +13690,7 @@
     </row>
     <row r="126" spans="1:6">
       <c r="A126" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B126">
         <v>2045</v>
@@ -13178,7 +13710,7 @@
     </row>
     <row r="127" spans="1:6">
       <c r="A127" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B127">
         <v>2046</v>
@@ -13198,7 +13730,7 @@
     </row>
     <row r="128" spans="1:6">
       <c r="A128" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B128">
         <v>2047</v>
@@ -13218,7 +13750,7 @@
     </row>
     <row r="129" spans="1:6">
       <c r="A129" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B129">
         <v>2048</v>
@@ -13238,7 +13770,7 @@
     </row>
     <row r="130" spans="1:6">
       <c r="A130" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B130">
         <v>2049</v>
@@ -13258,7 +13790,7 @@
     </row>
     <row r="131" spans="1:6">
       <c r="A131" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B131">
         <v>2050</v>
@@ -13278,7 +13810,7 @@
     </row>
     <row r="132" spans="1:6">
       <c r="A132" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B132">
         <v>2025</v>
@@ -13298,7 +13830,7 @@
     </row>
     <row r="133" spans="1:6">
       <c r="A133" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B133">
         <v>2026</v>
@@ -13318,7 +13850,7 @@
     </row>
     <row r="134" spans="1:6">
       <c r="A134" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B134">
         <v>2027</v>
@@ -13338,7 +13870,7 @@
     </row>
     <row r="135" spans="1:6">
       <c r="A135" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B135">
         <v>2028</v>
@@ -13358,7 +13890,7 @@
     </row>
     <row r="136" spans="1:6">
       <c r="A136" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B136">
         <v>2029</v>
@@ -13378,7 +13910,7 @@
     </row>
     <row r="137" spans="1:6">
       <c r="A137" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B137">
         <v>2030</v>
@@ -13398,7 +13930,7 @@
     </row>
     <row r="138" spans="1:6">
       <c r="A138" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B138">
         <v>2031</v>
@@ -13418,7 +13950,7 @@
     </row>
     <row r="139" spans="1:6">
       <c r="A139" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B139">
         <v>2032</v>
@@ -13438,7 +13970,7 @@
     </row>
     <row r="140" spans="1:6">
       <c r="A140" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B140">
         <v>2033</v>
@@ -13458,7 +13990,7 @@
     </row>
     <row r="141" spans="1:6">
       <c r="A141" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B141">
         <v>2034</v>
@@ -13478,7 +14010,7 @@
     </row>
     <row r="142" spans="1:6">
       <c r="A142" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B142">
         <v>2035</v>
@@ -13498,7 +14030,7 @@
     </row>
     <row r="143" spans="1:6">
       <c r="A143" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B143">
         <v>2036</v>
@@ -13518,7 +14050,7 @@
     </row>
     <row r="144" spans="1:6">
       <c r="A144" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B144">
         <v>2037</v>
@@ -13538,7 +14070,7 @@
     </row>
     <row r="145" spans="1:6">
       <c r="A145" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B145">
         <v>2038</v>
@@ -13558,7 +14090,7 @@
     </row>
     <row r="146" spans="1:6">
       <c r="A146" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B146">
         <v>2039</v>
@@ -13578,7 +14110,7 @@
     </row>
     <row r="147" spans="1:6">
       <c r="A147" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B147">
         <v>2040</v>
@@ -13598,7 +14130,7 @@
     </row>
     <row r="148" spans="1:6">
       <c r="A148" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B148">
         <v>2041</v>
@@ -13618,7 +14150,7 @@
     </row>
     <row r="149" spans="1:6">
       <c r="A149" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B149">
         <v>2042</v>
@@ -13638,7 +14170,7 @@
     </row>
     <row r="150" spans="1:6">
       <c r="A150" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B150">
         <v>2043</v>
@@ -13658,7 +14190,7 @@
     </row>
     <row r="151" spans="1:6">
       <c r="A151" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B151">
         <v>2044</v>
@@ -13678,7 +14210,7 @@
     </row>
     <row r="152" spans="1:6">
       <c r="A152" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B152">
         <v>2045</v>
@@ -13698,7 +14230,7 @@
     </row>
     <row r="153" spans="1:6">
       <c r="A153" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B153">
         <v>2046</v>
@@ -13718,7 +14250,7 @@
     </row>
     <row r="154" spans="1:6">
       <c r="A154" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B154">
         <v>2047</v>
@@ -13738,7 +14270,7 @@
     </row>
     <row r="155" spans="1:6">
       <c r="A155" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B155">
         <v>2048</v>
@@ -13758,7 +14290,7 @@
     </row>
     <row r="156" spans="1:6">
       <c r="A156" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B156">
         <v>2049</v>
@@ -13778,7 +14310,7 @@
     </row>
     <row r="157" spans="1:6">
       <c r="A157" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B157">
         <v>2050</v>
@@ -13798,7 +14330,7 @@
     </row>
     <row r="158" spans="1:6">
       <c r="A158" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B158">
         <v>2025</v>
@@ -13818,7 +14350,7 @@
     </row>
     <row r="159" spans="1:6">
       <c r="A159" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B159">
         <v>2026</v>
@@ -13838,7 +14370,7 @@
     </row>
     <row r="160" spans="1:6">
       <c r="A160" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B160">
         <v>2027</v>
@@ -13858,7 +14390,7 @@
     </row>
     <row r="161" spans="1:6">
       <c r="A161" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B161">
         <v>2028</v>
@@ -13878,7 +14410,7 @@
     </row>
     <row r="162" spans="1:6">
       <c r="A162" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B162">
         <v>2029</v>
@@ -13898,7 +14430,7 @@
     </row>
     <row r="163" spans="1:6">
       <c r="A163" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B163">
         <v>2030</v>
@@ -13918,7 +14450,7 @@
     </row>
     <row r="164" spans="1:6">
       <c r="A164" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B164">
         <v>2031</v>
@@ -13938,7 +14470,7 @@
     </row>
     <row r="165" spans="1:6">
       <c r="A165" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B165">
         <v>2032</v>
@@ -13958,7 +14490,7 @@
     </row>
     <row r="166" spans="1:6">
       <c r="A166" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B166">
         <v>2033</v>
@@ -13978,7 +14510,7 @@
     </row>
     <row r="167" spans="1:6">
       <c r="A167" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B167">
         <v>2034</v>
@@ -13998,7 +14530,7 @@
     </row>
     <row r="168" spans="1:6">
       <c r="A168" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B168">
         <v>2035</v>
@@ -14018,7 +14550,7 @@
     </row>
     <row r="169" spans="1:6">
       <c r="A169" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B169">
         <v>2036</v>
@@ -14038,7 +14570,7 @@
     </row>
     <row r="170" spans="1:6">
       <c r="A170" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B170">
         <v>2037</v>
@@ -14058,7 +14590,7 @@
     </row>
     <row r="171" spans="1:6">
       <c r="A171" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B171">
         <v>2038</v>
@@ -14078,7 +14610,7 @@
     </row>
     <row r="172" spans="1:6">
       <c r="A172" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B172">
         <v>2039</v>
@@ -14098,7 +14630,7 @@
     </row>
     <row r="173" spans="1:6">
       <c r="A173" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B173">
         <v>2040</v>
@@ -14118,7 +14650,7 @@
     </row>
     <row r="174" spans="1:6">
       <c r="A174" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B174">
         <v>2041</v>
@@ -14138,7 +14670,7 @@
     </row>
     <row r="175" spans="1:6">
       <c r="A175" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B175">
         <v>2042</v>
@@ -14158,7 +14690,7 @@
     </row>
     <row r="176" spans="1:6">
       <c r="A176" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B176">
         <v>2043</v>
@@ -14178,7 +14710,7 @@
     </row>
     <row r="177" spans="1:6">
       <c r="A177" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B177">
         <v>2044</v>
@@ -14198,7 +14730,7 @@
     </row>
     <row r="178" spans="1:6">
       <c r="A178" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B178">
         <v>2045</v>
@@ -14218,7 +14750,7 @@
     </row>
     <row r="179" spans="1:6">
       <c r="A179" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B179">
         <v>2046</v>
@@ -14238,7 +14770,7 @@
     </row>
     <row r="180" spans="1:6">
       <c r="A180" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B180">
         <v>2047</v>
@@ -14258,7 +14790,7 @@
     </row>
     <row r="181" spans="1:6">
       <c r="A181" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B181">
         <v>2048</v>
@@ -14278,7 +14810,7 @@
     </row>
     <row r="182" spans="1:6">
       <c r="A182" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B182">
         <v>2049</v>
@@ -14298,7 +14830,7 @@
     </row>
     <row r="183" spans="1:6">
       <c r="A183" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B183">
         <v>2050</v>
@@ -14318,7 +14850,7 @@
     </row>
     <row r="184" spans="1:6">
       <c r="A184" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B184">
         <v>2025</v>
@@ -14338,7 +14870,7 @@
     </row>
     <row r="185" spans="1:6">
       <c r="A185" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B185">
         <v>2026</v>
@@ -14358,7 +14890,7 @@
     </row>
     <row r="186" spans="1:6">
       <c r="A186" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B186">
         <v>2027</v>
@@ -14378,7 +14910,7 @@
     </row>
     <row r="187" spans="1:6">
       <c r="A187" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B187">
         <v>2028</v>
@@ -14398,7 +14930,7 @@
     </row>
     <row r="188" spans="1:6">
       <c r="A188" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B188">
         <v>2029</v>
@@ -14418,7 +14950,7 @@
     </row>
     <row r="189" spans="1:6">
       <c r="A189" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B189">
         <v>2030</v>
@@ -14438,7 +14970,7 @@
     </row>
     <row r="190" spans="1:6">
       <c r="A190" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B190">
         <v>2031</v>
@@ -14458,7 +14990,7 @@
     </row>
     <row r="191" spans="1:6">
       <c r="A191" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B191">
         <v>2032</v>
@@ -14478,7 +15010,7 @@
     </row>
     <row r="192" spans="1:6">
       <c r="A192" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B192">
         <v>2033</v>
@@ -14498,7 +15030,7 @@
     </row>
     <row r="193" spans="1:6">
       <c r="A193" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B193">
         <v>2034</v>
@@ -14518,7 +15050,7 @@
     </row>
     <row r="194" spans="1:6">
       <c r="A194" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B194">
         <v>2035</v>
@@ -14538,7 +15070,7 @@
     </row>
     <row r="195" spans="1:6">
       <c r="A195" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B195">
         <v>2036</v>
@@ -14558,7 +15090,7 @@
     </row>
     <row r="196" spans="1:6">
       <c r="A196" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B196">
         <v>2037</v>
@@ -14578,7 +15110,7 @@
     </row>
     <row r="197" spans="1:6">
       <c r="A197" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B197">
         <v>2038</v>
@@ -14598,7 +15130,7 @@
     </row>
     <row r="198" spans="1:6">
       <c r="A198" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B198">
         <v>2039</v>
@@ -14618,7 +15150,7 @@
     </row>
     <row r="199" spans="1:6">
       <c r="A199" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B199">
         <v>2040</v>
@@ -14638,7 +15170,7 @@
     </row>
     <row r="200" spans="1:6">
       <c r="A200" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B200">
         <v>2041</v>
@@ -14658,7 +15190,7 @@
     </row>
     <row r="201" spans="1:6">
       <c r="A201" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B201">
         <v>2042</v>
@@ -14678,7 +15210,7 @@
     </row>
     <row r="202" spans="1:6">
       <c r="A202" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B202">
         <v>2043</v>
@@ -14698,7 +15230,7 @@
     </row>
     <row r="203" spans="1:6">
       <c r="A203" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B203">
         <v>2044</v>
@@ -14718,7 +15250,7 @@
     </row>
     <row r="204" spans="1:6">
       <c r="A204" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B204">
         <v>2045</v>
@@ -14738,7 +15270,7 @@
     </row>
     <row r="205" spans="1:6">
       <c r="A205" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B205">
         <v>2046</v>
@@ -14758,7 +15290,7 @@
     </row>
     <row r="206" spans="1:6">
       <c r="A206" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B206">
         <v>2047</v>
@@ -14778,7 +15310,7 @@
     </row>
     <row r="207" spans="1:6">
       <c r="A207" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B207">
         <v>2048</v>
@@ -14798,7 +15330,7 @@
     </row>
     <row r="208" spans="1:6">
       <c r="A208" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B208">
         <v>2049</v>
@@ -14818,7 +15350,7 @@
     </row>
     <row r="209" spans="1:6">
       <c r="A209" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B209">
         <v>2050</v>
@@ -14838,7 +15370,7 @@
     </row>
     <row r="210" spans="1:6">
       <c r="A210" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B210">
         <v>2025</v>
@@ -14858,7 +15390,7 @@
     </row>
     <row r="211" spans="1:6">
       <c r="A211" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B211">
         <v>2026</v>
@@ -14878,7 +15410,7 @@
     </row>
     <row r="212" spans="1:6">
       <c r="A212" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B212">
         <v>2027</v>
@@ -14898,7 +15430,7 @@
     </row>
     <row r="213" spans="1:6">
       <c r="A213" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B213">
         <v>2028</v>
@@ -14918,7 +15450,7 @@
     </row>
     <row r="214" spans="1:6">
       <c r="A214" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B214">
         <v>2029</v>
@@ -14938,7 +15470,7 @@
     </row>
     <row r="215" spans="1:6">
       <c r="A215" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B215">
         <v>2030</v>
@@ -14958,7 +15490,7 @@
     </row>
     <row r="216" spans="1:6">
       <c r="A216" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B216">
         <v>2031</v>
@@ -14978,7 +15510,7 @@
     </row>
     <row r="217" spans="1:6">
       <c r="A217" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B217">
         <v>2032</v>
@@ -14998,7 +15530,7 @@
     </row>
     <row r="218" spans="1:6">
       <c r="A218" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B218">
         <v>2033</v>
@@ -15018,7 +15550,7 @@
     </row>
     <row r="219" spans="1:6">
       <c r="A219" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B219">
         <v>2034</v>
@@ -15038,7 +15570,7 @@
     </row>
     <row r="220" spans="1:6">
       <c r="A220" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B220">
         <v>2035</v>
@@ -15058,7 +15590,7 @@
     </row>
     <row r="221" spans="1:6">
       <c r="A221" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B221">
         <v>2036</v>
@@ -15078,7 +15610,7 @@
     </row>
     <row r="222" spans="1:6">
       <c r="A222" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B222">
         <v>2037</v>
@@ -15098,7 +15630,7 @@
     </row>
     <row r="223" spans="1:6">
       <c r="A223" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B223">
         <v>2038</v>
@@ -15118,7 +15650,7 @@
     </row>
     <row r="224" spans="1:6">
       <c r="A224" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B224">
         <v>2039</v>
@@ -15138,7 +15670,7 @@
     </row>
     <row r="225" spans="1:6">
       <c r="A225" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B225">
         <v>2040</v>
@@ -15158,7 +15690,7 @@
     </row>
     <row r="226" spans="1:6">
       <c r="A226" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B226">
         <v>2041</v>
@@ -15178,7 +15710,7 @@
     </row>
     <row r="227" spans="1:6">
       <c r="A227" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B227">
         <v>2042</v>
@@ -15198,7 +15730,7 @@
     </row>
     <row r="228" spans="1:6">
       <c r="A228" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B228">
         <v>2043</v>
@@ -15218,7 +15750,7 @@
     </row>
     <row r="229" spans="1:6">
       <c r="A229" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B229">
         <v>2044</v>
@@ -15238,7 +15770,7 @@
     </row>
     <row r="230" spans="1:6">
       <c r="A230" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B230">
         <v>2045</v>
@@ -15258,7 +15790,7 @@
     </row>
     <row r="231" spans="1:6">
       <c r="A231" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B231">
         <v>2046</v>
@@ -15278,7 +15810,7 @@
     </row>
     <row r="232" spans="1:6">
       <c r="A232" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B232">
         <v>2047</v>
@@ -15298,7 +15830,7 @@
     </row>
     <row r="233" spans="1:6">
       <c r="A233" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B233">
         <v>2048</v>
@@ -15318,7 +15850,7 @@
     </row>
     <row r="234" spans="1:6">
       <c r="A234" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B234">
         <v>2049</v>
@@ -15338,7 +15870,7 @@
     </row>
     <row r="235" spans="1:6">
       <c r="A235" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B235">
         <v>2050</v>
@@ -15358,7 +15890,7 @@
     </row>
     <row r="236" spans="1:6">
       <c r="A236" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B236">
         <v>2025</v>
@@ -15378,7 +15910,7 @@
     </row>
     <row r="237" spans="1:6">
       <c r="A237" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B237">
         <v>2026</v>
@@ -15398,7 +15930,7 @@
     </row>
     <row r="238" spans="1:6">
       <c r="A238" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B238">
         <v>2027</v>
@@ -15418,7 +15950,7 @@
     </row>
     <row r="239" spans="1:6">
       <c r="A239" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B239">
         <v>2028</v>
@@ -15438,7 +15970,7 @@
     </row>
     <row r="240" spans="1:6">
       <c r="A240" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B240">
         <v>2029</v>
@@ -15458,7 +15990,7 @@
     </row>
     <row r="241" spans="1:6">
       <c r="A241" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B241">
         <v>2030</v>
@@ -15478,7 +16010,7 @@
     </row>
     <row r="242" spans="1:6">
       <c r="A242" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B242">
         <v>2031</v>
@@ -15498,7 +16030,7 @@
     </row>
     <row r="243" spans="1:6">
       <c r="A243" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B243">
         <v>2032</v>
@@ -15518,7 +16050,7 @@
     </row>
     <row r="244" spans="1:6">
       <c r="A244" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B244">
         <v>2033</v>
@@ -15538,7 +16070,7 @@
     </row>
     <row r="245" spans="1:6">
       <c r="A245" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B245">
         <v>2034</v>
@@ -15558,7 +16090,7 @@
     </row>
     <row r="246" spans="1:6">
       <c r="A246" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B246">
         <v>2035</v>
@@ -15578,7 +16110,7 @@
     </row>
     <row r="247" spans="1:6">
       <c r="A247" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B247">
         <v>2036</v>
@@ -15598,7 +16130,7 @@
     </row>
     <row r="248" spans="1:6">
       <c r="A248" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B248">
         <v>2037</v>
@@ -15618,7 +16150,7 @@
     </row>
     <row r="249" spans="1:6">
       <c r="A249" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B249">
         <v>2038</v>
@@ -15638,7 +16170,7 @@
     </row>
     <row r="250" spans="1:6">
       <c r="A250" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B250">
         <v>2039</v>
@@ -15658,7 +16190,7 @@
     </row>
     <row r="251" spans="1:6">
       <c r="A251" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B251">
         <v>2040</v>
@@ -15678,7 +16210,7 @@
     </row>
     <row r="252" spans="1:6">
       <c r="A252" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B252">
         <v>2041</v>
@@ -15698,7 +16230,7 @@
     </row>
     <row r="253" spans="1:6">
       <c r="A253" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B253">
         <v>2042</v>
@@ -15718,7 +16250,7 @@
     </row>
     <row r="254" spans="1:6">
       <c r="A254" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B254">
         <v>2043</v>
@@ -15738,7 +16270,7 @@
     </row>
     <row r="255" spans="1:6">
       <c r="A255" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B255">
         <v>2044</v>
@@ -15758,7 +16290,7 @@
     </row>
     <row r="256" spans="1:6">
       <c r="A256" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B256">
         <v>2045</v>
@@ -15778,7 +16310,7 @@
     </row>
     <row r="257" spans="1:6">
       <c r="A257" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B257">
         <v>2046</v>
@@ -15798,7 +16330,7 @@
     </row>
     <row r="258" spans="1:6">
       <c r="A258" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B258">
         <v>2047</v>
@@ -15818,7 +16350,7 @@
     </row>
     <row r="259" spans="1:6">
       <c r="A259" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B259">
         <v>2048</v>
@@ -15838,7 +16370,7 @@
     </row>
     <row r="260" spans="1:6">
       <c r="A260" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B260">
         <v>2049</v>
@@ -15858,7 +16390,7 @@
     </row>
     <row r="261" spans="1:6">
       <c r="A261" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B261">
         <v>2050</v>
@@ -15874,6 +16406,1046 @@
       </c>
       <c r="F261">
         <v>1058.791559918723</v>
+      </c>
+    </row>
+    <row r="262" spans="1:6">
+      <c r="A262" t="s">
+        <v>37</v>
+      </c>
+      <c r="B262">
+        <v>2025</v>
+      </c>
+      <c r="C262">
+        <v>0</v>
+      </c>
+      <c r="D262">
+        <v>0</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="263" spans="1:6">
+      <c r="A263" t="s">
+        <v>37</v>
+      </c>
+      <c r="B263">
+        <v>2026</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263">
+        <v>0</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="264" spans="1:6">
+      <c r="A264" t="s">
+        <v>37</v>
+      </c>
+      <c r="B264">
+        <v>2027</v>
+      </c>
+      <c r="C264">
+        <v>0</v>
+      </c>
+      <c r="D264">
+        <v>0</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="265" spans="1:6">
+      <c r="A265" t="s">
+        <v>37</v>
+      </c>
+      <c r="B265">
+        <v>2028</v>
+      </c>
+      <c r="C265">
+        <v>0</v>
+      </c>
+      <c r="D265">
+        <v>0</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="266" spans="1:6">
+      <c r="A266" t="s">
+        <v>37</v>
+      </c>
+      <c r="B266">
+        <v>2029</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266">
+        <v>0</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="267" spans="1:6">
+      <c r="A267" t="s">
+        <v>37</v>
+      </c>
+      <c r="B267">
+        <v>2030</v>
+      </c>
+      <c r="C267">
+        <v>0</v>
+      </c>
+      <c r="D267">
+        <v>0</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="268" spans="1:6">
+      <c r="A268" t="s">
+        <v>37</v>
+      </c>
+      <c r="B268">
+        <v>2031</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268">
+        <v>0</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="269" spans="1:6">
+      <c r="A269" t="s">
+        <v>37</v>
+      </c>
+      <c r="B269">
+        <v>2032</v>
+      </c>
+      <c r="C269">
+        <v>0</v>
+      </c>
+      <c r="D269">
+        <v>0</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:6">
+      <c r="A270" t="s">
+        <v>37</v>
+      </c>
+      <c r="B270">
+        <v>2033</v>
+      </c>
+      <c r="C270">
+        <v>0</v>
+      </c>
+      <c r="D270">
+        <v>0</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="271" spans="1:6">
+      <c r="A271" t="s">
+        <v>37</v>
+      </c>
+      <c r="B271">
+        <v>2034</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271">
+        <v>0</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:6">
+      <c r="A272" t="s">
+        <v>37</v>
+      </c>
+      <c r="B272">
+        <v>2035</v>
+      </c>
+      <c r="C272">
+        <v>0</v>
+      </c>
+      <c r="D272">
+        <v>0</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="273" spans="1:6">
+      <c r="A273" t="s">
+        <v>37</v>
+      </c>
+      <c r="B273">
+        <v>2036</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273">
+        <v>0</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="274" spans="1:6">
+      <c r="A274" t="s">
+        <v>37</v>
+      </c>
+      <c r="B274">
+        <v>2037</v>
+      </c>
+      <c r="C274">
+        <v>0</v>
+      </c>
+      <c r="D274">
+        <v>0</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="275" spans="1:6">
+      <c r="A275" t="s">
+        <v>37</v>
+      </c>
+      <c r="B275">
+        <v>2038</v>
+      </c>
+      <c r="C275">
+        <v>0</v>
+      </c>
+      <c r="D275">
+        <v>0</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="276" spans="1:6">
+      <c r="A276" t="s">
+        <v>37</v>
+      </c>
+      <c r="B276">
+        <v>2039</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276">
+        <v>0</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="277" spans="1:6">
+      <c r="A277" t="s">
+        <v>37</v>
+      </c>
+      <c r="B277">
+        <v>2040</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="278" spans="1:6">
+      <c r="A278" t="s">
+        <v>37</v>
+      </c>
+      <c r="B278">
+        <v>2041</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278">
+        <v>0</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="279" spans="1:6">
+      <c r="A279" t="s">
+        <v>37</v>
+      </c>
+      <c r="B279">
+        <v>2042</v>
+      </c>
+      <c r="C279">
+        <v>0</v>
+      </c>
+      <c r="D279">
+        <v>0</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:6">
+      <c r="A280" t="s">
+        <v>37</v>
+      </c>
+      <c r="B280">
+        <v>2043</v>
+      </c>
+      <c r="C280">
+        <v>0</v>
+      </c>
+      <c r="D280">
+        <v>0</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="281" spans="1:6">
+      <c r="A281" t="s">
+        <v>37</v>
+      </c>
+      <c r="B281">
+        <v>2044</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:6">
+      <c r="A282" t="s">
+        <v>37</v>
+      </c>
+      <c r="B282">
+        <v>2045</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="283" spans="1:6">
+      <c r="A283" t="s">
+        <v>37</v>
+      </c>
+      <c r="B283">
+        <v>2046</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283">
+        <v>0</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="284" spans="1:6">
+      <c r="A284" t="s">
+        <v>37</v>
+      </c>
+      <c r="B284">
+        <v>2047</v>
+      </c>
+      <c r="C284">
+        <v>0</v>
+      </c>
+      <c r="D284">
+        <v>0</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="285" spans="1:6">
+      <c r="A285" t="s">
+        <v>37</v>
+      </c>
+      <c r="B285">
+        <v>2048</v>
+      </c>
+      <c r="C285">
+        <v>0</v>
+      </c>
+      <c r="D285">
+        <v>0</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="286" spans="1:6">
+      <c r="A286" t="s">
+        <v>37</v>
+      </c>
+      <c r="B286">
+        <v>2049</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286">
+        <v>0</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="287" spans="1:6">
+      <c r="A287" t="s">
+        <v>37</v>
+      </c>
+      <c r="B287">
+        <v>2050</v>
+      </c>
+      <c r="C287">
+        <v>0</v>
+      </c>
+      <c r="D287">
+        <v>0</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="288" spans="1:6">
+      <c r="A288" t="s">
+        <v>38</v>
+      </c>
+      <c r="B288">
+        <v>2025</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:6">
+      <c r="A289" t="s">
+        <v>38</v>
+      </c>
+      <c r="B289">
+        <v>2026</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="290" spans="1:6">
+      <c r="A290" t="s">
+        <v>38</v>
+      </c>
+      <c r="B290">
+        <v>2027</v>
+      </c>
+      <c r="C290">
+        <v>0</v>
+      </c>
+      <c r="D290">
+        <v>0</v>
+      </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
+      <c r="F290">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="291" spans="1:6">
+      <c r="A291" t="s">
+        <v>38</v>
+      </c>
+      <c r="B291">
+        <v>2028</v>
+      </c>
+      <c r="C291">
+        <v>0</v>
+      </c>
+      <c r="D291">
+        <v>0</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="292" spans="1:6">
+      <c r="A292" t="s">
+        <v>38</v>
+      </c>
+      <c r="B292">
+        <v>2029</v>
+      </c>
+      <c r="C292">
+        <v>0</v>
+      </c>
+      <c r="D292">
+        <v>0</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="293" spans="1:6">
+      <c r="A293" t="s">
+        <v>38</v>
+      </c>
+      <c r="B293">
+        <v>2030</v>
+      </c>
+      <c r="C293">
+        <v>0</v>
+      </c>
+      <c r="D293">
+        <v>0</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="294" spans="1:6">
+      <c r="A294" t="s">
+        <v>38</v>
+      </c>
+      <c r="B294">
+        <v>2031</v>
+      </c>
+      <c r="C294">
+        <v>0</v>
+      </c>
+      <c r="D294">
+        <v>0</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="295" spans="1:6">
+      <c r="A295" t="s">
+        <v>38</v>
+      </c>
+      <c r="B295">
+        <v>2032</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="296" spans="1:6">
+      <c r="A296" t="s">
+        <v>38</v>
+      </c>
+      <c r="B296">
+        <v>2033</v>
+      </c>
+      <c r="C296">
+        <v>0</v>
+      </c>
+      <c r="D296">
+        <v>0</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:6">
+      <c r="A297" t="s">
+        <v>38</v>
+      </c>
+      <c r="B297">
+        <v>2034</v>
+      </c>
+      <c r="C297">
+        <v>0</v>
+      </c>
+      <c r="D297">
+        <v>0</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="298" spans="1:6">
+      <c r="A298" t="s">
+        <v>38</v>
+      </c>
+      <c r="B298">
+        <v>2035</v>
+      </c>
+      <c r="C298">
+        <v>0</v>
+      </c>
+      <c r="D298">
+        <v>0</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="299" spans="1:6">
+      <c r="A299" t="s">
+        <v>38</v>
+      </c>
+      <c r="B299">
+        <v>2036</v>
+      </c>
+      <c r="C299">
+        <v>0</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="300" spans="1:6">
+      <c r="A300" t="s">
+        <v>38</v>
+      </c>
+      <c r="B300">
+        <v>2037</v>
+      </c>
+      <c r="C300">
+        <v>0</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="301" spans="1:6">
+      <c r="A301" t="s">
+        <v>38</v>
+      </c>
+      <c r="B301">
+        <v>2038</v>
+      </c>
+      <c r="C301">
+        <v>0</v>
+      </c>
+      <c r="D301">
+        <v>0</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="302" spans="1:6">
+      <c r="A302" t="s">
+        <v>38</v>
+      </c>
+      <c r="B302">
+        <v>2039</v>
+      </c>
+      <c r="C302">
+        <v>0</v>
+      </c>
+      <c r="D302">
+        <v>0</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="303" spans="1:6">
+      <c r="A303" t="s">
+        <v>38</v>
+      </c>
+      <c r="B303">
+        <v>2040</v>
+      </c>
+      <c r="C303">
+        <v>0</v>
+      </c>
+      <c r="D303">
+        <v>0</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="304" spans="1:6">
+      <c r="A304" t="s">
+        <v>38</v>
+      </c>
+      <c r="B304">
+        <v>2041</v>
+      </c>
+      <c r="C304">
+        <v>0</v>
+      </c>
+      <c r="D304">
+        <v>0</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="305" spans="1:6">
+      <c r="A305" t="s">
+        <v>38</v>
+      </c>
+      <c r="B305">
+        <v>2042</v>
+      </c>
+      <c r="C305">
+        <v>0</v>
+      </c>
+      <c r="D305">
+        <v>0</v>
+      </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="306" spans="1:6">
+      <c r="A306" t="s">
+        <v>38</v>
+      </c>
+      <c r="B306">
+        <v>2043</v>
+      </c>
+      <c r="C306">
+        <v>0</v>
+      </c>
+      <c r="D306">
+        <v>0</v>
+      </c>
+      <c r="E306">
+        <v>0</v>
+      </c>
+      <c r="F306">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="307" spans="1:6">
+      <c r="A307" t="s">
+        <v>38</v>
+      </c>
+      <c r="B307">
+        <v>2044</v>
+      </c>
+      <c r="C307">
+        <v>0</v>
+      </c>
+      <c r="D307">
+        <v>0</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="308" spans="1:6">
+      <c r="A308" t="s">
+        <v>38</v>
+      </c>
+      <c r="B308">
+        <v>2045</v>
+      </c>
+      <c r="C308">
+        <v>0</v>
+      </c>
+      <c r="D308">
+        <v>0</v>
+      </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
+      <c r="F308">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="309" spans="1:6">
+      <c r="A309" t="s">
+        <v>38</v>
+      </c>
+      <c r="B309">
+        <v>2046</v>
+      </c>
+      <c r="C309">
+        <v>0</v>
+      </c>
+      <c r="D309">
+        <v>0</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+      <c r="F309">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="310" spans="1:6">
+      <c r="A310" t="s">
+        <v>38</v>
+      </c>
+      <c r="B310">
+        <v>2047</v>
+      </c>
+      <c r="C310">
+        <v>0</v>
+      </c>
+      <c r="D310">
+        <v>0</v>
+      </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
+      <c r="F310">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="311" spans="1:6">
+      <c r="A311" t="s">
+        <v>38</v>
+      </c>
+      <c r="B311">
+        <v>2048</v>
+      </c>
+      <c r="C311">
+        <v>0</v>
+      </c>
+      <c r="D311">
+        <v>0</v>
+      </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
+      <c r="F311">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="312" spans="1:6">
+      <c r="A312" t="s">
+        <v>38</v>
+      </c>
+      <c r="B312">
+        <v>2049</v>
+      </c>
+      <c r="C312">
+        <v>0</v>
+      </c>
+      <c r="D312">
+        <v>0</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="313" spans="1:6">
+      <c r="A313" t="s">
+        <v>38</v>
+      </c>
+      <c r="B313">
+        <v>2050</v>
+      </c>
+      <c r="C313">
+        <v>0</v>
+      </c>
+      <c r="D313">
+        <v>0</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+      <c r="F313">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -15883,20 +17455,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B74"/>
+  <dimension ref="A1:B75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B2">
         <v>0.1</v>
@@ -15904,7 +17476,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B3">
         <v>1</v>
@@ -15912,7 +17484,7 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B4">
         <v>0.5</v>
@@ -15920,7 +17492,7 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B5">
         <v>0.5</v>
@@ -15928,31 +17500,31 @@
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B7" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B8" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -15960,7 +17532,7 @@
     </row>
     <row r="10" spans="1:2">
       <c r="A10" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -15968,7 +17540,7 @@
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B11">
         <v>0.5</v>
@@ -15976,7 +17548,7 @@
     </row>
     <row r="12" spans="1:2">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B12">
         <v>0.5</v>
@@ -15984,7 +17556,7 @@
     </row>
     <row r="13" spans="1:2">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B13">
         <v>0.5</v>
@@ -15992,7 +17564,7 @@
     </row>
     <row r="14" spans="1:2">
       <c r="A14" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B14">
         <v>0.5</v>
@@ -16000,7 +17572,7 @@
     </row>
     <row r="15" spans="1:2">
       <c r="A15" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -16008,7 +17580,7 @@
     </row>
     <row r="16" spans="1:2">
       <c r="A16" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B16">
         <v>0.5</v>
@@ -16016,7 +17588,7 @@
     </row>
     <row r="17" spans="1:2">
       <c r="A17" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B17">
         <v>0.5</v>
@@ -16024,7 +17596,7 @@
     </row>
     <row r="18" spans="1:2">
       <c r="A18" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -16032,7 +17604,7 @@
     </row>
     <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="B19">
         <v>0.5</v>
@@ -16040,7 +17612,7 @@
     </row>
     <row r="20" spans="1:2">
       <c r="A20" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B20">
         <v>0.5</v>
@@ -16048,7 +17620,7 @@
     </row>
     <row r="21" spans="1:2">
       <c r="A21" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -16056,7 +17628,7 @@
     </row>
     <row r="22" spans="1:2">
       <c r="A22" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="B22">
         <v>1</v>
@@ -16064,7 +17636,7 @@
     </row>
     <row r="23" spans="1:2">
       <c r="A23" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -16072,7 +17644,7 @@
     </row>
     <row r="24" spans="1:2">
       <c r="A24" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -16080,7 +17652,7 @@
     </row>
     <row r="25" spans="1:2">
       <c r="A25" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -16088,7 +17660,7 @@
     </row>
     <row r="26" spans="1:2">
       <c r="A26" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -16096,7 +17668,7 @@
     </row>
     <row r="27" spans="1:2">
       <c r="A27" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -16104,7 +17676,7 @@
     </row>
     <row r="28" spans="1:2">
       <c r="A28" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -16112,7 +17684,7 @@
     </row>
     <row r="29" spans="1:2">
       <c r="A29" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B29">
         <v>0.5</v>
@@ -16120,7 +17692,7 @@
     </row>
     <row r="30" spans="1:2">
       <c r="A30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -16128,7 +17700,7 @@
     </row>
     <row r="31" spans="1:2">
       <c r="A31" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -16136,7 +17708,7 @@
     </row>
     <row r="32" spans="1:2">
       <c r="A32" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B32">
         <v>0.5</v>
@@ -16144,7 +17716,7 @@
     </row>
     <row r="33" spans="1:2">
       <c r="A33" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -16152,7 +17724,7 @@
     </row>
     <row r="34" spans="1:2">
       <c r="A34" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -16160,7 +17732,7 @@
     </row>
     <row r="35" spans="1:2">
       <c r="A35" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B35">
         <v>0.5</v>
@@ -16168,7 +17740,7 @@
     </row>
     <row r="36" spans="1:2">
       <c r="A36" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -16176,7 +17748,7 @@
     </row>
     <row r="37" spans="1:2">
       <c r="A37" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -16184,7 +17756,7 @@
     </row>
     <row r="38" spans="1:2">
       <c r="A38" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="B38">
         <v>1</v>
@@ -16192,7 +17764,7 @@
     </row>
     <row r="39" spans="1:2">
       <c r="A39" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -16200,7 +17772,7 @@
     </row>
     <row r="40" spans="1:2">
       <c r="A40" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B40">
         <v>1</v>
@@ -16208,7 +17780,7 @@
     </row>
     <row r="41" spans="1:2">
       <c r="A41" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -16216,7 +17788,7 @@
     </row>
     <row r="42" spans="1:2">
       <c r="A42" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="B42">
         <v>0</v>
@@ -16224,7 +17796,7 @@
     </row>
     <row r="43" spans="1:2">
       <c r="A43" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B43">
         <v>1</v>
@@ -16232,7 +17804,7 @@
     </row>
     <row r="44" spans="1:2">
       <c r="A44" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B44">
         <v>0.5</v>
@@ -16240,7 +17812,7 @@
     </row>
     <row r="45" spans="1:2">
       <c r="A45" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="B45">
         <v>0</v>
@@ -16248,7 +17820,7 @@
     </row>
     <row r="46" spans="1:2">
       <c r="A46" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B46">
         <v>1</v>
@@ -16256,7 +17828,7 @@
     </row>
     <row r="47" spans="1:2">
       <c r="A47" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="B47">
         <v>0.5</v>
@@ -16264,7 +17836,7 @@
     </row>
     <row r="48" spans="1:2">
       <c r="A48" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -16272,7 +17844,7 @@
     </row>
     <row r="49" spans="1:2">
       <c r="A49" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B49">
         <v>1</v>
@@ -16280,7 +17852,7 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="B50">
         <v>1</v>
@@ -16288,7 +17860,7 @@
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B51">
         <v>0</v>
@@ -16296,7 +17868,7 @@
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B52">
         <v>1</v>
@@ -16304,7 +17876,7 @@
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -16312,7 +17884,7 @@
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B54">
         <v>0</v>
@@ -16320,7 +17892,7 @@
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B55">
         <v>1</v>
@@ -16328,7 +17900,7 @@
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="B56">
         <v>0</v>
@@ -16336,7 +17908,7 @@
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="B57">
         <v>0</v>
@@ -16344,7 +17916,7 @@
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="B58">
         <v>1</v>
@@ -16352,7 +17924,7 @@
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="B59">
         <v>0.5</v>
@@ -16360,7 +17932,7 @@
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="B60">
         <v>0</v>
@@ -16368,7 +17940,7 @@
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -16376,7 +17948,7 @@
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="B62">
         <v>0.5</v>
@@ -16384,7 +17956,7 @@
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="B63">
         <v>0</v>
@@ -16392,7 +17964,7 @@
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="B64">
         <v>1</v>
@@ -16400,7 +17972,7 @@
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="B65">
         <v>1</v>
@@ -16408,7 +17980,7 @@
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="B66">
         <v>0</v>
@@ -16416,7 +17988,7 @@
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="B67">
         <v>1</v>
@@ -16424,7 +17996,7 @@
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B68">
         <v>0</v>
@@ -16432,7 +18004,7 @@
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="B69">
         <v>0</v>
@@ -16440,7 +18012,7 @@
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="B70">
         <v>1</v>
@@ -16448,7 +18020,7 @@
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B71">
         <v>1</v>
@@ -16456,7 +18028,7 @@
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="B72">
         <v>0</v>
@@ -16464,7 +18036,7 @@
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="B73">
         <v>1</v>
@@ -16472,9 +18044,17 @@
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="B74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>114</v>
+      </c>
+      <c r="B75">
         <v>0</v>
       </c>
     </row>
@@ -16490,50 +18070,50 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B2">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="B3">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="B4">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="B5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>

--- a/biodym_mfa_tool/data/02_output/results_scientific.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific.xlsx
@@ -6928,16 +6928,16 @@
         <v>2025</v>
       </c>
       <c r="C314">
-        <v>76152.5516601002</v>
+        <v>115956.3752316096</v>
       </c>
       <c r="D314">
-        <v>10661.35723241403</v>
+        <v>0</v>
       </c>
       <c r="E314">
-        <v>65491.19442768617</v>
+        <v>115956.3752316096</v>
       </c>
       <c r="F314">
-        <v>31435.77332528936</v>
+        <v>115956.3752316096</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -6948,16 +6948,16 @@
         <v>2026</v>
       </c>
       <c r="C315">
-        <v>91437.93988816446</v>
+        <v>131436.9846483817</v>
       </c>
       <c r="D315">
-        <v>12801.31158434302</v>
+        <v>0</v>
       </c>
       <c r="E315">
-        <v>78636.62830382143</v>
+        <v>131436.9846483817</v>
       </c>
       <c r="F315">
-        <v>37745.58158583429</v>
+        <v>131436.9846483817</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -6968,16 +6968,16 @@
         <v>2027</v>
       </c>
       <c r="C316">
-        <v>75933.62793176042</v>
+        <v>99188.86568059392</v>
       </c>
       <c r="D316">
-        <v>10630.70791044646</v>
+        <v>0</v>
       </c>
       <c r="E316">
-        <v>65302.92002131396</v>
+        <v>99188.86568059392</v>
       </c>
       <c r="F316">
-        <v>31345.40161023071</v>
+        <v>99188.86568059392</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -6988,16 +6988,16 @@
         <v>2028</v>
       </c>
       <c r="C317">
-        <v>81523.84591414238</v>
+        <v>101444.6951950469</v>
       </c>
       <c r="D317">
-        <v>11413.33842797994</v>
+        <v>0</v>
       </c>
       <c r="E317">
-        <v>70110.50748616246</v>
+        <v>101444.6951950469</v>
       </c>
       <c r="F317">
-        <v>33653.04359335798</v>
+        <v>101444.6951950469</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -7008,16 +7008,16 @@
         <v>2029</v>
       </c>
       <c r="C318">
-        <v>105460.5057283388</v>
+        <v>131641.1610056631</v>
       </c>
       <c r="D318">
-        <v>14764.47080196743</v>
+        <v>0</v>
       </c>
       <c r="E318">
-        <v>90696.03492637136</v>
+        <v>131641.1610056631</v>
       </c>
       <c r="F318">
-        <v>43534.09676465825</v>
+        <v>131641.1610056631</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -7028,16 +7028,16 @@
         <v>2030</v>
       </c>
       <c r="C319">
-        <v>103210.3666870139</v>
+        <v>120089.9474229112</v>
       </c>
       <c r="D319">
-        <v>14449.45133618195</v>
+        <v>0</v>
       </c>
       <c r="E319">
-        <v>88760.91535083197</v>
+        <v>120089.9474229112</v>
       </c>
       <c r="F319">
-        <v>42605.23936839935</v>
+        <v>120089.9474229112</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -7048,16 +7048,16 @@
         <v>2031</v>
       </c>
       <c r="C320">
-        <v>122312.7544009445</v>
+        <v>142031.4743389855</v>
       </c>
       <c r="D320">
-        <v>17123.78561613223</v>
+        <v>0</v>
       </c>
       <c r="E320">
-        <v>105188.9687848122</v>
+        <v>142031.4743389855</v>
       </c>
       <c r="F320">
-        <v>50490.70501670987</v>
+        <v>142031.4743389855</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -7068,16 +7068,16 @@
         <v>2032</v>
       </c>
       <c r="C321">
-        <v>122097.291674162</v>
+        <v>133261.7869665299</v>
       </c>
       <c r="D321">
-        <v>17093.62083438268</v>
+        <v>0</v>
       </c>
       <c r="E321">
-        <v>105003.6708397793</v>
+        <v>133261.7869665299</v>
       </c>
       <c r="F321">
-        <v>50401.76200309406</v>
+        <v>133261.7869665299</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -7088,16 +7088,16 @@
         <v>2033</v>
       </c>
       <c r="C322">
-        <v>135716.0640804863</v>
+        <v>146357.798125677</v>
       </c>
       <c r="D322">
-        <v>19000.24897126808</v>
+        <v>0</v>
       </c>
       <c r="E322">
-        <v>116715.8151092182</v>
+        <v>146357.798125677</v>
       </c>
       <c r="F322">
-        <v>56023.59125242474</v>
+        <v>146357.798125677</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -7108,16 +7108,16 @@
         <v>2034</v>
       </c>
       <c r="C323">
-        <v>128888.4222308774</v>
+        <v>127631.1078735566</v>
       </c>
       <c r="D323">
-        <v>18044.37911232284</v>
+        <v>0</v>
       </c>
       <c r="E323">
-        <v>110844.0431185546</v>
+        <v>127631.1078735566</v>
       </c>
       <c r="F323">
-        <v>53205.1406969062</v>
+        <v>127631.1078735566</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -7128,16 +7128,16 @@
         <v>2035</v>
       </c>
       <c r="C324">
-        <v>128438.7141891218</v>
+        <v>120083.0124878945</v>
       </c>
       <c r="D324">
-        <v>17981.41998647705</v>
+        <v>0</v>
       </c>
       <c r="E324">
-        <v>110457.2942026447</v>
+        <v>120083.0124878945</v>
       </c>
       <c r="F324">
-        <v>53019.50121726948</v>
+        <v>120083.0124878945</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -7148,16 +7148,16 @@
         <v>2036</v>
       </c>
       <c r="C325">
-        <v>131605.0161911844</v>
+        <v>118719.9054598083</v>
       </c>
       <c r="D325">
-        <v>18424.70226676582</v>
+        <v>0</v>
       </c>
       <c r="E325">
-        <v>113180.3139244186</v>
+        <v>118719.9054598083</v>
       </c>
       <c r="F325">
-        <v>54326.55068372092</v>
+        <v>118719.9054598083</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -7168,16 +7168,16 @@
         <v>2037</v>
       </c>
       <c r="C326">
-        <v>149611.7794189357</v>
+        <v>140200.3849545098</v>
       </c>
       <c r="D326">
-        <v>20945.64911865101</v>
+        <v>0</v>
       </c>
       <c r="E326">
-        <v>128666.1303002847</v>
+        <v>140200.3849545098</v>
       </c>
       <c r="F326">
-        <v>61759.74254413667</v>
+        <v>140200.3849545098</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -7188,16 +7188,16 @@
         <v>2038</v>
       </c>
       <c r="C327">
-        <v>150401.180819298</v>
+        <v>134168.8424897742</v>
       </c>
       <c r="D327">
-        <v>21056.16531470171</v>
+        <v>0</v>
       </c>
       <c r="E327">
-        <v>129345.0155045962</v>
+        <v>134168.8424897742</v>
       </c>
       <c r="F327">
-        <v>62085.60744220619</v>
+        <v>134168.8424897742</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -7208,16 +7208,16 @@
         <v>2039</v>
       </c>
       <c r="C328">
-        <v>142980.4655017415</v>
+        <v>116222.1358897134</v>
       </c>
       <c r="D328">
-        <v>20017.26517024382</v>
+        <v>0</v>
       </c>
       <c r="E328">
-        <v>122963.2003314977</v>
+        <v>116222.1358897134</v>
       </c>
       <c r="F328">
-        <v>59022.33615911889</v>
+        <v>116222.1358897134</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -7228,16 +7228,16 @@
         <v>2040</v>
       </c>
       <c r="C329">
-        <v>164748.4326988467</v>
+        <v>144093.1128934026</v>
       </c>
       <c r="D329">
-        <v>23064.78057783854</v>
+        <v>0</v>
       </c>
       <c r="E329">
-        <v>141683.6521210082</v>
+        <v>144093.1128934026</v>
       </c>
       <c r="F329">
-        <v>68008.15301808392</v>
+        <v>144093.1128934026</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -7248,16 +7248,16 @@
         <v>2041</v>
       </c>
       <c r="C330">
-        <v>151884.422289513</v>
+        <v>117488.9539341407</v>
       </c>
       <c r="D330">
-        <v>21263.81912053183</v>
+        <v>0</v>
       </c>
       <c r="E330">
-        <v>130620.6031689812</v>
+        <v>117488.9539341407</v>
       </c>
       <c r="F330">
-        <v>62697.88952111098</v>
+        <v>117488.9539341407</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -7268,16 +7268,16 @@
         <v>2042</v>
       </c>
       <c r="C331">
-        <v>162357.661853877</v>
+        <v>128383.7406617088</v>
       </c>
       <c r="D331">
-        <v>22730.07265954279</v>
+        <v>0</v>
       </c>
       <c r="E331">
-        <v>139627.5891943343</v>
+        <v>128383.7406617088</v>
       </c>
       <c r="F331">
-        <v>67021.24281328042</v>
+        <v>128383.7406617088</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -7288,16 +7288,16 @@
         <v>2043</v>
       </c>
       <c r="C332">
-        <v>163013.8311712152</v>
+        <v>123724.2211043001</v>
       </c>
       <c r="D332">
-        <v>22821.93636397013</v>
+        <v>0</v>
       </c>
       <c r="E332">
-        <v>140191.8948072451</v>
+        <v>123724.2211043001</v>
       </c>
       <c r="F332">
-        <v>67292.10950747764</v>
+        <v>123724.2211043001</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -7308,16 +7308,16 @@
         <v>2044</v>
       </c>
       <c r="C333">
-        <v>157322.6877295265</v>
+        <v>109854.4062660498</v>
       </c>
       <c r="D333">
-        <v>22025.17628213373</v>
+        <v>0</v>
       </c>
       <c r="E333">
-        <v>135297.5114473928</v>
+        <v>109854.4062660498</v>
       </c>
       <c r="F333">
-        <v>64942.80549474856</v>
+        <v>109854.4062660498</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -7328,16 +7328,16 @@
         <v>2045</v>
       </c>
       <c r="C334">
-        <v>161821.8048530462</v>
+        <v>112563.5376910088</v>
       </c>
       <c r="D334">
-        <v>22655.05267942647</v>
+        <v>0</v>
       </c>
       <c r="E334">
-        <v>139166.7521736197</v>
+        <v>112563.5376910088</v>
       </c>
       <c r="F334">
-        <v>66800.04104333746</v>
+        <v>112563.5376910088</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -7348,16 +7348,16 @@
         <v>2046</v>
       </c>
       <c r="C335">
-        <v>171406.8913709315</v>
+        <v>122938.4410417697</v>
       </c>
       <c r="D335">
-        <v>23996.96479193042</v>
+        <v>0</v>
       </c>
       <c r="E335">
-        <v>147409.9265790011</v>
+        <v>122938.4410417697</v>
       </c>
       <c r="F335">
-        <v>70756.76475792054</v>
+        <v>122938.4410417697</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -7368,16 +7368,16 @@
         <v>2047</v>
       </c>
       <c r="C336">
-        <v>175665.8878204365</v>
+        <v>124611.5204488498</v>
       </c>
       <c r="D336">
-        <v>24593.22429486111</v>
+        <v>0</v>
       </c>
       <c r="E336">
-        <v>151072.6635255754</v>
+        <v>124611.5204488498</v>
       </c>
       <c r="F336">
-        <v>72514.87849227618</v>
+        <v>124611.5204488498</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -7388,16 +7388,16 @@
         <v>2048</v>
       </c>
       <c r="C337">
-        <v>163630.4736631432</v>
+        <v>101481.1810425606</v>
       </c>
       <c r="D337">
-        <v>22908.26631284006</v>
+        <v>0</v>
       </c>
       <c r="E337">
-        <v>140722.2073503032</v>
+        <v>101481.1810425606</v>
       </c>
       <c r="F337">
-        <v>67546.65952814552</v>
+        <v>101481.1810425606</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -7408,16 +7408,16 @@
         <v>2049</v>
       </c>
       <c r="C338">
-        <v>177335.750879446</v>
+        <v>119220.669781142</v>
       </c>
       <c r="D338">
-        <v>24827.00512312245</v>
+        <v>0</v>
       </c>
       <c r="E338">
-        <v>152508.7457563236</v>
+        <v>119220.669781142</v>
       </c>
       <c r="F338">
-        <v>73204.1979630353</v>
+        <v>119220.669781142</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -7428,16 +7428,16 @@
         <v>2050</v>
       </c>
       <c r="C339">
-        <v>178412.2605856631</v>
+        <v>116616.3592362279</v>
       </c>
       <c r="D339">
-        <v>24977.71648199284</v>
+        <v>0</v>
       </c>
       <c r="E339">
-        <v>153434.5441036703</v>
+        <v>116616.3592362279</v>
       </c>
       <c r="F339">
-        <v>73648.58116976175</v>
+        <v>116616.3592362279</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -7448,13 +7448,13 @@
         <v>2025</v>
       </c>
       <c r="C340">
-        <v>0</v>
+        <v>164945.6965503904</v>
       </c>
       <c r="D340">
-        <v>0</v>
+        <v>39326.28995296545</v>
       </c>
       <c r="E340">
-        <v>0</v>
+        <v>125619.4065974249</v>
       </c>
       <c r="F340">
         <v>0</v>
@@ -7468,13 +7468,13 @@
         <v>2026</v>
       </c>
       <c r="C341">
-        <v>0</v>
+        <v>186966.5634339383</v>
       </c>
       <c r="D341">
-        <v>0</v>
+        <v>44576.4966221252</v>
       </c>
       <c r="E341">
-        <v>0</v>
+        <v>142390.0668118131</v>
       </c>
       <c r="F341">
         <v>0</v>
@@ -7488,13 +7488,13 @@
         <v>2027</v>
       </c>
       <c r="C342">
-        <v>0</v>
+        <v>141094.2391658061</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>33639.63459593763</v>
       </c>
       <c r="E342">
-        <v>0</v>
+        <v>107454.6045698684</v>
       </c>
       <c r="F342">
         <v>0</v>
@@ -7508,13 +7508,13 @@
         <v>2028</v>
       </c>
       <c r="C343">
-        <v>0</v>
+        <v>144303.1129324891</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>34404.69305341908</v>
       </c>
       <c r="E343">
-        <v>0</v>
+        <v>109898.4198790701</v>
       </c>
       <c r="F343">
         <v>0</v>
@@ -7528,13 +7528,13 @@
         <v>2029</v>
       </c>
       <c r="C344">
-        <v>0</v>
+        <v>187257.0003452649</v>
       </c>
       <c r="D344">
-        <v>0</v>
+        <v>44645.74247956038</v>
       </c>
       <c r="E344">
-        <v>0</v>
+        <v>142611.2578657045</v>
       </c>
       <c r="F344">
         <v>0</v>
@@ -7548,13 +7548,13 @@
         <v>2030</v>
       </c>
       <c r="C345">
-        <v>0</v>
+        <v>170825.6228845288</v>
       </c>
       <c r="D345">
-        <v>0</v>
+        <v>40728.17974308654</v>
       </c>
       <c r="E345">
-        <v>0</v>
+        <v>130097.4431414422</v>
       </c>
       <c r="F345">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>2031</v>
       </c>
       <c r="C346">
-        <v>0</v>
+        <v>202037.0196992545</v>
       </c>
       <c r="D346">
-        <v>0</v>
+        <v>48169.58904713584</v>
       </c>
       <c r="E346">
-        <v>0</v>
+        <v>153867.4306521187</v>
       </c>
       <c r="F346">
         <v>0</v>
@@ -7588,13 +7588,13 @@
         <v>2032</v>
       </c>
       <c r="C347">
-        <v>0</v>
+        <v>189562.3093671181</v>
       </c>
       <c r="D347">
-        <v>0</v>
+        <v>45195.37337579228</v>
       </c>
       <c r="E347">
-        <v>0</v>
+        <v>144366.9359913258</v>
       </c>
       <c r="F347">
         <v>0</v>
@@ -7608,13 +7608,13 @@
         <v>2033</v>
       </c>
       <c r="C348">
-        <v>0</v>
+        <v>208191.131442339</v>
       </c>
       <c r="D348">
-        <v>0</v>
+        <v>49636.85001770352</v>
       </c>
       <c r="E348">
-        <v>0</v>
+        <v>158554.2814246354</v>
       </c>
       <c r="F348">
         <v>0</v>
@@ -7628,13 +7628,13 @@
         <v>2034</v>
       </c>
       <c r="C349">
-        <v>0</v>
+        <v>181552.7774790514</v>
       </c>
       <c r="D349">
-        <v>0</v>
+        <v>43285.74384313329</v>
       </c>
       <c r="E349">
-        <v>0</v>
+        <v>138267.0336359181</v>
       </c>
       <c r="F349">
         <v>0</v>
@@ -7648,13 +7648,13 @@
         <v>2035</v>
       </c>
       <c r="C350">
-        <v>0</v>
+        <v>170815.7580738655</v>
       </c>
       <c r="D350">
-        <v>0</v>
+        <v>40725.82777869711</v>
       </c>
       <c r="E350">
-        <v>0</v>
+        <v>130089.9302951683</v>
       </c>
       <c r="F350">
         <v>0</v>
@@ -7668,13 +7668,13 @@
         <v>2036</v>
       </c>
       <c r="C351">
-        <v>0</v>
+        <v>168876.7647432157</v>
       </c>
       <c r="D351">
-        <v>0</v>
+        <v>40263.53372960863</v>
       </c>
       <c r="E351">
-        <v>0</v>
+        <v>128613.231013607</v>
       </c>
       <c r="F351">
         <v>0</v>
@@ -7688,13 +7688,13 @@
         <v>2037</v>
       </c>
       <c r="C352">
-        <v>0</v>
+        <v>199432.3305360662</v>
       </c>
       <c r="D352">
-        <v>0</v>
+        <v>47548.58005198695</v>
       </c>
       <c r="E352">
-        <v>0</v>
+        <v>151883.7504840792</v>
       </c>
       <c r="F352">
         <v>0</v>
@@ -7708,13 +7708,13 @@
         <v>2038</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>190852.5782703377</v>
       </c>
       <c r="D353">
-        <v>0</v>
+        <v>45502.99879474226</v>
       </c>
       <c r="E353">
-        <v>0</v>
+        <v>145349.5794755955</v>
       </c>
       <c r="F353">
         <v>0</v>
@@ -7728,13 +7728,13 @@
         <v>2039</v>
       </c>
       <c r="C354">
-        <v>0</v>
+        <v>165323.7359361426</v>
       </c>
       <c r="D354">
-        <v>0</v>
+        <v>39416.42195888409</v>
       </c>
       <c r="E354">
-        <v>0</v>
+        <v>125907.3139772585</v>
       </c>
       <c r="F354">
         <v>0</v>
@@ -7748,13 +7748,13 @@
         <v>2040</v>
       </c>
       <c r="C355">
-        <v>0</v>
+        <v>204969.6605886774</v>
       </c>
       <c r="D355">
-        <v>0</v>
+        <v>48868.78816755746</v>
       </c>
       <c r="E355">
-        <v>0</v>
+        <v>156100.8724211199</v>
       </c>
       <c r="F355">
         <v>0</v>
@@ -7768,13 +7768,13 @@
         <v>2041</v>
       </c>
       <c r="C356">
-        <v>0</v>
+        <v>167125.7600536033</v>
       </c>
       <c r="D356">
-        <v>0</v>
+        <v>39846.059860494</v>
       </c>
       <c r="E356">
-        <v>0</v>
+        <v>127279.7001931093</v>
       </c>
       <c r="F356">
         <v>0</v>
@@ -7788,13 +7788,13 @@
         <v>2042</v>
       </c>
       <c r="C357">
-        <v>0</v>
+        <v>182623.3830342912</v>
       </c>
       <c r="D357">
-        <v>0</v>
+        <v>43540.99721058172</v>
       </c>
       <c r="E357">
-        <v>0</v>
+        <v>139082.3858237095</v>
       </c>
       <c r="F357">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>2043</v>
       </c>
       <c r="C358">
-        <v>0</v>
+        <v>175995.3067646439</v>
       </c>
       <c r="D358">
-        <v>0</v>
+        <v>41960.73379867217</v>
       </c>
       <c r="E358">
-        <v>0</v>
+        <v>134034.5729659717</v>
       </c>
       <c r="F358">
         <v>0</v>
@@ -7828,13 +7828,13 @@
         <v>2044</v>
       </c>
       <c r="C359">
-        <v>0</v>
+        <v>156265.7639520942</v>
       </c>
       <c r="D359">
-        <v>0</v>
+        <v>37256.8237391045</v>
       </c>
       <c r="E359">
-        <v>0</v>
+        <v>119008.9402129896</v>
       </c>
       <c r="F359">
         <v>0</v>
@@ -7848,13 +7848,13 @@
         <v>2045</v>
       </c>
       <c r="C360">
-        <v>0</v>
+        <v>160119.4509015513</v>
       </c>
       <c r="D360">
-        <v>0</v>
+        <v>38175.61830926784</v>
       </c>
       <c r="E360">
-        <v>0</v>
+        <v>121943.8325922834</v>
       </c>
       <c r="F360">
         <v>0</v>
@@ -7868,13 +7868,13 @@
         <v>2046</v>
       </c>
       <c r="C361">
-        <v>0</v>
+        <v>174877.5498539903</v>
       </c>
       <c r="D361">
-        <v>0</v>
+        <v>41694.23862308044</v>
       </c>
       <c r="E361">
-        <v>0</v>
+        <v>133183.3112309098</v>
       </c>
       <c r="F361">
         <v>0</v>
@@ -7888,13 +7888,13 @@
         <v>2047</v>
       </c>
       <c r="C362">
-        <v>0</v>
+        <v>177257.4728865422</v>
       </c>
       <c r="D362">
-        <v>0</v>
+        <v>42261.65896323635</v>
       </c>
       <c r="E362">
-        <v>0</v>
+        <v>134995.8139233058</v>
       </c>
       <c r="F362">
         <v>0</v>
@@ -7908,13 +7908,13 @@
         <v>2048</v>
       </c>
       <c r="C363">
-        <v>0</v>
+        <v>144355.0133434874</v>
       </c>
       <c r="D363">
-        <v>0</v>
+        <v>34417.06712958039</v>
       </c>
       <c r="E363">
-        <v>0</v>
+        <v>109937.946213907</v>
       </c>
       <c r="F363">
         <v>0</v>
@@ -7928,13 +7928,13 @@
         <v>2049</v>
       </c>
       <c r="C364">
-        <v>0</v>
+        <v>169589.092285578</v>
       </c>
       <c r="D364">
-        <v>0</v>
+        <v>40433.36659010927</v>
       </c>
       <c r="E364">
-        <v>0</v>
+        <v>129155.7256954687</v>
       </c>
       <c r="F364">
         <v>0</v>
@@ -7948,13 +7948,13 @@
         <v>2050</v>
       </c>
       <c r="C365">
-        <v>0</v>
+        <v>165884.5110065722</v>
       </c>
       <c r="D365">
-        <v>0</v>
+        <v>39550.12173692813</v>
       </c>
       <c r="E365">
-        <v>0</v>
+        <v>126334.389269644</v>
       </c>
       <c r="F365">
         <v>0</v>
@@ -7998,16 +7998,16 @@
         <v>2025</v>
       </c>
       <c r="C2">
-        <v>-39803.82253150942</v>
+        <v>0.001040000002831221</v>
       </c>
       <c r="D2">
-        <v>10661.35723241403</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>-50465.17976392346</v>
+        <v>0.001040000002831221</v>
       </c>
       <c r="F2">
-        <v>-84520.60086632025</v>
+        <v>0.001040000002831221</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8018,16 +8018,16 @@
         <v>2026</v>
       </c>
       <c r="C3">
-        <v>-39999.04804021725</v>
+        <v>-0.003280000004451722</v>
       </c>
       <c r="D3">
-        <v>12801.31158434302</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>-52800.35962456028</v>
+        <v>-0.003280000004451722</v>
       </c>
       <c r="F3">
-        <v>-93691.40634254742</v>
+        <v>-0.003280000004451722</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8038,16 +8038,16 @@
         <v>2027</v>
       </c>
       <c r="C4">
-        <v>-23255.24054883348</v>
+        <v>-0.002799999987473711</v>
       </c>
       <c r="D4">
-        <v>10630.70791044646</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>-33885.94845927993</v>
+        <v>-0.002799999987473711</v>
       </c>
       <c r="F4">
-        <v>-67843.46687036319</v>
+        <v>-0.002799999987473711</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8058,16 +8058,16 @@
         <v>2028</v>
       </c>
       <c r="C5">
-        <v>-19920.84932890447</v>
+        <v>-4.799995804205537E-05</v>
       </c>
       <c r="D5">
-        <v>11413.33842797994</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>-31334.18775688438</v>
+        <v>-4.799995804205537E-05</v>
       </c>
       <c r="F5">
-        <v>-67791.65164968887</v>
+        <v>-4.799995804205537E-05</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8078,16 +8078,16 @@
         <v>2029</v>
       </c>
       <c r="C6">
-        <v>-26180.6554053243</v>
+        <v>-0.0001279999851249158</v>
       </c>
       <c r="D6">
-        <v>14764.47080196743</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>-40945.12620729173</v>
+        <v>-0.0001279999851249158</v>
       </c>
       <c r="F6">
-        <v>-88107.06436900483</v>
+        <v>-0.0001279999851249158</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8098,16 +8098,16 @@
         <v>2030</v>
       </c>
       <c r="C7">
-        <v>-16879.57836789731</v>
+        <v>0.002367999986745417</v>
       </c>
       <c r="D7">
-        <v>14449.45133618195</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>-31329.02970407926</v>
+        <v>0.002367999986745417</v>
       </c>
       <c r="F7">
-        <v>-77484.70568651191</v>
+        <v>0.002367999986745417</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8118,16 +8118,16 @@
         <v>2031</v>
       </c>
       <c r="C8">
-        <v>-19718.720098041</v>
+        <v>-0.00015999999595806</v>
       </c>
       <c r="D8">
-        <v>17123.78561613223</v>
+        <v>0</v>
       </c>
       <c r="E8">
-        <v>-36842.5057141732</v>
+        <v>-0.00015999999595806</v>
       </c>
       <c r="F8">
-        <v>-91540.76948227559</v>
+        <v>-0.00015999999595806</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8138,16 +8138,16 @@
         <v>2032</v>
       </c>
       <c r="C9">
-        <v>-11164.49514836795</v>
+        <v>0.0001439999905414879</v>
       </c>
       <c r="D9">
-        <v>17093.62083438268</v>
+        <v>0</v>
       </c>
       <c r="E9">
-        <v>-28258.11598275061</v>
+        <v>0.0001439999905414879</v>
       </c>
       <c r="F9">
-        <v>-82860.02481943584</v>
+        <v>0.0001439999905414879</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8158,16 +8158,16 @@
         <v>2033</v>
       </c>
       <c r="C10">
-        <v>-10641.73105319077</v>
+        <v>0.002991999965161085</v>
       </c>
       <c r="D10">
-        <v>19000.24897126808</v>
+        <v>0</v>
       </c>
       <c r="E10">
-        <v>-29641.98002445878</v>
+        <v>0.002991999965161085</v>
       </c>
       <c r="F10">
-        <v>-90334.20388125227</v>
+        <v>0.002991999965161085</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8178,16 +8178,16 @@
         <v>2034</v>
       </c>
       <c r="C11">
-        <v>1257.315109320858</v>
+        <v>0.0007520000217482448</v>
       </c>
       <c r="D11">
-        <v>18044.37911232284</v>
+        <v>0</v>
       </c>
       <c r="E11">
-        <v>-16787.06400300196</v>
+        <v>0.0007520000217482448</v>
       </c>
       <c r="F11">
-        <v>-74425.96642465034</v>
+        <v>0.0007520000217482448</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8198,16 +8198,16 @@
         <v>2035</v>
       </c>
       <c r="C12">
-        <v>8355.70371722721</v>
+        <v>0.002015999983996153</v>
       </c>
       <c r="D12">
-        <v>17981.41998647705</v>
+        <v>0</v>
       </c>
       <c r="E12">
-        <v>-9625.716269249795</v>
+        <v>0.002015999983996153</v>
       </c>
       <c r="F12">
-        <v>-67063.50925462507</v>
+        <v>0.002015999983996153</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8218,16 +8218,16 @@
         <v>2036</v>
       </c>
       <c r="C13">
-        <v>12885.11119537608</v>
+        <v>0.000463999982457608</v>
       </c>
       <c r="D13">
-        <v>18424.70226676582</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>-5539.591071389732</v>
+        <v>0.000463999982457608</v>
       </c>
       <c r="F13">
-        <v>-64393.35431208741</v>
+        <v>0.000463999982457608</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8238,16 +8238,16 @@
         <v>2037</v>
       </c>
       <c r="C14">
-        <v>9411.397872425965</v>
+        <v>0.003407999989576638</v>
       </c>
       <c r="D14">
-        <v>20945.64911865101</v>
+        <v>0</v>
       </c>
       <c r="E14">
-        <v>-11534.25124622503</v>
+        <v>0.003407999989576638</v>
       </c>
       <c r="F14">
-        <v>-78440.63900237309</v>
+        <v>0.003407999989576638</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -8258,16 +8258,16 @@
         <v>2038</v>
       </c>
       <c r="C15">
-        <v>16232.33783352375</v>
+        <v>-0.0004960000514984131</v>
       </c>
       <c r="D15">
-        <v>21056.16531470171</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>-4823.827481177985</v>
+        <v>-0.0004960000514984131</v>
       </c>
       <c r="F15">
-        <v>-72083.23554356804</v>
+        <v>-0.0004960000514984131</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -8278,16 +8278,16 @@
         <v>2039</v>
       </c>
       <c r="C16">
-        <v>26758.33039602812</v>
+        <v>0.000784000032581389</v>
       </c>
       <c r="D16">
-        <v>20017.26517024382</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>6741.065225784376</v>
+        <v>0.000784000032581389</v>
       </c>
       <c r="F16">
-        <v>-57199.79894659444</v>
+        <v>0.000784000032581389</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -8298,16 +8298,16 @@
         <v>2040</v>
       </c>
       <c r="C17">
-        <v>20655.32047744398</v>
+        <v>0.0006719999946653843</v>
       </c>
       <c r="D17">
-        <v>23064.78057783854</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>-2409.460100394499</v>
+        <v>0.0006719999946653843</v>
       </c>
       <c r="F17">
-        <v>-76084.95920331875</v>
+        <v>0.0006719999946653843</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -8318,16 +8318,16 @@
         <v>2041</v>
       </c>
       <c r="C18">
-        <v>34395.4676193723</v>
+        <v>-0.0007359999581240118</v>
       </c>
       <c r="D18">
-        <v>21263.81912053183</v>
+        <v>0</v>
       </c>
       <c r="E18">
-        <v>13131.64849884051</v>
+        <v>-0.0007359999581240118</v>
       </c>
       <c r="F18">
-        <v>-54791.06514902972</v>
+        <v>-0.0007359999581240118</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -8338,16 +8338,16 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>33973.91919216816</v>
+        <v>-0.001999999978579581</v>
       </c>
       <c r="D19">
-        <v>22730.07265954279</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>11243.8465326255</v>
+        <v>-0.001999999978579581</v>
       </c>
       <c r="F19">
-        <v>-61362.49984842836</v>
+        <v>-0.001999999978579581</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -8358,16 +8358,16 @@
         <v>2043</v>
       </c>
       <c r="C20">
-        <v>39289.60763491516</v>
+        <v>-0.002431999950204045</v>
       </c>
       <c r="D20">
-        <v>22821.93636397013</v>
+        <v>0</v>
       </c>
       <c r="E20">
-        <v>16467.67127094505</v>
+        <v>-0.002431999950204045</v>
       </c>
       <c r="F20">
-        <v>-56432.1140288224</v>
+        <v>-0.002431999950204045</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -8378,16 +8378,16 @@
         <v>2044</v>
       </c>
       <c r="C21">
-        <v>47468.28035947675</v>
+        <v>-0.001103999966289848</v>
       </c>
       <c r="D21">
-        <v>22025.17628213373</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>25443.10407734307</v>
+        <v>-0.001103999966289848</v>
       </c>
       <c r="F21">
-        <v>-44911.60187530122</v>
+        <v>-0.001103999966289848</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -8398,16 +8398,16 @@
         <v>2045</v>
       </c>
       <c r="C22">
-        <v>49258.2643300374</v>
+        <v>-0.002831999969203025</v>
       </c>
       <c r="D22">
-        <v>22655.05267942647</v>
+        <v>0</v>
       </c>
       <c r="E22">
-        <v>26603.21165061096</v>
+        <v>-0.002831999969203025</v>
       </c>
       <c r="F22">
-        <v>-45763.4994796713</v>
+        <v>-0.002831999969203025</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -8418,16 +8418,16 @@
         <v>2046</v>
       </c>
       <c r="C23">
-        <v>48468.45008916181</v>
+        <v>-0.0002399999648332596</v>
       </c>
       <c r="D23">
-        <v>23996.96479193042</v>
+        <v>0</v>
       </c>
       <c r="E23">
-        <v>24471.48529723141</v>
+        <v>-0.0002399999648332596</v>
       </c>
       <c r="F23">
-        <v>-52181.67652384919</v>
+        <v>-0.0002399999648332596</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -8438,16 +8438,16 @@
         <v>2047</v>
       </c>
       <c r="C24">
-        <v>51054.36722758663</v>
+        <v>-0.0001439999905414879</v>
       </c>
       <c r="D24">
-        <v>24593.22429486111</v>
+        <v>0</v>
       </c>
       <c r="E24">
-        <v>26461.14293272555</v>
+        <v>-0.0001439999905414879</v>
       </c>
       <c r="F24">
-        <v>-52096.64210057363</v>
+        <v>-0.0001439999905414879</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -8458,16 +8458,16 @@
         <v>2048</v>
       </c>
       <c r="C25">
-        <v>62149.28991658258</v>
+        <v>-0.002703999984078109</v>
       </c>
       <c r="D25">
-        <v>22908.26631284006</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>39241.02360374259</v>
+        <v>-0.002703999984078109</v>
       </c>
       <c r="F25">
-        <v>-33934.52421841508</v>
+        <v>-0.002703999984078109</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -8478,16 +8478,16 @@
         <v>2049</v>
       </c>
       <c r="C26">
-        <v>58115.08197830402</v>
+        <v>0.0008800000068731606</v>
       </c>
       <c r="D26">
-        <v>24827.00512312245</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>33288.07685518154</v>
+        <v>0.0008800000068731606</v>
       </c>
       <c r="F26">
-        <v>-46016.47093810671</v>
+        <v>0.0008800000068731606</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -8498,16 +8498,16 @@
         <v>2050</v>
       </c>
       <c r="C27">
-        <v>61795.90197343536</v>
+        <v>0.0006240000366233289</v>
       </c>
       <c r="D27">
-        <v>24977.71648199284</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>36818.18549144251</v>
+        <v>0.0006240000366233289</v>
       </c>
       <c r="F27">
-        <v>-42967.77744246606</v>
+        <v>0.0006240000366233289</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -8538,16 +8538,16 @@
         <v>2026</v>
       </c>
       <c r="C29">
-        <v>-39803.82253150942</v>
+        <v>0.001040000002831221</v>
       </c>
       <c r="D29">
-        <v>10661.35723241403</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>-50465.17976392346</v>
+        <v>0.001040000002831221</v>
       </c>
       <c r="F29">
-        <v>-84520.60086632025</v>
+        <v>0.001040000002831221</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -8558,16 +8558,16 @@
         <v>2027</v>
       </c>
       <c r="C30">
-        <v>-79802.87057172667</v>
+        <v>-0.002240000001620501</v>
       </c>
       <c r="D30">
-        <v>23462.66881675705</v>
+        <v>0</v>
       </c>
       <c r="E30">
-        <v>-103265.5393884837</v>
+        <v>-0.002240000001620501</v>
       </c>
       <c r="F30">
-        <v>-178212.0072088677</v>
+        <v>-0.002240000001620501</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -8578,16 +8578,16 @@
         <v>2028</v>
       </c>
       <c r="C31">
-        <v>-103058.1111205601</v>
+        <v>-0.005039999989094213</v>
       </c>
       <c r="D31">
-        <v>34093.37672720352</v>
+        <v>0</v>
       </c>
       <c r="E31">
-        <v>-137151.4878477637</v>
+        <v>-0.005039999989094213</v>
       </c>
       <c r="F31">
-        <v>-246055.4740792309</v>
+        <v>-0.005039999989094213</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -8598,16 +8598,16 @@
         <v>2029</v>
       </c>
       <c r="C32">
-        <v>-122978.9604494646</v>
+        <v>-0.005087999947136268</v>
       </c>
       <c r="D32">
-        <v>45506.71515518345</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>-168485.675604648</v>
+        <v>-0.005087999947136268</v>
       </c>
       <c r="F32">
-        <v>-313847.1257289198</v>
+        <v>-0.005087999947136268</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -8618,16 +8618,16 @@
         <v>2030</v>
       </c>
       <c r="C33">
-        <v>-149159.6158547889</v>
+        <v>-0.005215999932261184</v>
       </c>
       <c r="D33">
-        <v>60271.18595715088</v>
+        <v>0</v>
       </c>
       <c r="E33">
-        <v>-209430.8018119398</v>
+        <v>-0.005215999932261184</v>
       </c>
       <c r="F33">
-        <v>-401954.1900979246</v>
+        <v>-0.005215999932261184</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -8638,16 +8638,16 @@
         <v>2031</v>
       </c>
       <c r="C34">
-        <v>-166039.1942226862</v>
+        <v>-0.002847999945515767</v>
       </c>
       <c r="D34">
-        <v>74720.63729333284</v>
+        <v>0</v>
       </c>
       <c r="E34">
-        <v>-240759.831516019</v>
+        <v>-0.002847999945515767</v>
       </c>
       <c r="F34">
-        <v>-479438.8957844365</v>
+        <v>-0.002847999945515767</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -8658,16 +8658,16 @@
         <v>2032</v>
       </c>
       <c r="C35">
-        <v>-185757.9143207272</v>
+        <v>-0.003007999941473827</v>
       </c>
       <c r="D35">
-        <v>91844.42290946507</v>
+        <v>0</v>
       </c>
       <c r="E35">
-        <v>-277602.3372301923</v>
+        <v>-0.003007999941473827</v>
       </c>
       <c r="F35">
-        <v>-570979.6652667121</v>
+        <v>-0.003007999941473827</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -8678,16 +8678,16 @@
         <v>2033</v>
       </c>
       <c r="C36">
-        <v>-196922.4094690952</v>
+        <v>-0.002863999950932339</v>
       </c>
       <c r="D36">
-        <v>108938.0437438477</v>
+        <v>0</v>
       </c>
       <c r="E36">
-        <v>-305860.4532129429</v>
+        <v>-0.002863999950932339</v>
       </c>
       <c r="F36">
-        <v>-653839.690086148</v>
+        <v>-0.002863999950932339</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -8698,16 +8698,16 @@
         <v>2034</v>
       </c>
       <c r="C37">
-        <v>-207564.1405222859</v>
+        <v>0.0001280000142287463</v>
       </c>
       <c r="D37">
-        <v>127938.2927151158</v>
+        <v>0</v>
       </c>
       <c r="E37">
-        <v>-335502.4332374017</v>
+        <v>0.0001280000142287463</v>
       </c>
       <c r="F37">
-        <v>-744173.8939674003</v>
+        <v>0.0001280000142287463</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -8718,16 +8718,16 @@
         <v>2035</v>
       </c>
       <c r="C38">
-        <v>-206306.8254129651</v>
+        <v>0.0008800000359769911</v>
       </c>
       <c r="D38">
-        <v>145982.6718274387</v>
+        <v>0</v>
       </c>
       <c r="E38">
-        <v>-352289.4972404036</v>
+        <v>0.0008800000359769911</v>
       </c>
       <c r="F38">
-        <v>-818599.8603920506</v>
+        <v>0.0008800000359769911</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -8738,16 +8738,16 @@
         <v>2036</v>
       </c>
       <c r="C39">
-        <v>-197951.1216957379</v>
+        <v>0.002896000019973144</v>
       </c>
       <c r="D39">
-        <v>163964.0918139157</v>
+        <v>0</v>
       </c>
       <c r="E39">
-        <v>-361915.2135096534</v>
+        <v>0.002896000019973144</v>
       </c>
       <c r="F39">
-        <v>-885663.3696466757</v>
+        <v>0.002896000019973144</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -8758,16 +8758,16 @@
         <v>2037</v>
       </c>
       <c r="C40">
-        <v>-185066.0105003618</v>
+        <v>0.003360000002430752</v>
       </c>
       <c r="D40">
-        <v>182388.7940806815</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>-367454.8045810431</v>
+        <v>0.003360000002430752</v>
       </c>
       <c r="F40">
-        <v>-950056.7239587631</v>
+        <v>0.003360000002430752</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -8778,16 +8778,16 @@
         <v>2038</v>
       </c>
       <c r="C41">
-        <v>-175654.6126279358</v>
+        <v>0.00676799999200739</v>
       </c>
       <c r="D41">
-        <v>203334.4431993325</v>
+        <v>0</v>
       </c>
       <c r="E41">
-        <v>-378989.0558272682</v>
+        <v>0.00676799999200739</v>
       </c>
       <c r="F41">
-        <v>-1028497.362961136</v>
+        <v>0.00676799999200739</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -8798,16 +8798,16 @@
         <v>2039</v>
       </c>
       <c r="C42">
-        <v>-159422.2747944121</v>
+        <v>0.006271999940508977</v>
       </c>
       <c r="D42">
-        <v>224390.6085140342</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>-383812.8833084462</v>
+        <v>0.006271999940508977</v>
       </c>
       <c r="F42">
-        <v>-1100580.598504704</v>
+        <v>0.006271999940508977</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -8818,16 +8818,16 @@
         <v>2040</v>
       </c>
       <c r="C43">
-        <v>-132663.944398384</v>
+        <v>0.007055999973090366</v>
       </c>
       <c r="D43">
-        <v>244407.8736842781</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>-377071.8180826618</v>
+        <v>0.007055999973090366</v>
       </c>
       <c r="F43">
-        <v>-1157780.397451299</v>
+        <v>0.007055999973090366</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -8838,16 +8838,16 @@
         <v>2041</v>
       </c>
       <c r="C44">
-        <v>-112008.62392094</v>
+        <v>0.00772799996775575</v>
       </c>
       <c r="D44">
-        <v>267472.6542621166</v>
+        <v>0</v>
       </c>
       <c r="E44">
-        <v>-379481.2781830563</v>
+        <v>0.00772799996775575</v>
       </c>
       <c r="F44">
-        <v>-1233865.356654617</v>
+        <v>0.00772799996775575</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -8858,16 +8858,16 @@
         <v>2042</v>
       </c>
       <c r="C45">
-        <v>-77613.15630156768</v>
+        <v>0.006992000009631738</v>
       </c>
       <c r="D45">
-        <v>288736.4733826485</v>
+        <v>0</v>
       </c>
       <c r="E45">
-        <v>-366349.6296842158</v>
+        <v>0.006992000009631738</v>
       </c>
       <c r="F45">
-        <v>-1288656.421803647</v>
+        <v>0.006992000009631738</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -8878,16 +8878,16 @@
         <v>2043</v>
       </c>
       <c r="C46">
-        <v>-43639.23710939952</v>
+        <v>0.004992000031052157</v>
       </c>
       <c r="D46">
-        <v>311466.5460421913</v>
+        <v>0</v>
       </c>
       <c r="E46">
-        <v>-355105.7831515903</v>
+        <v>0.004992000031052157</v>
       </c>
       <c r="F46">
-        <v>-1350018.921652075</v>
+        <v>0.004992000031052157</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -8898,16 +8898,16 @@
         <v>2044</v>
       </c>
       <c r="C47">
-        <v>-4349.629474484362</v>
+        <v>0.002560000080848113</v>
       </c>
       <c r="D47">
-        <v>334288.4824061614</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>-338638.1118806452</v>
+        <v>0.002560000080848113</v>
       </c>
       <c r="F47">
-        <v>-1406451.035680898</v>
+        <v>0.002560000080848113</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -8918,16 +8918,16 @@
         <v>2045</v>
       </c>
       <c r="C48">
-        <v>43118.65088499238</v>
+        <v>0.001456000114558265</v>
       </c>
       <c r="D48">
-        <v>356313.6586882951</v>
+        <v>0</v>
       </c>
       <c r="E48">
-        <v>-313195.0078033021</v>
+        <v>0.001456000114558265</v>
       </c>
       <c r="F48">
-        <v>-1451362.637556199</v>
+        <v>0.001456000114558265</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -8938,16 +8938,16 @@
         <v>2046</v>
       </c>
       <c r="C49">
-        <v>92376.91521502979</v>
+        <v>-0.00137599985464476</v>
       </c>
       <c r="D49">
-        <v>378968.7113677216</v>
+        <v>0</v>
       </c>
       <c r="E49">
-        <v>-286591.7961526912</v>
+        <v>-0.00137599985464476</v>
       </c>
       <c r="F49">
-        <v>-1497126.13703587</v>
+        <v>-0.00137599985464476</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -8958,16 +8958,16 @@
         <v>2047</v>
       </c>
       <c r="C50">
-        <v>140845.3653041916</v>
+        <v>-0.00161599981947802</v>
       </c>
       <c r="D50">
-        <v>402965.676159652</v>
+        <v>0</v>
       </c>
       <c r="E50">
-        <v>-262120.3108554598</v>
+        <v>-0.00161599981947802</v>
       </c>
       <c r="F50">
-        <v>-1549307.813559719</v>
+        <v>-0.00161599981947802</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -8978,16 +8978,16 @@
         <v>2048</v>
       </c>
       <c r="C51">
-        <v>191899.7325317782</v>
+        <v>-0.001759999810019508</v>
       </c>
       <c r="D51">
-        <v>427558.9004545131</v>
+        <v>0</v>
       </c>
       <c r="E51">
-        <v>-235659.1679227342</v>
+        <v>-0.001759999810019508</v>
       </c>
       <c r="F51">
-        <v>-1601404.455660293</v>
+        <v>-0.001759999810019508</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -8998,16 +8998,16 @@
         <v>2049</v>
       </c>
       <c r="C52">
-        <v>254049.0224483608</v>
+        <v>-0.004463999794097617</v>
       </c>
       <c r="D52">
-        <v>450467.1667673531</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>-196418.1443189916</v>
+        <v>-0.004463999794097617</v>
       </c>
       <c r="F52">
-        <v>-1635338.979878708</v>
+        <v>-0.004463999794097617</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -9018,16 +9018,16 @@
         <v>2050</v>
       </c>
       <c r="C53">
-        <v>312164.1044266648</v>
+        <v>-0.003583999787224457</v>
       </c>
       <c r="D53">
-        <v>475294.1718904756</v>
+        <v>0</v>
       </c>
       <c r="E53">
-        <v>-163130.0674638101</v>
+        <v>-0.003583999787224457</v>
       </c>
       <c r="F53">
-        <v>-1681355.450816815</v>
+        <v>-0.003583999787224457</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -9038,13 +9038,13 @@
         <v>2025</v>
       </c>
       <c r="C54">
-        <v>-164945.6975903904</v>
+        <v>-0.001040000002831221</v>
       </c>
       <c r="D54">
-        <v>-39326.29020092187</v>
+        <v>-0.0002479564136592671</v>
       </c>
       <c r="E54">
-        <v>-125619.4073894685</v>
+        <v>-0.0007920435746200383</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -9058,13 +9058,13 @@
         <v>2026</v>
       </c>
       <c r="C55">
-        <v>-186966.5601539384</v>
+        <v>0.003279999946244061</v>
       </c>
       <c r="D55">
-        <v>-44576.49584010887</v>
+        <v>0.0007820163300493732</v>
       </c>
       <c r="E55">
-        <v>-142390.0643138295</v>
+        <v>0.002497983630746603</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>2027</v>
       </c>
       <c r="C56">
-        <v>-141094.2363658061</v>
+        <v>0.002800000016577542</v>
       </c>
       <c r="D56">
-        <v>-33639.63392836272</v>
+        <v>0.0006675749173155054</v>
       </c>
       <c r="E56">
-        <v>-107454.6024374434</v>
+        <v>0.002132425084710121</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -9098,13 +9098,13 @@
         <v>2028</v>
       </c>
       <c r="C57">
-        <v>-144303.1128844892</v>
+        <v>4.799995804205537E-05</v>
       </c>
       <c r="D57">
-        <v>-34404.69304197494</v>
+        <v>1.144413545262069E-05</v>
       </c>
       <c r="E57">
-        <v>-109898.4198425142</v>
+        <v>3.655586624518037E-05</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -9118,13 +9118,13 @@
         <v>2029</v>
       </c>
       <c r="C58">
-        <v>-187257.000217265</v>
+        <v>0.0001279999269172549</v>
       </c>
       <c r="D58">
-        <v>-44645.74244904269</v>
+        <v>3.051769454032183E-05</v>
       </c>
       <c r="E58">
-        <v>-142611.2577682223</v>
+        <v>9.74822323769331E-05</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -9138,13 +9138,13 @@
         <v>2030</v>
       </c>
       <c r="C59">
-        <v>-170825.6252525288</v>
+        <v>-0.002367999986745417</v>
       </c>
       <c r="D59">
-        <v>-40728.1803076642</v>
+        <v>-0.0005645776545861736</v>
       </c>
       <c r="E59">
-        <v>-130097.4449448646</v>
+        <v>-0.001803422346711159</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -9158,13 +9158,13 @@
         <v>2031</v>
       </c>
       <c r="C60">
-        <v>-202037.0195392545</v>
+        <v>0.0001600000541657209</v>
       </c>
       <c r="D60">
-        <v>-48169.58900898871</v>
+        <v>3.814713272731751E-05</v>
       </c>
       <c r="E60">
-        <v>-153867.4305302658</v>
+        <v>0.0001218528486788273</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -9178,13 +9178,13 @@
         <v>2032</v>
       </c>
       <c r="C61">
-        <v>-189562.3095111181</v>
+        <v>-0.0001439999905414879</v>
       </c>
       <c r="D61">
-        <v>-45195.37341012471</v>
+        <v>-3.433242090977728E-05</v>
       </c>
       <c r="E61">
-        <v>-144366.9361009934</v>
+        <v>-0.0001096675987355411</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -9198,13 +9198,13 @@
         <v>2033</v>
       </c>
       <c r="C62">
-        <v>-208191.134434339</v>
+        <v>-0.002991999965161085</v>
       </c>
       <c r="D62">
-        <v>-49636.85073105502</v>
+        <v>-0.0007133515027817339</v>
       </c>
       <c r="E62">
-        <v>-158554.283703284</v>
+        <v>-0.002278648549690843</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -9218,13 +9218,13 @@
         <v>2034</v>
       </c>
       <c r="C63">
-        <v>-181552.7782310514</v>
+        <v>-0.0007519999635405838</v>
       </c>
       <c r="D63">
-        <v>-43285.74402242484</v>
+        <v>-0.0001792915572877973</v>
       </c>
       <c r="E63">
-        <v>-138267.0342086266</v>
+        <v>-0.000572708435356617</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -9238,13 +9238,13 @@
         <v>2035</v>
       </c>
       <c r="C64">
-        <v>-170815.7600898655</v>
+        <v>-0.002016000042203814</v>
       </c>
       <c r="D64">
-        <v>-40725.82825935107</v>
+        <v>-0.0004806539509445429</v>
       </c>
       <c r="E64">
-        <v>-130089.9318305145</v>
+        <v>-0.001535346091259271</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -9258,13 +9258,13 @@
         <v>2036</v>
       </c>
       <c r="C65">
-        <v>-168876.7652072157</v>
+        <v>-0.0004640000988729298</v>
       </c>
       <c r="D65">
-        <v>-40263.53384023535</v>
+        <v>-0.000110626730020158</v>
       </c>
       <c r="E65">
-        <v>-128613.2313669804</v>
+        <v>-0.0003533732960931957</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -9278,13 +9278,13 @@
         <v>2037</v>
       </c>
       <c r="C66">
-        <v>-199432.3339440663</v>
+        <v>-0.003407999989576638</v>
       </c>
       <c r="D66">
-        <v>-47548.58086452102</v>
+        <v>-0.0008125340682454407</v>
       </c>
       <c r="E66">
-        <v>-151883.7530795452</v>
+        <v>-0.002595465921331197</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -9298,13 +9298,13 @@
         <v>2038</v>
       </c>
       <c r="C67">
-        <v>-190852.5777743378</v>
+        <v>0.0004959999932907522</v>
       </c>
       <c r="D67">
-        <v>-45502.99867648614</v>
+        <v>0.0001182561099994928</v>
       </c>
       <c r="E67">
-        <v>-145349.5790978516</v>
+        <v>0.000377743795979768</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -9318,13 +9318,13 @@
         <v>2039</v>
       </c>
       <c r="C68">
-        <v>-165323.7367201426</v>
+        <v>-0.000783999974373728</v>
       </c>
       <c r="D68">
-        <v>-39416.42214580506</v>
+        <v>-0.0001869209663709626</v>
       </c>
       <c r="E68">
-        <v>-125907.3145743376</v>
+        <v>-0.0005970789934508502</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -9338,13 +9338,13 @@
         <v>2040</v>
       </c>
       <c r="C69">
-        <v>-204969.6612606774</v>
+        <v>-0.0006719999946653843</v>
       </c>
       <c r="D69">
-        <v>-48868.78832777544</v>
+        <v>-0.000160217983648181</v>
       </c>
       <c r="E69">
-        <v>-156100.872932902</v>
+        <v>-0.0005117820692248642</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -9358,13 +9358,13 @@
         <v>2041</v>
       </c>
       <c r="C70">
-        <v>-167125.7593176033</v>
+        <v>0.0007359999581240118</v>
       </c>
       <c r="D70">
-        <v>-39846.05968501716</v>
+        <v>0.0001754768454702571</v>
       </c>
       <c r="E70">
-        <v>-127279.6996325861</v>
+        <v>0.0005605231272056699</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>2042</v>
       </c>
       <c r="C71">
-        <v>-182623.3810342913</v>
+        <v>0.001999999862164259</v>
       </c>
       <c r="D71">
-        <v>-43540.9967337425</v>
+        <v>0.0004768392245750874</v>
       </c>
       <c r="E71">
-        <v>-139082.3843005488</v>
+        <v>0.001523160666693002</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -9398,13 +9398,13 @@
         <v>2043</v>
       </c>
       <c r="C72">
-        <v>-175995.3043326439</v>
+        <v>0.002432000008411705</v>
       </c>
       <c r="D72">
-        <v>-41960.73321883565</v>
+        <v>0.0005798365164082497</v>
       </c>
       <c r="E72">
-        <v>-134034.5711138083</v>
+        <v>0.001852163462899625</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -9418,13 +9418,13 @@
         <v>2044</v>
       </c>
       <c r="C73">
-        <v>-156265.7628480942</v>
+        <v>0.001104000024497509</v>
       </c>
       <c r="D73">
-        <v>-37256.82347588925</v>
+        <v>0.0002632152463775128</v>
       </c>
       <c r="E73">
-        <v>-119008.9393722049</v>
+        <v>0.0008407847490161657</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -9438,13 +9438,13 @@
         <v>2045</v>
       </c>
       <c r="C74">
-        <v>-160119.4480695512</v>
+        <v>0.002832000085618347</v>
       </c>
       <c r="D74">
-        <v>-38175.61763406348</v>
+        <v>0.0006752043555025011</v>
       </c>
       <c r="E74">
-        <v>-121943.8304354877</v>
+        <v>0.002156795701012015</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -9458,13 +9458,13 @@
         <v>2046</v>
       </c>
       <c r="C75">
-        <v>-174877.5496139904</v>
+        <v>0.0002399999066255987</v>
       </c>
       <c r="D75">
-        <v>-41694.23856585975</v>
+        <v>5.722069181501865E-05</v>
       </c>
       <c r="E75">
-        <v>-133183.3110481306</v>
+        <v>0.00018277921481058</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -9478,13 +9478,13 @@
         <v>2047</v>
       </c>
       <c r="C76">
-        <v>-177257.4727425422</v>
+        <v>0.0001439999905414879</v>
       </c>
       <c r="D76">
-        <v>-42261.65892890394</v>
+        <v>3.433240635786206E-05</v>
       </c>
       <c r="E76">
-        <v>-134995.8138136383</v>
+        <v>0.0001096674823202193</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -9498,13 +9498,13 @@
         <v>2048</v>
       </c>
       <c r="C77">
-        <v>-144355.0106394874</v>
+        <v>0.002703999984078109</v>
       </c>
       <c r="D77">
-        <v>-34417.06648489375</v>
+        <v>0.0006446866464102641</v>
       </c>
       <c r="E77">
-        <v>-109937.9441545937</v>
+        <v>0.00205931335221976</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -9518,13 +9518,13 @@
         <v>2049</v>
       </c>
       <c r="C78">
-        <v>-169589.093165578</v>
+        <v>-0.0008800000650808215</v>
       </c>
       <c r="D78">
-        <v>-40433.36679991853</v>
+        <v>-0.0002098092518281192</v>
       </c>
       <c r="E78">
-        <v>-129155.7263656595</v>
+        <v>-0.0006701907841488719</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -9538,13 +9538,13 @@
         <v>2050</v>
       </c>
       <c r="C79">
-        <v>-165884.5116305721</v>
+        <v>-0.000623999978415668</v>
       </c>
       <c r="D79">
-        <v>-39550.12188570197</v>
+        <v>-0.0001487738481955603</v>
       </c>
       <c r="E79">
-        <v>-126334.3897448702</v>
+        <v>-0.000475226144772023</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -9578,13 +9578,13 @@
         <v>2026</v>
       </c>
       <c r="C81">
-        <v>-164945.6975903904</v>
+        <v>-0.001040000002831221</v>
       </c>
       <c r="D81">
-        <v>-39326.29020092187</v>
+        <v>-0.0002479564136592671</v>
       </c>
       <c r="E81">
-        <v>-125619.4073894685</v>
+        <v>-0.0007920435746200383</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -9598,13 +9598,13 @@
         <v>2027</v>
       </c>
       <c r="C82">
-        <v>-351912.2577443288</v>
+        <v>0.00223999994341284</v>
       </c>
       <c r="D82">
-        <v>-83902.78604103073</v>
+        <v>0.0005340599163901061</v>
       </c>
       <c r="E82">
-        <v>-268009.471703298</v>
+        <v>0.001705940056126565</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -9618,13 +9618,13 @@
         <v>2028</v>
       </c>
       <c r="C83">
-        <v>-493006.4941101348</v>
+        <v>0.005039999959990382</v>
       </c>
       <c r="D83">
-        <v>-117542.4199693934</v>
+        <v>0.001201634833705612</v>
       </c>
       <c r="E83">
-        <v>-375464.0741407414</v>
+        <v>0.003838365140836686</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -9638,13 +9638,13 @@
         <v>2029</v>
       </c>
       <c r="C84">
-        <v>-637309.606994624</v>
+        <v>0.005087999918032438</v>
       </c>
       <c r="D84">
-        <v>-151947.1130113684</v>
+        <v>0.001213078969158232</v>
       </c>
       <c r="E84">
-        <v>-485362.4939832556</v>
+        <v>0.003874921007081866</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -9658,13 +9658,13 @@
         <v>2030</v>
       </c>
       <c r="C85">
-        <v>-824566.607211889</v>
+        <v>0.005215999844949692</v>
       </c>
       <c r="D85">
-        <v>-196592.8554604111</v>
+        <v>0.001243596663698554</v>
       </c>
       <c r="E85">
-        <v>-627973.7517514778</v>
+        <v>0.003972403239458799</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -9678,13 +9678,13 @@
         <v>2031</v>
       </c>
       <c r="C86">
-        <v>-995392.2324644178</v>
+        <v>0.002847999858204275</v>
       </c>
       <c r="D86">
-        <v>-237321.0357680753</v>
+        <v>0.0006790190091123804</v>
       </c>
       <c r="E86">
-        <v>-758071.1966963424</v>
+        <v>0.002168980892747641</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -9698,13 +9698,13 @@
         <v>2032</v>
       </c>
       <c r="C87">
-        <v>-1197429.252003672</v>
+        <v>0.003007999912369996</v>
       </c>
       <c r="D87">
-        <v>-285490.624777064</v>
+        <v>0.000717166141839698</v>
       </c>
       <c r="E87">
-        <v>-911938.6272266083</v>
+        <v>0.002290833741426468</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -9718,13 +9718,13 @@
         <v>2033</v>
       </c>
       <c r="C88">
-        <v>-1386991.56151479</v>
+        <v>0.002863999921828508</v>
       </c>
       <c r="D88">
-        <v>-330685.9981871886</v>
+        <v>0.0006828337209299207</v>
       </c>
       <c r="E88">
-        <v>-1056305.563327602</v>
+        <v>0.002181166142690927</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -9738,13 +9738,13 @@
         <v>2034</v>
       </c>
       <c r="C89">
-        <v>-1595182.695949129</v>
+        <v>-0.0001280000433325768</v>
       </c>
       <c r="D89">
-        <v>-380322.8489182437</v>
+        <v>-3.05177818518132E-05</v>
       </c>
       <c r="E89">
-        <v>-1214859.847030886</v>
+        <v>-9.748240699991584E-05</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -9758,13 +9758,13 @@
         <v>2035</v>
       </c>
       <c r="C90">
-        <v>-1776735.474180181</v>
+        <v>-0.0008800000068731606</v>
       </c>
       <c r="D90">
-        <v>-423608.5929406685</v>
+        <v>-0.0002098093391396105</v>
       </c>
       <c r="E90">
-        <v>-1353126.881239512</v>
+        <v>-0.0006701908423565328</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -9778,13 +9778,13 @@
         <v>2036</v>
       </c>
       <c r="C91">
-        <v>-1947551.234270046</v>
+        <v>-0.002896000049076974</v>
       </c>
       <c r="D91">
-        <v>-464334.4212000196</v>
+        <v>-0.0006904632900841534</v>
       </c>
       <c r="E91">
-        <v>-1483216.813070026</v>
+        <v>-0.002205536933615804</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -9798,13 +9798,13 @@
         <v>2037</v>
       </c>
       <c r="C92">
-        <v>-2116427.999477262</v>
+        <v>-0.003360000147949904</v>
       </c>
       <c r="D92">
-        <v>-504597.955040255</v>
+        <v>-0.0008010900201043114</v>
       </c>
       <c r="E92">
-        <v>-1611830.044437007</v>
+        <v>-0.002558910229708999</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -9818,13 +9818,13 @@
         <v>2038</v>
       </c>
       <c r="C93">
-        <v>-2315860.333421328</v>
+        <v>-0.006768000137526542</v>
       </c>
       <c r="D93">
-        <v>-552146.535904776</v>
+        <v>-0.001613624088349752</v>
       </c>
       <c r="E93">
-        <v>-1763713.797516552</v>
+        <v>-0.005154376151040196</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -9838,13 +9838,13 @@
         <v>2039</v>
       </c>
       <c r="C94">
-        <v>-2506712.911195666</v>
+        <v>-0.00627200014423579</v>
       </c>
       <c r="D94">
-        <v>-597649.5345812622</v>
+        <v>-0.001495367978350259</v>
       </c>
       <c r="E94">
-        <v>-1909063.376614404</v>
+        <v>-0.004776632355060428</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -9858,13 +9858,13 @@
         <v>2040</v>
       </c>
       <c r="C95">
-        <v>-2672036.647915808</v>
+        <v>-0.007056000118609518</v>
       </c>
       <c r="D95">
-        <v>-637065.9567270672</v>
+        <v>-0.001682288944721222</v>
       </c>
       <c r="E95">
-        <v>-2034970.691188741</v>
+        <v>-0.005373711348511279</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -9878,13 +9878,13 @@
         <v>2041</v>
       </c>
       <c r="C96">
-        <v>-2877006.309176486</v>
+        <v>-0.007728000113274902</v>
       </c>
       <c r="D96">
-        <v>-685934.7450548427</v>
+        <v>-0.001842506928369403</v>
       </c>
       <c r="E96">
-        <v>-2191071.564121643</v>
+        <v>-0.005885493417736143</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -9898,13 +9898,13 @@
         <v>2042</v>
       </c>
       <c r="C97">
-        <v>-3044132.068494089</v>
+        <v>-0.00699200015515089</v>
       </c>
       <c r="D97">
-        <v>-725780.8047398599</v>
+        <v>-0.001667030082899146</v>
       </c>
       <c r="E97">
-        <v>-2318351.263754229</v>
+        <v>-0.005324970290530473</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -9918,13 +9918,13 @@
         <v>2043</v>
       </c>
       <c r="C98">
-        <v>-3226755.449528381</v>
+        <v>-0.004992000292986631</v>
       </c>
       <c r="D98">
-        <v>-769321.8014736024</v>
+        <v>-0.001190190858324058</v>
       </c>
       <c r="E98">
-        <v>-2457433.648054778</v>
+        <v>-0.003801809623837471</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -9938,13 +9938,13 @@
         <v>2044</v>
       </c>
       <c r="C99">
-        <v>-3402750.753861025</v>
+        <v>-0.002560000284574926</v>
       </c>
       <c r="D99">
-        <v>-811282.5346924381</v>
+        <v>-0.0006103543419158086</v>
       </c>
       <c r="E99">
-        <v>-2591468.219168586</v>
+        <v>-0.001949646160937846</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -9958,13 +9958,13 @@
         <v>2045</v>
       </c>
       <c r="C100">
-        <v>-3559016.516709119</v>
+        <v>-0.001456000260077417</v>
       </c>
       <c r="D100">
-        <v>-848539.3581683274</v>
+        <v>-0.0003471390955382958</v>
       </c>
       <c r="E100">
-        <v>-2710477.15854079</v>
+        <v>-0.00110886141192168</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -9978,13 +9978,13 @@
         <v>2046</v>
       </c>
       <c r="C101">
-        <v>-3719135.96477867</v>
+        <v>0.00137599982554093</v>
       </c>
       <c r="D101">
-        <v>-886714.9758023908</v>
+        <v>0.0003280652599642053</v>
       </c>
       <c r="E101">
-        <v>-2832420.988976278</v>
+        <v>0.001047934289090335</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -9998,13 +9998,13 @@
         <v>2047</v>
       </c>
       <c r="C102">
-        <v>-3894013.51439266</v>
+        <v>0.001615999732166529</v>
       </c>
       <c r="D102">
-        <v>-928409.2143682506</v>
+        <v>0.000385285951779224</v>
       </c>
       <c r="E102">
-        <v>-2965604.300024409</v>
+        <v>0.001230713503900915</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -10018,13 +10018,13 @@
         <v>2048</v>
       </c>
       <c r="C103">
-        <v>-4071270.987135202</v>
+        <v>0.001759999722708017</v>
       </c>
       <c r="D103">
-        <v>-970670.8732971546</v>
+        <v>0.000419618358137086</v>
       </c>
       <c r="E103">
-        <v>-3100600.113838047</v>
+        <v>0.001340380986221135</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -10038,13 +10038,13 @@
         <v>2049</v>
       </c>
       <c r="C104">
-        <v>-4215625.997774689</v>
+        <v>0.004463999706786126</v>
       </c>
       <c r="D104">
-        <v>-1005087.939782048</v>
+        <v>0.00106430500454735</v>
       </c>
       <c r="E104">
-        <v>-3210538.057992641</v>
+        <v>0.003399694338440895</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -10058,13 +10058,13 @@
         <v>2050</v>
       </c>
       <c r="C105">
-        <v>-4385215.090940268</v>
+        <v>0.003583999641705304</v>
       </c>
       <c r="D105">
-        <v>-1045521.306581967</v>
+        <v>0.0008544957527192309</v>
       </c>
       <c r="E105">
-        <v>-3339693.7843583</v>
+        <v>0.002729503554292023</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -10078,16 +10078,16 @@
         <v>2025</v>
       </c>
       <c r="C106">
-        <v>204749.5201218998</v>
+        <v>0</v>
       </c>
       <c r="D106">
-        <v>28664.93281706598</v>
+        <v>9.651455184211954E-05</v>
       </c>
       <c r="E106">
-        <v>176084.5873048338</v>
+        <v>-9.65145300142467E-05</v>
       </c>
       <c r="F106">
-        <v>84520.60190632024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -10098,16 +10098,16 @@
         <v>2026</v>
       </c>
       <c r="C107">
-        <v>226965.6081941556</v>
+        <v>0</v>
       </c>
       <c r="D107">
-        <v>31775.18514718178</v>
+        <v>0.0001093996033887379</v>
       </c>
       <c r="E107">
-        <v>195190.4230469738</v>
+        <v>-0.0001093996106646955</v>
       </c>
       <c r="F107">
-        <v>93691.40306254741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -10118,16 +10118,16 @@
         <v>2027</v>
       </c>
       <c r="C108">
-        <v>164349.4769146396</v>
+        <v>2.91038304567337E-11</v>
       </c>
       <c r="D108">
-        <v>23008.92676804954</v>
+        <v>8.255837019532919E-05</v>
       </c>
       <c r="E108">
-        <v>141340.55014659</v>
+        <v>-8.255834109149873E-05</v>
       </c>
       <c r="F108">
-        <v>67843.46407036322</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -10138,16 +10138,16 @@
         <v>2028</v>
       </c>
       <c r="C109">
-        <v>164223.9622133937</v>
+        <v>0</v>
       </c>
       <c r="D109">
-        <v>22991.35470987512</v>
+        <v>8.443597471341491E-05</v>
       </c>
       <c r="E109">
-        <v>141232.6075035185</v>
+        <v>-8.443594560958445E-05</v>
       </c>
       <c r="F109">
-        <v>67791.65160168891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -10158,16 +10158,16 @@
         <v>2029</v>
       </c>
       <c r="C110">
-        <v>213437.6556225892</v>
+        <v>0</v>
       </c>
       <c r="D110">
-        <v>29881.2717871625</v>
+        <v>0.0001095695479307324</v>
       </c>
       <c r="E110">
-        <v>183556.3838354267</v>
+        <v>-0.0001095695188269019</v>
       </c>
       <c r="F110">
-        <v>88107.06424100482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -10178,16 +10178,16 @@
         <v>2030</v>
       </c>
       <c r="C111">
-        <v>187705.2036204261</v>
+        <v>0</v>
       </c>
       <c r="D111">
-        <v>26278.72850685965</v>
+        <v>9.995506115956232E-05</v>
       </c>
       <c r="E111">
-        <v>161426.4751135664</v>
+        <v>-9.995503933168948E-05</v>
       </c>
       <c r="F111">
-        <v>77484.7080545119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -10198,16 +10198,16 @@
         <v>2031</v>
       </c>
       <c r="C112">
-        <v>221755.7396372956</v>
+        <v>0</v>
       </c>
       <c r="D112">
-        <v>31045.80354922138</v>
+        <v>0.000118217765702866</v>
       </c>
       <c r="E112">
-        <v>190709.9360880742</v>
+        <v>-0.0001182177220471203</v>
       </c>
       <c r="F112">
-        <v>91540.76932227562</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -10218,16 +10218,16 @@
         <v>2032</v>
       </c>
       <c r="C113">
-        <v>200726.804659486</v>
+        <v>0</v>
       </c>
       <c r="D113">
-        <v>28101.75265232805</v>
+        <v>0.0001109184449887834</v>
       </c>
       <c r="E113">
-        <v>172625.052007158</v>
+        <v>-0.0001109184231609106</v>
       </c>
       <c r="F113">
-        <v>82860.02496343585</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -10238,16 +10238,16 @@
         <v>2033</v>
       </c>
       <c r="C114">
-        <v>218832.8654875298</v>
+        <v>5.820766091346741E-11</v>
       </c>
       <c r="D114">
-        <v>30636.60116825417</v>
+        <v>0.0001218187244376168</v>
       </c>
       <c r="E114">
-        <v>188196.2643192756</v>
+        <v>-0.0001218186807818711</v>
       </c>
       <c r="F114">
-        <v>90334.20687325227</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -10258,16 +10258,16 @@
         <v>2034</v>
       </c>
       <c r="C115">
-        <v>180295.4631217306</v>
+        <v>0</v>
       </c>
       <c r="D115">
-        <v>25241.36483704229</v>
+        <v>0.0001062318406184204</v>
       </c>
       <c r="E115">
-        <v>155054.0982846884</v>
+        <v>-0.0001062317751348019</v>
       </c>
       <c r="F115">
-        <v>74425.96717665039</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -10278,16 +10278,16 @@
         <v>2035</v>
       </c>
       <c r="C116">
-        <v>162460.0563726382</v>
+        <v>0</v>
       </c>
       <c r="D116">
-        <v>22744.40789216935</v>
+        <v>9.994929860113189E-05</v>
       </c>
       <c r="E116">
-        <v>139715.6484804688</v>
+        <v>-9.994927677325904E-05</v>
       </c>
       <c r="F116">
-        <v>67063.51127062505</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -10298,16 +10298,16 @@
         <v>2036</v>
       </c>
       <c r="C117">
-        <v>155991.6540118396</v>
+        <v>5.820766091346741E-11</v>
       </c>
       <c r="D117">
-        <v>21838.83156165755</v>
+        <v>9.881473670247942E-05</v>
       </c>
       <c r="E117">
-        <v>134152.8224501821</v>
+        <v>-9.881469304673374E-05</v>
       </c>
       <c r="F117">
-        <v>64393.35477608738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -10318,16 +10318,16 @@
         <v>2037</v>
       </c>
       <c r="C118">
-        <v>190020.9360716403</v>
+        <v>0</v>
       </c>
       <c r="D118">
-        <v>26602.93105002964</v>
+        <v>0.0001166936926892959</v>
       </c>
       <c r="E118">
-        <v>163418.0050216106</v>
+        <v>-0.000116693670861423</v>
       </c>
       <c r="F118">
-        <v>78440.64241037308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -10338,16 +10338,16 @@
         <v>2038</v>
       </c>
       <c r="C119">
-        <v>174620.239940814</v>
+        <v>0</v>
       </c>
       <c r="D119">
-        <v>24446.83359171397</v>
+        <v>0.0001116734274546616</v>
       </c>
       <c r="E119">
-        <v>150173.4063491001</v>
+        <v>-0.0001116734347306192</v>
       </c>
       <c r="F119">
-        <v>72083.23504756803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -10358,16 +10358,16 @@
         <v>2039</v>
       </c>
       <c r="C120">
-        <v>138565.4063241146</v>
+        <v>0</v>
       </c>
       <c r="D120">
-        <v>19399.15688537603</v>
+        <v>9.673575550550595E-05</v>
       </c>
       <c r="E120">
-        <v>119166.2494387385</v>
+        <v>-9.673574822954834E-05</v>
       </c>
       <c r="F120">
-        <v>57199.79973059449</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -10378,16 +10378,16 @@
         <v>2040</v>
       </c>
       <c r="C121">
-        <v>184314.3407832333</v>
+        <v>5.820766091346741E-11</v>
       </c>
       <c r="D121">
-        <v>25804.00770965267</v>
+        <v>0.0001199337493744679</v>
       </c>
       <c r="E121">
-        <v>158510.3330735807</v>
+        <v>-0.0001199336838908494</v>
       </c>
       <c r="F121">
-        <v>76084.95987531872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -10398,16 +10398,16 @@
         <v>2041</v>
       </c>
       <c r="C122">
-        <v>132730.291698231</v>
+        <v>0</v>
       </c>
       <c r="D122">
-        <v>18582.24083775234</v>
+        <v>9.779017273103818E-05</v>
       </c>
       <c r="E122">
-        <v>114148.0508604786</v>
+        <v>-9.779015090316534E-05</v>
       </c>
       <c r="F122">
-        <v>54791.06441302974</v>
+        <v>0</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -10418,16 +10418,16 @@
         <v>2042</v>
       </c>
       <c r="C123">
-        <v>148649.461842123</v>
+        <v>5.820766091346741E-11</v>
       </c>
       <c r="D123">
-        <v>20810.92465789722</v>
+        <v>0.0001068582860170864</v>
       </c>
       <c r="E123">
-        <v>127838.5371842258</v>
+        <v>-0.0001068582641892135</v>
       </c>
       <c r="F123">
-        <v>61362.49784842839</v>
+        <v>0</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -10438,16 +10438,16 @@
         <v>2043</v>
       </c>
       <c r="C124">
-        <v>136705.6966977289</v>
+        <v>0</v>
       </c>
       <c r="D124">
-        <v>19138.79753768204</v>
+        <v>0.000102980004157871</v>
       </c>
       <c r="E124">
-        <v>117566.8991600468</v>
+        <v>-0.0001029799459502101</v>
       </c>
       <c r="F124">
-        <v>56432.11159682246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -10458,16 +10458,16 @@
         <v>2044</v>
       </c>
       <c r="C125">
-        <v>108797.4824886175</v>
+        <v>0</v>
       </c>
       <c r="D125">
-        <v>15231.64754840644</v>
+        <v>9.14356714929454E-05</v>
       </c>
       <c r="E125">
-        <v>93565.834940211</v>
+        <v>-9.143564966507256E-05</v>
       </c>
       <c r="F125">
-        <v>44911.60077130129</v>
+        <v>0</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -10478,16 +10478,16 @@
         <v>2045</v>
       </c>
       <c r="C126">
-        <v>110861.1837395139</v>
+        <v>0</v>
       </c>
       <c r="D126">
-        <v>15520.56572353194</v>
+        <v>9.36905707931146E-05</v>
       </c>
       <c r="E126">
-        <v>95340.61801598192</v>
+        <v>-9.369055624119937E-05</v>
       </c>
       <c r="F126">
-        <v>45763.49664767133</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -10498,16 +10498,16 @@
         <v>2046</v>
       </c>
       <c r="C127">
-        <v>126409.0995248285</v>
+        <v>0</v>
       </c>
       <c r="D127">
-        <v>17697.27393347599</v>
+        <v>0.0001023259683279321</v>
       </c>
       <c r="E127">
-        <v>108711.8255913525</v>
+        <v>-0.0001023259246721864</v>
       </c>
       <c r="F127">
-        <v>52181.6762838492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -10518,16 +10518,16 @@
         <v>2047</v>
       </c>
       <c r="C128">
-        <v>126203.1055149556</v>
+        <v>5.820766091346741E-11</v>
       </c>
       <c r="D128">
-        <v>17668.43477209378</v>
+        <v>0.0001037185356835835</v>
       </c>
       <c r="E128">
-        <v>108534.6707428618</v>
+        <v>-0.0001037184847518802</v>
       </c>
       <c r="F128">
-        <v>52096.64195657364</v>
+        <v>0</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -10538,16 +10538,16 @@
         <v>2048</v>
       </c>
       <c r="C129">
-        <v>82205.72072290487</v>
+        <v>2.91038304567337E-11</v>
       </c>
       <c r="D129">
-        <v>11508.80090120667</v>
+        <v>8.446633728453889E-05</v>
       </c>
       <c r="E129">
-        <v>70696.91982169813</v>
+        <v>-8.446633000858128E-05</v>
       </c>
       <c r="F129">
-        <v>33934.5215144151</v>
+        <v>0</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -10558,16 +10558,16 @@
         <v>2049</v>
       </c>
       <c r="C130">
-        <v>111474.011187274</v>
+        <v>0</v>
       </c>
       <c r="D130">
-        <v>15606.36156621835</v>
+        <v>9.923153265845031E-05</v>
       </c>
       <c r="E130">
-        <v>95867.64962105564</v>
+        <v>-9.923148900270462E-05</v>
       </c>
       <c r="F130">
-        <v>46016.47181810671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -10578,16 +10578,16 @@
         <v>2050</v>
       </c>
       <c r="C131">
-        <v>104088.6096571369</v>
+        <v>0</v>
       </c>
       <c r="D131">
-        <v>14572.40535199916</v>
+        <v>9.706387936603278E-05</v>
       </c>
       <c r="E131">
-        <v>89516.20430513768</v>
+        <v>-9.706386481411755E-05</v>
       </c>
       <c r="F131">
-        <v>42967.77806646611</v>
+        <v>0</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -10618,16 +10618,16 @@
         <v>2026</v>
       </c>
       <c r="C133">
-        <v>204749.5201218998</v>
+        <v>0</v>
       </c>
       <c r="D133">
-        <v>28664.93281706598</v>
+        <v>9.651455184211954E-05</v>
       </c>
       <c r="E133">
-        <v>176084.5873048338</v>
+        <v>-9.65145300142467E-05</v>
       </c>
       <c r="F133">
-        <v>84520.60190632024</v>
+        <v>0</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -10638,16 +10638,16 @@
         <v>2027</v>
       </c>
       <c r="C134">
-        <v>431715.1283160554</v>
+        <v>0</v>
       </c>
       <c r="D134">
-        <v>60440.11796424776</v>
+        <v>0.0002059141552308574</v>
       </c>
       <c r="E134">
-        <v>371275.0103518076</v>
+        <v>-0.0002059141406789422</v>
       </c>
       <c r="F134">
-        <v>178212.0049688676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -10658,16 +10658,16 @@
         <v>2028</v>
       </c>
       <c r="C135">
-        <v>596064.605230695</v>
+        <v>2.91038304567337E-11</v>
       </c>
       <c r="D135">
-        <v>83449.04473229731</v>
+        <v>0.0002884725254261866</v>
       </c>
       <c r="E135">
-        <v>512615.5604983976</v>
+        <v>-0.0002884724817704409</v>
       </c>
       <c r="F135">
-        <v>246055.4690392308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -10678,16 +10678,16 @@
         <v>2029</v>
       </c>
       <c r="C136">
-        <v>760288.5674440886</v>
+        <v>2.91038304567337E-11</v>
       </c>
       <c r="D136">
-        <v>106440.3994421724</v>
+        <v>0.0003729085001396015</v>
       </c>
       <c r="E136">
-        <v>653848.1680019161</v>
+        <v>-0.0003729084273800254</v>
       </c>
       <c r="F136">
-        <v>313847.1206409198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -10698,16 +10698,16 @@
         <v>2030</v>
       </c>
       <c r="C137">
-        <v>973726.2230666778</v>
+        <v>2.91038304567337E-11</v>
       </c>
       <c r="D137">
-        <v>136321.6712293349</v>
+        <v>0.0004824780480703339</v>
       </c>
       <c r="E137">
-        <v>837404.5518373428</v>
+        <v>-0.0004824779462069273</v>
       </c>
       <c r="F137">
-        <v>401954.1848819246</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -10718,16 +10718,16 @@
         <v>2031</v>
       </c>
       <c r="C138">
-        <v>1161431.426687104</v>
+        <v>2.91038304567337E-11</v>
       </c>
       <c r="D138">
-        <v>162600.3997361946</v>
+        <v>0.0005824331092298962</v>
       </c>
       <c r="E138">
-        <v>998831.0269509093</v>
+        <v>-0.0005824329855386168</v>
       </c>
       <c r="F138">
-        <v>479438.8929364365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -10738,16 +10738,16 @@
         <v>2032</v>
       </c>
       <c r="C139">
-        <v>1383187.166324399</v>
+        <v>2.91038304567337E-11</v>
       </c>
       <c r="D139">
-        <v>193646.2032854159</v>
+        <v>0.0007006508749327622</v>
       </c>
       <c r="E139">
-        <v>1189540.963038984</v>
+        <v>-0.0007006507075857371</v>
       </c>
       <c r="F139">
-        <v>570979.6622587121</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -10758,16 +10758,16 @@
         <v>2033</v>
       </c>
       <c r="C140">
-        <v>1583913.970983885</v>
+        <v>2.91038304567337E-11</v>
       </c>
       <c r="D140">
-        <v>221747.955937744</v>
+        <v>0.0008115693199215457</v>
       </c>
       <c r="E140">
-        <v>1362166.015046142</v>
+        <v>-0.0008115691307466477</v>
       </c>
       <c r="F140">
-        <v>653839.6872221479</v>
+        <v>0</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -10778,16 +10778,16 @@
         <v>2034</v>
       </c>
       <c r="C141">
-        <v>1802746.836471415</v>
+        <v>8.731149137020111E-11</v>
       </c>
       <c r="D141">
-        <v>252384.5571059982</v>
+        <v>0.0009333880443591624</v>
       </c>
       <c r="E141">
-        <v>1550362.279365417</v>
+        <v>-0.0009333878115285188</v>
       </c>
       <c r="F141">
-        <v>744173.8940954002</v>
+        <v>0</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -10798,16 +10798,16 @@
         <v>2035</v>
       </c>
       <c r="C142">
-        <v>1983042.299593146</v>
+        <v>8.731149137020111E-11</v>
       </c>
       <c r="D142">
-        <v>277625.9219430404</v>
+        <v>0.001039619884977583</v>
       </c>
       <c r="E142">
-        <v>1705416.377650105</v>
+        <v>-0.001039619586663321</v>
       </c>
       <c r="F142">
-        <v>818599.8612720506</v>
+        <v>0</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -10818,16 +10818,16 @@
         <v>2036</v>
       </c>
       <c r="C143">
-        <v>2145502.355965784</v>
+        <v>8.731149137020111E-11</v>
       </c>
       <c r="D143">
-        <v>300370.3298352098</v>
+        <v>0.001139569183578715</v>
       </c>
       <c r="E143">
-        <v>1845132.026130574</v>
+        <v>-0.00113956886343658</v>
       </c>
       <c r="F143">
-        <v>885663.3725426757</v>
+        <v>0</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -10838,16 +10838,16 @@
         <v>2037</v>
       </c>
       <c r="C144">
-        <v>2301494.009977623</v>
+        <v>1.455191522836685E-10</v>
       </c>
       <c r="D144">
-        <v>322209.1613968674</v>
+        <v>0.001238383920281194</v>
       </c>
       <c r="E144">
-        <v>1979284.848580756</v>
+        <v>-0.001238383556483313</v>
       </c>
       <c r="F144">
-        <v>950056.727318763</v>
+        <v>0</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -10858,16 +10858,16 @@
         <v>2038</v>
       </c>
       <c r="C145">
-        <v>2491514.946049264</v>
+        <v>1.455191522836685E-10</v>
       </c>
       <c r="D145">
-        <v>348812.092446897</v>
+        <v>0.00135507761297049</v>
       </c>
       <c r="E145">
-        <v>2142702.853602367</v>
+        <v>-0.001355077227344736</v>
       </c>
       <c r="F145">
-        <v>1028497.369729136</v>
+        <v>0</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -10878,16 +10878,16 @@
         <v>2039</v>
       </c>
       <c r="C146">
-        <v>2666135.185990078</v>
+        <v>1.455191522836685E-10</v>
       </c>
       <c r="D146">
-        <v>373258.926038611</v>
+        <v>0.001466751040425152</v>
       </c>
       <c r="E146">
-        <v>2292876.259951467</v>
+        <v>-0.001466750662075356</v>
       </c>
       <c r="F146">
-        <v>1100580.604776704</v>
+        <v>0</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -10898,16 +10898,16 @@
         <v>2040</v>
       </c>
       <c r="C147">
-        <v>2804700.592314193</v>
+        <v>1.455191522836685E-10</v>
       </c>
       <c r="D147">
-        <v>392658.082923987</v>
+        <v>0.001563486795930658</v>
       </c>
       <c r="E147">
-        <v>2412042.509390206</v>
+        <v>-0.001563486410304904</v>
       </c>
       <c r="F147">
-        <v>1157780.404507299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -10918,16 +10918,16 @@
         <v>2041</v>
       </c>
       <c r="C148">
-        <v>2989014.933097426</v>
+        <v>2.037268131971359E-10</v>
       </c>
       <c r="D148">
-        <v>418462.0906336397</v>
+        <v>0.001683420545305125</v>
       </c>
       <c r="E148">
-        <v>2570552.842463786</v>
+        <v>-0.001683420094195753</v>
       </c>
       <c r="F148">
-        <v>1233865.364382617</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -10938,16 +10938,16 @@
         <v>2042</v>
       </c>
       <c r="C149">
-        <v>3121745.224795657</v>
+        <v>2.037268131971359E-10</v>
       </c>
       <c r="D149">
-        <v>437044.331471392</v>
+        <v>0.001781210718036164</v>
       </c>
       <c r="E149">
-        <v>2684700.893324265</v>
+        <v>-0.001781210245098919</v>
       </c>
       <c r="F149">
-        <v>1288656.428795647</v>
+        <v>0</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -10958,16 +10958,16 @@
         <v>2043</v>
       </c>
       <c r="C150">
-        <v>3270394.68663778</v>
+        <v>2.619344741106033E-10</v>
       </c>
       <c r="D150">
-        <v>457855.2561292892</v>
+        <v>0.00188806900405325</v>
       </c>
       <c r="E150">
-        <v>2812539.430508491</v>
+        <v>-0.001888068509288132</v>
       </c>
       <c r="F150">
-        <v>1350018.926644075</v>
+        <v>0</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -10978,16 +10978,16 @@
         <v>2044</v>
       </c>
       <c r="C151">
-        <v>3407100.383335508</v>
+        <v>2.619344741106033E-10</v>
       </c>
       <c r="D151">
-        <v>476994.0536669713</v>
+        <v>0.001991049008211121</v>
       </c>
       <c r="E151">
-        <v>2930106.329668537</v>
+        <v>-0.001991048455238342</v>
       </c>
       <c r="F151">
-        <v>1406451.038240898</v>
+        <v>0</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -10998,16 +10998,16 @@
         <v>2045</v>
       </c>
       <c r="C152">
-        <v>3515897.865824126</v>
+        <v>2.619344741106033E-10</v>
       </c>
       <c r="D152">
-        <v>492225.7012153777</v>
+        <v>0.002082484679704066</v>
       </c>
       <c r="E152">
-        <v>3023672.164608748</v>
+        <v>-0.002082484104903415</v>
       </c>
       <c r="F152">
-        <v>1451362.639012199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -11018,16 +11018,16 @@
         <v>2046</v>
       </c>
       <c r="C153">
-        <v>3626759.04956364</v>
+        <v>2.619344741106033E-10</v>
       </c>
       <c r="D153">
-        <v>507746.2669389097</v>
+        <v>0.002176175250497181</v>
       </c>
       <c r="E153">
-        <v>3119012.78262473</v>
+        <v>-0.002176174661144614</v>
       </c>
       <c r="F153">
-        <v>1497126.13565987</v>
+        <v>0</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -11038,16 +11038,16 @@
         <v>2047</v>
       </c>
       <c r="C154">
-        <v>3753168.149088468</v>
+        <v>2.619344741106033E-10</v>
       </c>
       <c r="D154">
-        <v>525443.5408723856</v>
+        <v>0.002278501218825113</v>
       </c>
       <c r="E154">
-        <v>3227724.608216082</v>
+        <v>-0.002278500585816801</v>
       </c>
       <c r="F154">
-        <v>1549307.81194372</v>
+        <v>0</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -11058,16 +11058,16 @@
         <v>2048</v>
       </c>
       <c r="C155">
-        <v>3879371.254603424</v>
+        <v>3.201421350240707E-10</v>
       </c>
       <c r="D155">
-        <v>543111.9756444794</v>
+        <v>0.002382219754508696</v>
       </c>
       <c r="E155">
-        <v>3336259.278958944</v>
+        <v>-0.002382219070568681</v>
       </c>
       <c r="F155">
-        <v>1601404.453900293</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -11078,16 +11078,16 @@
         <v>2049</v>
       </c>
       <c r="C156">
-        <v>3961576.975326329</v>
+        <v>3.492459654808044E-10</v>
       </c>
       <c r="D156">
-        <v>554620.7765456861</v>
+        <v>0.002466686091793235</v>
       </c>
       <c r="E156">
-        <v>3406956.198780642</v>
+        <v>-0.002466685400577262</v>
       </c>
       <c r="F156">
-        <v>1635338.975414708</v>
+        <v>0</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -11098,16 +11098,16 @@
         <v>2050</v>
       </c>
       <c r="C157">
-        <v>4073050.986513603</v>
+        <v>3.492459654808044E-10</v>
       </c>
       <c r="D157">
-        <v>570227.1381119044</v>
+        <v>0.002565917624451686</v>
       </c>
       <c r="E157">
-        <v>3502823.848401698</v>
+        <v>-0.002565916889579967</v>
       </c>
       <c r="F157">
-        <v>1681355.447232815</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/biodym_mfa_tool/data/02_output/results_scientific.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific.xlsx
@@ -6928,16 +6928,16 @@
         <v>2025</v>
       </c>
       <c r="C314">
-        <v>115956.3752316096</v>
+        <v>0</v>
       </c>
       <c r="D314">
         <v>0</v>
       </c>
       <c r="E314">
-        <v>115956.3752316096</v>
+        <v>0</v>
       </c>
       <c r="F314">
-        <v>115956.3752316096</v>
+        <v>0</v>
       </c>
     </row>
     <row r="315" spans="1:6">
@@ -6948,16 +6948,16 @@
         <v>2026</v>
       </c>
       <c r="C315">
-        <v>131436.9846483817</v>
+        <v>0</v>
       </c>
       <c r="D315">
         <v>0</v>
       </c>
       <c r="E315">
-        <v>131436.9846483817</v>
+        <v>0</v>
       </c>
       <c r="F315">
-        <v>131436.9846483817</v>
+        <v>0</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -6968,16 +6968,16 @@
         <v>2027</v>
       </c>
       <c r="C316">
-        <v>99188.86568059392</v>
+        <v>0</v>
       </c>
       <c r="D316">
         <v>0</v>
       </c>
       <c r="E316">
-        <v>99188.86568059392</v>
+        <v>0</v>
       </c>
       <c r="F316">
-        <v>99188.86568059392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -6988,16 +6988,16 @@
         <v>2028</v>
       </c>
       <c r="C317">
-        <v>101444.6951950469</v>
+        <v>0</v>
       </c>
       <c r="D317">
         <v>0</v>
       </c>
       <c r="E317">
-        <v>101444.6951950469</v>
+        <v>0</v>
       </c>
       <c r="F317">
-        <v>101444.6951950469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -7008,16 +7008,16 @@
         <v>2029</v>
       </c>
       <c r="C318">
-        <v>131641.1610056631</v>
+        <v>0</v>
       </c>
       <c r="D318">
         <v>0</v>
       </c>
       <c r="E318">
-        <v>131641.1610056631</v>
+        <v>0</v>
       </c>
       <c r="F318">
-        <v>131641.1610056631</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -7028,16 +7028,16 @@
         <v>2030</v>
       </c>
       <c r="C319">
-        <v>120089.9474229112</v>
+        <v>0</v>
       </c>
       <c r="D319">
         <v>0</v>
       </c>
       <c r="E319">
-        <v>120089.9474229112</v>
+        <v>0</v>
       </c>
       <c r="F319">
-        <v>120089.9474229112</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -7048,16 +7048,16 @@
         <v>2031</v>
       </c>
       <c r="C320">
-        <v>142031.4743389855</v>
+        <v>0</v>
       </c>
       <c r="D320">
         <v>0</v>
       </c>
       <c r="E320">
-        <v>142031.4743389855</v>
+        <v>0</v>
       </c>
       <c r="F320">
-        <v>142031.4743389855</v>
+        <v>0</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -7068,16 +7068,16 @@
         <v>2032</v>
       </c>
       <c r="C321">
-        <v>133261.7869665299</v>
+        <v>0</v>
       </c>
       <c r="D321">
         <v>0</v>
       </c>
       <c r="E321">
-        <v>133261.7869665299</v>
+        <v>0</v>
       </c>
       <c r="F321">
-        <v>133261.7869665299</v>
+        <v>0</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -7088,16 +7088,16 @@
         <v>2033</v>
       </c>
       <c r="C322">
-        <v>146357.798125677</v>
+        <v>0</v>
       </c>
       <c r="D322">
         <v>0</v>
       </c>
       <c r="E322">
-        <v>146357.798125677</v>
+        <v>0</v>
       </c>
       <c r="F322">
-        <v>146357.798125677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -7108,16 +7108,16 @@
         <v>2034</v>
       </c>
       <c r="C323">
-        <v>127631.1078735566</v>
+        <v>0</v>
       </c>
       <c r="D323">
         <v>0</v>
       </c>
       <c r="E323">
-        <v>127631.1078735566</v>
+        <v>0</v>
       </c>
       <c r="F323">
-        <v>127631.1078735566</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -7128,16 +7128,16 @@
         <v>2035</v>
       </c>
       <c r="C324">
-        <v>120083.0124878945</v>
+        <v>0</v>
       </c>
       <c r="D324">
         <v>0</v>
       </c>
       <c r="E324">
-        <v>120083.0124878945</v>
+        <v>0</v>
       </c>
       <c r="F324">
-        <v>120083.0124878945</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -7148,16 +7148,16 @@
         <v>2036</v>
       </c>
       <c r="C325">
-        <v>118719.9054598083</v>
+        <v>0</v>
       </c>
       <c r="D325">
         <v>0</v>
       </c>
       <c r="E325">
-        <v>118719.9054598083</v>
+        <v>0</v>
       </c>
       <c r="F325">
-        <v>118719.9054598083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -7168,16 +7168,16 @@
         <v>2037</v>
       </c>
       <c r="C326">
-        <v>140200.3849545098</v>
+        <v>0</v>
       </c>
       <c r="D326">
         <v>0</v>
       </c>
       <c r="E326">
-        <v>140200.3849545098</v>
+        <v>0</v>
       </c>
       <c r="F326">
-        <v>140200.3849545098</v>
+        <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -7188,16 +7188,16 @@
         <v>2038</v>
       </c>
       <c r="C327">
-        <v>134168.8424897742</v>
+        <v>0</v>
       </c>
       <c r="D327">
         <v>0</v>
       </c>
       <c r="E327">
-        <v>134168.8424897742</v>
+        <v>0</v>
       </c>
       <c r="F327">
-        <v>134168.8424897742</v>
+        <v>0</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -7208,16 +7208,16 @@
         <v>2039</v>
       </c>
       <c r="C328">
-        <v>116222.1358897134</v>
+        <v>0</v>
       </c>
       <c r="D328">
         <v>0</v>
       </c>
       <c r="E328">
-        <v>116222.1358897134</v>
+        <v>0</v>
       </c>
       <c r="F328">
-        <v>116222.1358897134</v>
+        <v>0</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -7228,16 +7228,16 @@
         <v>2040</v>
       </c>
       <c r="C329">
-        <v>144093.1128934026</v>
+        <v>0</v>
       </c>
       <c r="D329">
         <v>0</v>
       </c>
       <c r="E329">
-        <v>144093.1128934026</v>
+        <v>0</v>
       </c>
       <c r="F329">
-        <v>144093.1128934026</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -7248,16 +7248,16 @@
         <v>2041</v>
       </c>
       <c r="C330">
-        <v>117488.9539341407</v>
+        <v>0</v>
       </c>
       <c r="D330">
         <v>0</v>
       </c>
       <c r="E330">
-        <v>117488.9539341407</v>
+        <v>0</v>
       </c>
       <c r="F330">
-        <v>117488.9539341407</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -7268,16 +7268,16 @@
         <v>2042</v>
       </c>
       <c r="C331">
-        <v>128383.7406617088</v>
+        <v>0</v>
       </c>
       <c r="D331">
         <v>0</v>
       </c>
       <c r="E331">
-        <v>128383.7406617088</v>
+        <v>0</v>
       </c>
       <c r="F331">
-        <v>128383.7406617088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -7288,16 +7288,16 @@
         <v>2043</v>
       </c>
       <c r="C332">
-        <v>123724.2211043001</v>
+        <v>0</v>
       </c>
       <c r="D332">
         <v>0</v>
       </c>
       <c r="E332">
-        <v>123724.2211043001</v>
+        <v>0</v>
       </c>
       <c r="F332">
-        <v>123724.2211043001</v>
+        <v>0</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -7308,16 +7308,16 @@
         <v>2044</v>
       </c>
       <c r="C333">
-        <v>109854.4062660498</v>
+        <v>0</v>
       </c>
       <c r="D333">
         <v>0</v>
       </c>
       <c r="E333">
-        <v>109854.4062660498</v>
+        <v>0</v>
       </c>
       <c r="F333">
-        <v>109854.4062660498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -7328,16 +7328,16 @@
         <v>2045</v>
       </c>
       <c r="C334">
-        <v>112563.5376910088</v>
+        <v>0</v>
       </c>
       <c r="D334">
         <v>0</v>
       </c>
       <c r="E334">
-        <v>112563.5376910088</v>
+        <v>0</v>
       </c>
       <c r="F334">
-        <v>112563.5376910088</v>
+        <v>0</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -7348,16 +7348,16 @@
         <v>2046</v>
       </c>
       <c r="C335">
-        <v>122938.4410417697</v>
+        <v>0</v>
       </c>
       <c r="D335">
         <v>0</v>
       </c>
       <c r="E335">
-        <v>122938.4410417697</v>
+        <v>0</v>
       </c>
       <c r="F335">
-        <v>122938.4410417697</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -7368,16 +7368,16 @@
         <v>2047</v>
       </c>
       <c r="C336">
-        <v>124611.5204488498</v>
+        <v>0</v>
       </c>
       <c r="D336">
         <v>0</v>
       </c>
       <c r="E336">
-        <v>124611.5204488498</v>
+        <v>0</v>
       </c>
       <c r="F336">
-        <v>124611.5204488498</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -7388,16 +7388,16 @@
         <v>2048</v>
       </c>
       <c r="C337">
-        <v>101481.1810425606</v>
+        <v>0</v>
       </c>
       <c r="D337">
         <v>0</v>
       </c>
       <c r="E337">
-        <v>101481.1810425606</v>
+        <v>0</v>
       </c>
       <c r="F337">
-        <v>101481.1810425606</v>
+        <v>0</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -7408,16 +7408,16 @@
         <v>2049</v>
       </c>
       <c r="C338">
-        <v>119220.669781142</v>
+        <v>0</v>
       </c>
       <c r="D338">
         <v>0</v>
       </c>
       <c r="E338">
-        <v>119220.669781142</v>
+        <v>0</v>
       </c>
       <c r="F338">
-        <v>119220.669781142</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -7428,16 +7428,16 @@
         <v>2050</v>
       </c>
       <c r="C339">
-        <v>116616.3592362279</v>
+        <v>0</v>
       </c>
       <c r="D339">
         <v>0</v>
       </c>
       <c r="E339">
-        <v>116616.3592362279</v>
+        <v>0</v>
       </c>
       <c r="F339">
-        <v>116616.3592362279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -7448,13 +7448,13 @@
         <v>2025</v>
       </c>
       <c r="C340">
-        <v>164945.6965503904</v>
+        <v>0</v>
       </c>
       <c r="D340">
-        <v>39326.28995296545</v>
+        <v>0</v>
       </c>
       <c r="E340">
-        <v>125619.4065974249</v>
+        <v>0</v>
       </c>
       <c r="F340">
         <v>0</v>
@@ -7468,13 +7468,13 @@
         <v>2026</v>
       </c>
       <c r="C341">
-        <v>186966.5634339383</v>
+        <v>0</v>
       </c>
       <c r="D341">
-        <v>44576.4966221252</v>
+        <v>0</v>
       </c>
       <c r="E341">
-        <v>142390.0668118131</v>
+        <v>0</v>
       </c>
       <c r="F341">
         <v>0</v>
@@ -7488,13 +7488,13 @@
         <v>2027</v>
       </c>
       <c r="C342">
-        <v>141094.2391658061</v>
+        <v>0</v>
       </c>
       <c r="D342">
-        <v>33639.63459593763</v>
+        <v>0</v>
       </c>
       <c r="E342">
-        <v>107454.6045698684</v>
+        <v>0</v>
       </c>
       <c r="F342">
         <v>0</v>
@@ -7508,13 +7508,13 @@
         <v>2028</v>
       </c>
       <c r="C343">
-        <v>144303.1129324891</v>
+        <v>0</v>
       </c>
       <c r="D343">
-        <v>34404.69305341908</v>
+        <v>0</v>
       </c>
       <c r="E343">
-        <v>109898.4198790701</v>
+        <v>0</v>
       </c>
       <c r="F343">
         <v>0</v>
@@ -7528,13 +7528,13 @@
         <v>2029</v>
       </c>
       <c r="C344">
-        <v>187257.0003452649</v>
+        <v>0</v>
       </c>
       <c r="D344">
-        <v>44645.74247956038</v>
+        <v>0</v>
       </c>
       <c r="E344">
-        <v>142611.2578657045</v>
+        <v>0</v>
       </c>
       <c r="F344">
         <v>0</v>
@@ -7548,13 +7548,13 @@
         <v>2030</v>
       </c>
       <c r="C345">
-        <v>170825.6228845288</v>
+        <v>0</v>
       </c>
       <c r="D345">
-        <v>40728.17974308654</v>
+        <v>0</v>
       </c>
       <c r="E345">
-        <v>130097.4431414422</v>
+        <v>0</v>
       </c>
       <c r="F345">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>2031</v>
       </c>
       <c r="C346">
-        <v>202037.0196992545</v>
+        <v>0</v>
       </c>
       <c r="D346">
-        <v>48169.58904713584</v>
+        <v>0</v>
       </c>
       <c r="E346">
-        <v>153867.4306521187</v>
+        <v>0</v>
       </c>
       <c r="F346">
         <v>0</v>
@@ -7588,13 +7588,13 @@
         <v>2032</v>
       </c>
       <c r="C347">
-        <v>189562.3093671181</v>
+        <v>0</v>
       </c>
       <c r="D347">
-        <v>45195.37337579228</v>
+        <v>0</v>
       </c>
       <c r="E347">
-        <v>144366.9359913258</v>
+        <v>0</v>
       </c>
       <c r="F347">
         <v>0</v>
@@ -7608,13 +7608,13 @@
         <v>2033</v>
       </c>
       <c r="C348">
-        <v>208191.131442339</v>
+        <v>0</v>
       </c>
       <c r="D348">
-        <v>49636.85001770352</v>
+        <v>0</v>
       </c>
       <c r="E348">
-        <v>158554.2814246354</v>
+        <v>0</v>
       </c>
       <c r="F348">
         <v>0</v>
@@ -7628,13 +7628,13 @@
         <v>2034</v>
       </c>
       <c r="C349">
-        <v>181552.7774790514</v>
+        <v>0</v>
       </c>
       <c r="D349">
-        <v>43285.74384313329</v>
+        <v>0</v>
       </c>
       <c r="E349">
-        <v>138267.0336359181</v>
+        <v>0</v>
       </c>
       <c r="F349">
         <v>0</v>
@@ -7648,13 +7648,13 @@
         <v>2035</v>
       </c>
       <c r="C350">
-        <v>170815.7580738655</v>
+        <v>0</v>
       </c>
       <c r="D350">
-        <v>40725.82777869711</v>
+        <v>0</v>
       </c>
       <c r="E350">
-        <v>130089.9302951683</v>
+        <v>0</v>
       </c>
       <c r="F350">
         <v>0</v>
@@ -7668,13 +7668,13 @@
         <v>2036</v>
       </c>
       <c r="C351">
-        <v>168876.7647432157</v>
+        <v>0</v>
       </c>
       <c r="D351">
-        <v>40263.53372960863</v>
+        <v>0</v>
       </c>
       <c r="E351">
-        <v>128613.231013607</v>
+        <v>0</v>
       </c>
       <c r="F351">
         <v>0</v>
@@ -7688,13 +7688,13 @@
         <v>2037</v>
       </c>
       <c r="C352">
-        <v>199432.3305360662</v>
+        <v>0</v>
       </c>
       <c r="D352">
-        <v>47548.58005198695</v>
+        <v>0</v>
       </c>
       <c r="E352">
-        <v>151883.7504840792</v>
+        <v>0</v>
       </c>
       <c r="F352">
         <v>0</v>
@@ -7708,13 +7708,13 @@
         <v>2038</v>
       </c>
       <c r="C353">
-        <v>190852.5782703377</v>
+        <v>0</v>
       </c>
       <c r="D353">
-        <v>45502.99879474226</v>
+        <v>0</v>
       </c>
       <c r="E353">
-        <v>145349.5794755955</v>
+        <v>0</v>
       </c>
       <c r="F353">
         <v>0</v>
@@ -7728,13 +7728,13 @@
         <v>2039</v>
       </c>
       <c r="C354">
-        <v>165323.7359361426</v>
+        <v>0</v>
       </c>
       <c r="D354">
-        <v>39416.42195888409</v>
+        <v>0</v>
       </c>
       <c r="E354">
-        <v>125907.3139772585</v>
+        <v>0</v>
       </c>
       <c r="F354">
         <v>0</v>
@@ -7748,13 +7748,13 @@
         <v>2040</v>
       </c>
       <c r="C355">
-        <v>204969.6605886774</v>
+        <v>0</v>
       </c>
       <c r="D355">
-        <v>48868.78816755746</v>
+        <v>0</v>
       </c>
       <c r="E355">
-        <v>156100.8724211199</v>
+        <v>0</v>
       </c>
       <c r="F355">
         <v>0</v>
@@ -7768,13 +7768,13 @@
         <v>2041</v>
       </c>
       <c r="C356">
-        <v>167125.7600536033</v>
+        <v>0</v>
       </c>
       <c r="D356">
-        <v>39846.059860494</v>
+        <v>0</v>
       </c>
       <c r="E356">
-        <v>127279.7001931093</v>
+        <v>0</v>
       </c>
       <c r="F356">
         <v>0</v>
@@ -7788,13 +7788,13 @@
         <v>2042</v>
       </c>
       <c r="C357">
-        <v>182623.3830342912</v>
+        <v>0</v>
       </c>
       <c r="D357">
-        <v>43540.99721058172</v>
+        <v>0</v>
       </c>
       <c r="E357">
-        <v>139082.3858237095</v>
+        <v>0</v>
       </c>
       <c r="F357">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>2043</v>
       </c>
       <c r="C358">
-        <v>175995.3067646439</v>
+        <v>0</v>
       </c>
       <c r="D358">
-        <v>41960.73379867217</v>
+        <v>0</v>
       </c>
       <c r="E358">
-        <v>134034.5729659717</v>
+        <v>0</v>
       </c>
       <c r="F358">
         <v>0</v>
@@ -7828,13 +7828,13 @@
         <v>2044</v>
       </c>
       <c r="C359">
-        <v>156265.7639520942</v>
+        <v>0</v>
       </c>
       <c r="D359">
-        <v>37256.8237391045</v>
+        <v>0</v>
       </c>
       <c r="E359">
-        <v>119008.9402129896</v>
+        <v>0</v>
       </c>
       <c r="F359">
         <v>0</v>
@@ -7848,13 +7848,13 @@
         <v>2045</v>
       </c>
       <c r="C360">
-        <v>160119.4509015513</v>
+        <v>0</v>
       </c>
       <c r="D360">
-        <v>38175.61830926784</v>
+        <v>0</v>
       </c>
       <c r="E360">
-        <v>121943.8325922834</v>
+        <v>0</v>
       </c>
       <c r="F360">
         <v>0</v>
@@ -7868,13 +7868,13 @@
         <v>2046</v>
       </c>
       <c r="C361">
-        <v>174877.5498539903</v>
+        <v>0</v>
       </c>
       <c r="D361">
-        <v>41694.23862308044</v>
+        <v>0</v>
       </c>
       <c r="E361">
-        <v>133183.3112309098</v>
+        <v>0</v>
       </c>
       <c r="F361">
         <v>0</v>
@@ -7888,13 +7888,13 @@
         <v>2047</v>
       </c>
       <c r="C362">
-        <v>177257.4728865422</v>
+        <v>0</v>
       </c>
       <c r="D362">
-        <v>42261.65896323635</v>
+        <v>0</v>
       </c>
       <c r="E362">
-        <v>134995.8139233058</v>
+        <v>0</v>
       </c>
       <c r="F362">
         <v>0</v>
@@ -7908,13 +7908,13 @@
         <v>2048</v>
       </c>
       <c r="C363">
-        <v>144355.0133434874</v>
+        <v>0</v>
       </c>
       <c r="D363">
-        <v>34417.06712958039</v>
+        <v>0</v>
       </c>
       <c r="E363">
-        <v>109937.946213907</v>
+        <v>0</v>
       </c>
       <c r="F363">
         <v>0</v>
@@ -7928,13 +7928,13 @@
         <v>2049</v>
       </c>
       <c r="C364">
-        <v>169589.092285578</v>
+        <v>0</v>
       </c>
       <c r="D364">
-        <v>40433.36659010927</v>
+        <v>0</v>
       </c>
       <c r="E364">
-        <v>129155.7256954687</v>
+        <v>0</v>
       </c>
       <c r="F364">
         <v>0</v>
@@ -7948,13 +7948,13 @@
         <v>2050</v>
       </c>
       <c r="C365">
-        <v>165884.5110065722</v>
+        <v>0</v>
       </c>
       <c r="D365">
-        <v>39550.12173692813</v>
+        <v>0</v>
       </c>
       <c r="E365">
-        <v>126334.389269644</v>
+        <v>0</v>
       </c>
       <c r="F365">
         <v>0</v>
@@ -7998,16 +7998,16 @@
         <v>2025</v>
       </c>
       <c r="C2">
-        <v>0.001040000002831221</v>
+        <v>-115956.3741916096</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.001040000002831221</v>
+        <v>-115956.3741916096</v>
       </c>
       <c r="F2">
-        <v>0.001040000002831221</v>
+        <v>-115956.3741916096</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -8018,16 +8018,16 @@
         <v>2026</v>
       </c>
       <c r="C3">
-        <v>-0.003280000004451722</v>
+        <v>-131436.9879283817</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-0.003280000004451722</v>
+        <v>-131436.9879283817</v>
       </c>
       <c r="F3">
-        <v>-0.003280000004451722</v>
+        <v>-131436.9879283817</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8038,16 +8038,16 @@
         <v>2027</v>
       </c>
       <c r="C4">
-        <v>-0.002799999987473711</v>
+        <v>-99188.8684805939</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>-0.002799999987473711</v>
+        <v>-99188.8684805939</v>
       </c>
       <c r="F4">
-        <v>-0.002799999987473711</v>
+        <v>-99188.8684805939</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8058,16 +8058,16 @@
         <v>2028</v>
       </c>
       <c r="C5">
-        <v>-4.799995804205537E-05</v>
+        <v>-101444.6952430469</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-4.799995804205537E-05</v>
+        <v>-101444.6952430469</v>
       </c>
       <c r="F5">
-        <v>-4.799995804205537E-05</v>
+        <v>-101444.6952430469</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8078,16 +8078,16 @@
         <v>2029</v>
       </c>
       <c r="C6">
-        <v>-0.0001279999851249158</v>
+        <v>-131641.1611336631</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>-0.0001279999851249158</v>
+        <v>-131641.1611336631</v>
       </c>
       <c r="F6">
-        <v>-0.0001279999851249158</v>
+        <v>-131641.1611336631</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8098,16 +8098,16 @@
         <v>2030</v>
       </c>
       <c r="C7">
-        <v>0.002367999986745417</v>
+        <v>-120089.9450549113</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>0.002367999986745417</v>
+        <v>-120089.9450549113</v>
       </c>
       <c r="F7">
-        <v>0.002367999986745417</v>
+        <v>-120089.9450549113</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8118,16 +8118,16 @@
         <v>2031</v>
       </c>
       <c r="C8">
-        <v>-0.00015999999595806</v>
+        <v>-142031.4744989855</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-0.00015999999595806</v>
+        <v>-142031.4744989855</v>
       </c>
       <c r="F8">
-        <v>-0.00015999999595806</v>
+        <v>-142031.4744989855</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8138,16 +8138,16 @@
         <v>2032</v>
       </c>
       <c r="C9">
-        <v>0.0001439999905414879</v>
+        <v>-133261.7868225299</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>0.0001439999905414879</v>
+        <v>-133261.7868225299</v>
       </c>
       <c r="F9">
-        <v>0.0001439999905414879</v>
+        <v>-133261.7868225299</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8158,16 +8158,16 @@
         <v>2033</v>
       </c>
       <c r="C10">
-        <v>0.002991999965161085</v>
+        <v>-146357.795133677</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>0.002991999965161085</v>
+        <v>-146357.795133677</v>
       </c>
       <c r="F10">
-        <v>0.002991999965161085</v>
+        <v>-146357.795133677</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8178,16 +8178,16 @@
         <v>2034</v>
       </c>
       <c r="C11">
-        <v>0.0007520000217482448</v>
+        <v>-127631.1071215566</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0.0007520000217482448</v>
+        <v>-127631.1071215566</v>
       </c>
       <c r="F11">
-        <v>0.0007520000217482448</v>
+        <v>-127631.1071215566</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8198,16 +8198,16 @@
         <v>2035</v>
       </c>
       <c r="C12">
-        <v>0.002015999983996153</v>
+        <v>-120083.0104718946</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>0.002015999983996153</v>
+        <v>-120083.0104718946</v>
       </c>
       <c r="F12">
-        <v>0.002015999983996153</v>
+        <v>-120083.0104718946</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8218,16 +8218,16 @@
         <v>2036</v>
       </c>
       <c r="C13">
-        <v>0.000463999982457608</v>
+        <v>-118719.9049958083</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>0.000463999982457608</v>
+        <v>-118719.9049958083</v>
       </c>
       <c r="F13">
-        <v>0.000463999982457608</v>
+        <v>-118719.9049958083</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8238,16 +8238,16 @@
         <v>2037</v>
       </c>
       <c r="C14">
-        <v>0.003407999989576638</v>
+        <v>-140200.3815465098</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>0.003407999989576638</v>
+        <v>-140200.3815465098</v>
       </c>
       <c r="F14">
-        <v>0.003407999989576638</v>
+        <v>-140200.3815465098</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -8258,16 +8258,16 @@
         <v>2038</v>
       </c>
       <c r="C15">
-        <v>-0.0004960000514984131</v>
+        <v>-134168.8429857742</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-0.0004960000514984131</v>
+        <v>-134168.8429857742</v>
       </c>
       <c r="F15">
-        <v>-0.0004960000514984131</v>
+        <v>-134168.8429857742</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -8278,16 +8278,16 @@
         <v>2039</v>
       </c>
       <c r="C16">
-        <v>0.000784000032581389</v>
+        <v>-116222.1351057133</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>0.000784000032581389</v>
+        <v>-116222.1351057133</v>
       </c>
       <c r="F16">
-        <v>0.000784000032581389</v>
+        <v>-116222.1351057133</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -8298,16 +8298,16 @@
         <v>2040</v>
       </c>
       <c r="C17">
-        <v>0.0006719999946653843</v>
+        <v>-144093.1122214027</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>0.0006719999946653843</v>
+        <v>-144093.1122214027</v>
       </c>
       <c r="F17">
-        <v>0.0006719999946653843</v>
+        <v>-144093.1122214027</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -8318,16 +8318,16 @@
         <v>2041</v>
       </c>
       <c r="C18">
-        <v>-0.0007359999581240118</v>
+        <v>-117488.9546701407</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-0.0007359999581240118</v>
+        <v>-117488.9546701407</v>
       </c>
       <c r="F18">
-        <v>-0.0007359999581240118</v>
+        <v>-117488.9546701407</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -8338,16 +8338,16 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>-0.001999999978579581</v>
+        <v>-128383.7426617088</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-0.001999999978579581</v>
+        <v>-128383.7426617088</v>
       </c>
       <c r="F19">
-        <v>-0.001999999978579581</v>
+        <v>-128383.7426617088</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -8358,16 +8358,16 @@
         <v>2043</v>
       </c>
       <c r="C20">
-        <v>-0.002431999950204045</v>
+        <v>-123724.2235363001</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-0.002431999950204045</v>
+        <v>-123724.2235363001</v>
       </c>
       <c r="F20">
-        <v>-0.002431999950204045</v>
+        <v>-123724.2235363001</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -8378,16 +8378,16 @@
         <v>2044</v>
       </c>
       <c r="C21">
-        <v>-0.001103999966289848</v>
+        <v>-109854.4073700498</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.001103999966289848</v>
+        <v>-109854.4073700498</v>
       </c>
       <c r="F21">
-        <v>-0.001103999966289848</v>
+        <v>-109854.4073700498</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -8398,16 +8398,16 @@
         <v>2045</v>
       </c>
       <c r="C22">
-        <v>-0.002831999969203025</v>
+        <v>-112563.5405230088</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>-0.002831999969203025</v>
+        <v>-112563.5405230088</v>
       </c>
       <c r="F22">
-        <v>-0.002831999969203025</v>
+        <v>-112563.5405230088</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -8418,16 +8418,16 @@
         <v>2046</v>
       </c>
       <c r="C23">
-        <v>-0.0002399999648332596</v>
+        <v>-122938.4412817697</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>-0.0002399999648332596</v>
+        <v>-122938.4412817697</v>
       </c>
       <c r="F23">
-        <v>-0.0002399999648332596</v>
+        <v>-122938.4412817697</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -8438,16 +8438,16 @@
         <v>2047</v>
       </c>
       <c r="C24">
-        <v>-0.0001439999905414879</v>
+        <v>-124611.5205928498</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>-0.0001439999905414879</v>
+        <v>-124611.5205928498</v>
       </c>
       <c r="F24">
-        <v>-0.0001439999905414879</v>
+        <v>-124611.5205928498</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -8458,16 +8458,16 @@
         <v>2048</v>
       </c>
       <c r="C25">
-        <v>-0.002703999984078109</v>
+        <v>-101481.1837465606</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-0.002703999984078109</v>
+        <v>-101481.1837465606</v>
       </c>
       <c r="F25">
-        <v>-0.002703999984078109</v>
+        <v>-101481.1837465606</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -8478,16 +8478,16 @@
         <v>2049</v>
       </c>
       <c r="C26">
-        <v>0.0008800000068731606</v>
+        <v>-119220.668901142</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>0.0008800000068731606</v>
+        <v>-119220.668901142</v>
       </c>
       <c r="F26">
-        <v>0.0008800000068731606</v>
+        <v>-119220.668901142</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -8498,16 +8498,16 @@
         <v>2050</v>
       </c>
       <c r="C27">
-        <v>0.0006240000366233289</v>
+        <v>-116616.3586122278</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>0.0006240000366233289</v>
+        <v>-116616.3586122278</v>
       </c>
       <c r="F27">
-        <v>0.0006240000366233289</v>
+        <v>-116616.3586122278</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -8538,16 +8538,16 @@
         <v>2026</v>
       </c>
       <c r="C29">
-        <v>0.001040000002831221</v>
+        <v>-115956.3741916096</v>
       </c>
       <c r="D29">
         <v>0</v>
       </c>
       <c r="E29">
-        <v>0.001040000002831221</v>
+        <v>-115956.3741916096</v>
       </c>
       <c r="F29">
-        <v>0.001040000002831221</v>
+        <v>-115956.3741916096</v>
       </c>
     </row>
     <row r="30" spans="1:6">
@@ -8558,16 +8558,16 @@
         <v>2027</v>
       </c>
       <c r="C30">
-        <v>-0.002240000001620501</v>
+        <v>-247393.3621199913</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>-0.002240000001620501</v>
+        <v>-247393.3621199913</v>
       </c>
       <c r="F30">
-        <v>-0.002240000001620501</v>
+        <v>-247393.3621199913</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -8578,16 +8578,16 @@
         <v>2028</v>
       </c>
       <c r="C31">
-        <v>-0.005039999989094213</v>
+        <v>-346582.2306005852</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>-0.005039999989094213</v>
+        <v>-346582.2306005852</v>
       </c>
       <c r="F31">
-        <v>-0.005039999989094213</v>
+        <v>-346582.2306005852</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -8598,16 +8598,16 @@
         <v>2029</v>
       </c>
       <c r="C32">
-        <v>-0.005087999947136268</v>
+        <v>-448026.9258436321</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>-0.005087999947136268</v>
+        <v>-448026.9258436321</v>
       </c>
       <c r="F32">
-        <v>-0.005087999947136268</v>
+        <v>-448026.9258436321</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -8618,16 +8618,16 @@
         <v>2030</v>
       </c>
       <c r="C33">
-        <v>-0.005215999932261184</v>
+        <v>-579668.0869772951</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>-0.005215999932261184</v>
+        <v>-579668.0869772951</v>
       </c>
       <c r="F33">
-        <v>-0.005215999932261184</v>
+        <v>-579668.0869772951</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -8638,16 +8638,16 @@
         <v>2031</v>
       </c>
       <c r="C34">
-        <v>-0.002847999945515767</v>
+        <v>-699758.0320322064</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>-0.002847999945515767</v>
+        <v>-699758.0320322064</v>
       </c>
       <c r="F34">
-        <v>-0.002847999945515767</v>
+        <v>-699758.0320322064</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -8658,16 +8658,16 @@
         <v>2032</v>
       </c>
       <c r="C35">
-        <v>-0.003007999941473827</v>
+        <v>-841789.5065311919</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>-0.003007999941473827</v>
+        <v>-841789.5065311919</v>
       </c>
       <c r="F35">
-        <v>-0.003007999941473827</v>
+        <v>-841789.5065311919</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -8678,16 +8678,16 @@
         <v>2033</v>
       </c>
       <c r="C36">
-        <v>-0.002863999950932339</v>
+        <v>-975051.2933537217</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>-0.002863999950932339</v>
+        <v>-975051.2933537217</v>
       </c>
       <c r="F36">
-        <v>-0.002863999950932339</v>
+        <v>-975051.2933537217</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -8698,16 +8698,16 @@
         <v>2034</v>
       </c>
       <c r="C37">
-        <v>0.0001280000142287463</v>
+        <v>-1121409.088487399</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>0.0001280000142287463</v>
+        <v>-1121409.088487399</v>
       </c>
       <c r="F37">
-        <v>0.0001280000142287463</v>
+        <v>-1121409.088487399</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -8718,16 +8718,16 @@
         <v>2035</v>
       </c>
       <c r="C38">
-        <v>0.0008800000359769911</v>
+        <v>-1249040.195608955</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>0.0008800000359769911</v>
+        <v>-1249040.195608955</v>
       </c>
       <c r="F38">
-        <v>0.0008800000359769911</v>
+        <v>-1249040.195608955</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -8738,16 +8738,16 @@
         <v>2036</v>
       </c>
       <c r="C39">
-        <v>0.002896000019973144</v>
+        <v>-1369123.20608085</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>0.002896000019973144</v>
+        <v>-1369123.20608085</v>
       </c>
       <c r="F39">
-        <v>0.002896000019973144</v>
+        <v>-1369123.20608085</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -8758,16 +8758,16 @@
         <v>2037</v>
       </c>
       <c r="C40">
-        <v>0.003360000002430752</v>
+        <v>-1487843.111076658</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>0.003360000002430752</v>
+        <v>-1487843.111076658</v>
       </c>
       <c r="F40">
-        <v>0.003360000002430752</v>
+        <v>-1487843.111076658</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -8778,16 +8778,16 @@
         <v>2038</v>
       </c>
       <c r="C41">
-        <v>0.00676799999200739</v>
+        <v>-1628043.492623168</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>0.00676799999200739</v>
+        <v>-1628043.492623168</v>
       </c>
       <c r="F41">
-        <v>0.00676799999200739</v>
+        <v>-1628043.492623168</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -8798,16 +8798,16 @@
         <v>2039</v>
       </c>
       <c r="C42">
-        <v>0.006271999940508977</v>
+        <v>-1762212.335608942</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>0.006271999940508977</v>
+        <v>-1762212.335608942</v>
       </c>
       <c r="F42">
-        <v>0.006271999940508977</v>
+        <v>-1762212.335608942</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -8818,16 +8818,16 @@
         <v>2040</v>
       </c>
       <c r="C43">
-        <v>0.007055999973090366</v>
+        <v>-1878434.470714655</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>0.007055999973090366</v>
+        <v>-1878434.470714655</v>
       </c>
       <c r="F43">
-        <v>0.007055999973090366</v>
+        <v>-1878434.470714655</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -8838,16 +8838,16 @@
         <v>2041</v>
       </c>
       <c r="C44">
-        <v>0.00772799996775575</v>
+        <v>-2022527.582936058</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>0.00772799996775575</v>
+        <v>-2022527.582936058</v>
       </c>
       <c r="F44">
-        <v>0.00772799996775575</v>
+        <v>-2022527.582936058</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -8858,16 +8858,16 @@
         <v>2042</v>
       </c>
       <c r="C45">
-        <v>0.006992000009631738</v>
+        <v>-2140016.537606199</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>0.006992000009631738</v>
+        <v>-2140016.537606199</v>
       </c>
       <c r="F45">
-        <v>0.006992000009631738</v>
+        <v>-2140016.537606199</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -8878,16 +8878,16 @@
         <v>2043</v>
       </c>
       <c r="C46">
-        <v>0.004992000031052157</v>
+        <v>-2268400.280267908</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>0.004992000031052157</v>
+        <v>-2268400.280267908</v>
       </c>
       <c r="F46">
-        <v>0.004992000031052157</v>
+        <v>-2268400.280267908</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -8898,16 +8898,16 @@
         <v>2044</v>
       </c>
       <c r="C47">
-        <v>0.002560000080848113</v>
+        <v>-2392124.503804208</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>0.002560000080848113</v>
+        <v>-2392124.503804208</v>
       </c>
       <c r="F47">
-        <v>0.002560000080848113</v>
+        <v>-2392124.503804208</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -8918,16 +8918,16 @@
         <v>2045</v>
       </c>
       <c r="C48">
-        <v>0.001456000114558265</v>
+        <v>-2501978.911174258</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>0.001456000114558265</v>
+        <v>-2501978.911174258</v>
       </c>
       <c r="F48">
-        <v>0.001456000114558265</v>
+        <v>-2501978.911174258</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -8938,16 +8938,16 @@
         <v>2046</v>
       </c>
       <c r="C49">
-        <v>-0.00137599985464476</v>
+        <v>-2614542.451697267</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>-0.00137599985464476</v>
+        <v>-2614542.451697267</v>
       </c>
       <c r="F49">
-        <v>-0.00137599985464476</v>
+        <v>-2614542.451697267</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -8958,16 +8958,16 @@
         <v>2047</v>
       </c>
       <c r="C50">
-        <v>-0.00161599981947802</v>
+        <v>-2737480.892979037</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>-0.00161599981947802</v>
+        <v>-2737480.892979037</v>
       </c>
       <c r="F50">
-        <v>-0.00161599981947802</v>
+        <v>-2737480.892979037</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -8978,16 +8978,16 @@
         <v>2048</v>
       </c>
       <c r="C51">
-        <v>-0.001759999810019508</v>
+        <v>-2862092.413571886</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>-0.001759999810019508</v>
+        <v>-2862092.413571886</v>
       </c>
       <c r="F51">
-        <v>-0.001759999810019508</v>
+        <v>-2862092.413571886</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -8998,16 +8998,16 @@
         <v>2049</v>
       </c>
       <c r="C52">
-        <v>-0.004463999794097617</v>
+        <v>-2963573.597318447</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>-0.004463999794097617</v>
+        <v>-2963573.597318447</v>
       </c>
       <c r="F52">
-        <v>-0.004463999794097617</v>
+        <v>-2963573.597318447</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -9018,16 +9018,16 @@
         <v>2050</v>
       </c>
       <c r="C53">
-        <v>-0.003583999787224457</v>
+        <v>-3082794.266219589</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>-0.003583999787224457</v>
+        <v>-3082794.266219589</v>
       </c>
       <c r="F53">
-        <v>-0.003583999787224457</v>
+        <v>-3082794.266219589</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -9038,13 +9038,13 @@
         <v>2025</v>
       </c>
       <c r="C54">
-        <v>-0.001040000002831221</v>
+        <v>-164945.6975903904</v>
       </c>
       <c r="D54">
-        <v>-0.0002479564136592671</v>
+        <v>-39326.29020092187</v>
       </c>
       <c r="E54">
-        <v>-0.0007920435746200383</v>
+        <v>-125619.4073894685</v>
       </c>
       <c r="F54">
         <v>0</v>
@@ -9058,13 +9058,13 @@
         <v>2026</v>
       </c>
       <c r="C55">
-        <v>0.003279999946244061</v>
+        <v>-186966.5601539384</v>
       </c>
       <c r="D55">
-        <v>0.0007820163300493732</v>
+        <v>-44576.49584010887</v>
       </c>
       <c r="E55">
-        <v>0.002497983630746603</v>
+        <v>-142390.0643138295</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>2027</v>
       </c>
       <c r="C56">
-        <v>0.002800000016577542</v>
+        <v>-141094.2363658061</v>
       </c>
       <c r="D56">
-        <v>0.0006675749173155054</v>
+        <v>-33639.63392836272</v>
       </c>
       <c r="E56">
-        <v>0.002132425084710121</v>
+        <v>-107454.6024374434</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -9098,13 +9098,13 @@
         <v>2028</v>
       </c>
       <c r="C57">
-        <v>4.799995804205537E-05</v>
+        <v>-144303.1128844892</v>
       </c>
       <c r="D57">
-        <v>1.144413545262069E-05</v>
+        <v>-34404.69304197494</v>
       </c>
       <c r="E57">
-        <v>3.655586624518037E-05</v>
+        <v>-109898.4198425142</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -9118,13 +9118,13 @@
         <v>2029</v>
       </c>
       <c r="C58">
-        <v>0.0001279999269172549</v>
+        <v>-187257.000217265</v>
       </c>
       <c r="D58">
-        <v>3.051769454032183E-05</v>
+        <v>-44645.74244904269</v>
       </c>
       <c r="E58">
-        <v>9.74822323769331E-05</v>
+        <v>-142611.2577682223</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -9138,13 +9138,13 @@
         <v>2030</v>
       </c>
       <c r="C59">
-        <v>-0.002367999986745417</v>
+        <v>-170825.6252525288</v>
       </c>
       <c r="D59">
-        <v>-0.0005645776545861736</v>
+        <v>-40728.1803076642</v>
       </c>
       <c r="E59">
-        <v>-0.001803422346711159</v>
+        <v>-130097.4449448646</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -9158,13 +9158,13 @@
         <v>2031</v>
       </c>
       <c r="C60">
-        <v>0.0001600000541657209</v>
+        <v>-202037.0195392545</v>
       </c>
       <c r="D60">
-        <v>3.814713272731751E-05</v>
+        <v>-48169.58900898871</v>
       </c>
       <c r="E60">
-        <v>0.0001218528486788273</v>
+        <v>-153867.4305302658</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -9178,13 +9178,13 @@
         <v>2032</v>
       </c>
       <c r="C61">
-        <v>-0.0001439999905414879</v>
+        <v>-189562.3095111181</v>
       </c>
       <c r="D61">
-        <v>-3.433242090977728E-05</v>
+        <v>-45195.37341012471</v>
       </c>
       <c r="E61">
-        <v>-0.0001096675987355411</v>
+        <v>-144366.9361009934</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -9198,13 +9198,13 @@
         <v>2033</v>
       </c>
       <c r="C62">
-        <v>-0.002991999965161085</v>
+        <v>-208191.134434339</v>
       </c>
       <c r="D62">
-        <v>-0.0007133515027817339</v>
+        <v>-49636.85073105502</v>
       </c>
       <c r="E62">
-        <v>-0.002278648549690843</v>
+        <v>-158554.283703284</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -9218,13 +9218,13 @@
         <v>2034</v>
       </c>
       <c r="C63">
-        <v>-0.0007519999635405838</v>
+        <v>-181552.7782310514</v>
       </c>
       <c r="D63">
-        <v>-0.0001792915572877973</v>
+        <v>-43285.74402242484</v>
       </c>
       <c r="E63">
-        <v>-0.000572708435356617</v>
+        <v>-138267.0342086266</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -9238,13 +9238,13 @@
         <v>2035</v>
       </c>
       <c r="C64">
-        <v>-0.002016000042203814</v>
+        <v>-170815.7600898655</v>
       </c>
       <c r="D64">
-        <v>-0.0004806539509445429</v>
+        <v>-40725.82825935107</v>
       </c>
       <c r="E64">
-        <v>-0.001535346091259271</v>
+        <v>-130089.9318305145</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -9258,13 +9258,13 @@
         <v>2036</v>
       </c>
       <c r="C65">
-        <v>-0.0004640000988729298</v>
+        <v>-168876.7652072157</v>
       </c>
       <c r="D65">
-        <v>-0.000110626730020158</v>
+        <v>-40263.53384023535</v>
       </c>
       <c r="E65">
-        <v>-0.0003533732960931957</v>
+        <v>-128613.2313669804</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -9278,13 +9278,13 @@
         <v>2037</v>
       </c>
       <c r="C66">
-        <v>-0.003407999989576638</v>
+        <v>-199432.3339440663</v>
       </c>
       <c r="D66">
-        <v>-0.0008125340682454407</v>
+        <v>-47548.58086452102</v>
       </c>
       <c r="E66">
-        <v>-0.002595465921331197</v>
+        <v>-151883.7530795452</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -9298,13 +9298,13 @@
         <v>2038</v>
       </c>
       <c r="C67">
-        <v>0.0004959999932907522</v>
+        <v>-190852.5777743378</v>
       </c>
       <c r="D67">
-        <v>0.0001182561099994928</v>
+        <v>-45502.99867648614</v>
       </c>
       <c r="E67">
-        <v>0.000377743795979768</v>
+        <v>-145349.5790978516</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -9318,13 +9318,13 @@
         <v>2039</v>
       </c>
       <c r="C68">
-        <v>-0.000783999974373728</v>
+        <v>-165323.7367201426</v>
       </c>
       <c r="D68">
-        <v>-0.0001869209663709626</v>
+        <v>-39416.42214580506</v>
       </c>
       <c r="E68">
-        <v>-0.0005970789934508502</v>
+        <v>-125907.3145743376</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -9338,13 +9338,13 @@
         <v>2040</v>
       </c>
       <c r="C69">
-        <v>-0.0006719999946653843</v>
+        <v>-204969.6612606774</v>
       </c>
       <c r="D69">
-        <v>-0.000160217983648181</v>
+        <v>-48868.78832777544</v>
       </c>
       <c r="E69">
-        <v>-0.0005117820692248642</v>
+        <v>-156100.872932902</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -9358,13 +9358,13 @@
         <v>2041</v>
       </c>
       <c r="C70">
-        <v>0.0007359999581240118</v>
+        <v>-167125.7593176033</v>
       </c>
       <c r="D70">
-        <v>0.0001754768454702571</v>
+        <v>-39846.05968501716</v>
       </c>
       <c r="E70">
-        <v>0.0005605231272056699</v>
+        <v>-127279.6996325861</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>2042</v>
       </c>
       <c r="C71">
-        <v>0.001999999862164259</v>
+        <v>-182623.3810342913</v>
       </c>
       <c r="D71">
-        <v>0.0004768392245750874</v>
+        <v>-43540.9967337425</v>
       </c>
       <c r="E71">
-        <v>0.001523160666693002</v>
+        <v>-139082.3843005488</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -9398,13 +9398,13 @@
         <v>2043</v>
       </c>
       <c r="C72">
-        <v>0.002432000008411705</v>
+        <v>-175995.3043326439</v>
       </c>
       <c r="D72">
-        <v>0.0005798365164082497</v>
+        <v>-41960.73321883565</v>
       </c>
       <c r="E72">
-        <v>0.001852163462899625</v>
+        <v>-134034.5711138083</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -9418,13 +9418,13 @@
         <v>2044</v>
       </c>
       <c r="C73">
-        <v>0.001104000024497509</v>
+        <v>-156265.7628480942</v>
       </c>
       <c r="D73">
-        <v>0.0002632152463775128</v>
+        <v>-37256.82347588925</v>
       </c>
       <c r="E73">
-        <v>0.0008407847490161657</v>
+        <v>-119008.9393722049</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -9438,13 +9438,13 @@
         <v>2045</v>
       </c>
       <c r="C74">
-        <v>0.002832000085618347</v>
+        <v>-160119.4480695512</v>
       </c>
       <c r="D74">
-        <v>0.0006752043555025011</v>
+        <v>-38175.61763406348</v>
       </c>
       <c r="E74">
-        <v>0.002156795701012015</v>
+        <v>-121943.8304354877</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -9458,13 +9458,13 @@
         <v>2046</v>
       </c>
       <c r="C75">
-        <v>0.0002399999066255987</v>
+        <v>-174877.5496139904</v>
       </c>
       <c r="D75">
-        <v>5.722069181501865E-05</v>
+        <v>-41694.23856585975</v>
       </c>
       <c r="E75">
-        <v>0.00018277921481058</v>
+        <v>-133183.3110481306</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -9478,13 +9478,13 @@
         <v>2047</v>
       </c>
       <c r="C76">
-        <v>0.0001439999905414879</v>
+        <v>-177257.4727425422</v>
       </c>
       <c r="D76">
-        <v>3.433240635786206E-05</v>
+        <v>-42261.65892890394</v>
       </c>
       <c r="E76">
-        <v>0.0001096674823202193</v>
+        <v>-134995.8138136383</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -9498,13 +9498,13 @@
         <v>2048</v>
       </c>
       <c r="C77">
-        <v>0.002703999984078109</v>
+        <v>-144355.0106394874</v>
       </c>
       <c r="D77">
-        <v>0.0006446866464102641</v>
+        <v>-34417.06648489375</v>
       </c>
       <c r="E77">
-        <v>0.00205931335221976</v>
+        <v>-109937.9441545937</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -9518,13 +9518,13 @@
         <v>2049</v>
       </c>
       <c r="C78">
-        <v>-0.0008800000650808215</v>
+        <v>-169589.093165578</v>
       </c>
       <c r="D78">
-        <v>-0.0002098092518281192</v>
+        <v>-40433.36679991853</v>
       </c>
       <c r="E78">
-        <v>-0.0006701907841488719</v>
+        <v>-129155.7263656595</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -9538,13 +9538,13 @@
         <v>2050</v>
       </c>
       <c r="C79">
-        <v>-0.000623999978415668</v>
+        <v>-165884.5116305721</v>
       </c>
       <c r="D79">
-        <v>-0.0001487738481955603</v>
+        <v>-39550.12188570197</v>
       </c>
       <c r="E79">
-        <v>-0.000475226144772023</v>
+        <v>-126334.3897448702</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -9578,13 +9578,13 @@
         <v>2026</v>
       </c>
       <c r="C81">
-        <v>-0.001040000002831221</v>
+        <v>-164945.6975903904</v>
       </c>
       <c r="D81">
-        <v>-0.0002479564136592671</v>
+        <v>-39326.29020092187</v>
       </c>
       <c r="E81">
-        <v>-0.0007920435746200383</v>
+        <v>-125619.4073894685</v>
       </c>
       <c r="F81">
         <v>0</v>
@@ -9598,13 +9598,13 @@
         <v>2027</v>
       </c>
       <c r="C82">
-        <v>0.00223999994341284</v>
+        <v>-351912.2577443288</v>
       </c>
       <c r="D82">
-        <v>0.0005340599163901061</v>
+        <v>-83902.78604103073</v>
       </c>
       <c r="E82">
-        <v>0.001705940056126565</v>
+        <v>-268009.471703298</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -9618,13 +9618,13 @@
         <v>2028</v>
       </c>
       <c r="C83">
-        <v>0.005039999959990382</v>
+        <v>-493006.4941101348</v>
       </c>
       <c r="D83">
-        <v>0.001201634833705612</v>
+        <v>-117542.4199693934</v>
       </c>
       <c r="E83">
-        <v>0.003838365140836686</v>
+        <v>-375464.0741407414</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -9638,13 +9638,13 @@
         <v>2029</v>
       </c>
       <c r="C84">
-        <v>0.005087999918032438</v>
+        <v>-637309.606994624</v>
       </c>
       <c r="D84">
-        <v>0.001213078969158232</v>
+        <v>-151947.1130113684</v>
       </c>
       <c r="E84">
-        <v>0.003874921007081866</v>
+        <v>-485362.4939832556</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -9658,13 +9658,13 @@
         <v>2030</v>
       </c>
       <c r="C85">
-        <v>0.005215999844949692</v>
+        <v>-824566.607211889</v>
       </c>
       <c r="D85">
-        <v>0.001243596663698554</v>
+        <v>-196592.8554604111</v>
       </c>
       <c r="E85">
-        <v>0.003972403239458799</v>
+        <v>-627973.7517514778</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -9678,13 +9678,13 @@
         <v>2031</v>
       </c>
       <c r="C86">
-        <v>0.002847999858204275</v>
+        <v>-995392.2324644178</v>
       </c>
       <c r="D86">
-        <v>0.0006790190091123804</v>
+        <v>-237321.0357680753</v>
       </c>
       <c r="E86">
-        <v>0.002168980892747641</v>
+        <v>-758071.1966963424</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -9698,13 +9698,13 @@
         <v>2032</v>
       </c>
       <c r="C87">
-        <v>0.003007999912369996</v>
+        <v>-1197429.252003672</v>
       </c>
       <c r="D87">
-        <v>0.000717166141839698</v>
+        <v>-285490.624777064</v>
       </c>
       <c r="E87">
-        <v>0.002290833741426468</v>
+        <v>-911938.6272266083</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -9718,13 +9718,13 @@
         <v>2033</v>
       </c>
       <c r="C88">
-        <v>0.002863999921828508</v>
+        <v>-1386991.56151479</v>
       </c>
       <c r="D88">
-        <v>0.0006828337209299207</v>
+        <v>-330685.9981871886</v>
       </c>
       <c r="E88">
-        <v>0.002181166142690927</v>
+        <v>-1056305.563327602</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -9738,13 +9738,13 @@
         <v>2034</v>
       </c>
       <c r="C89">
-        <v>-0.0001280000433325768</v>
+        <v>-1595182.695949129</v>
       </c>
       <c r="D89">
-        <v>-3.05177818518132E-05</v>
+        <v>-380322.8489182437</v>
       </c>
       <c r="E89">
-        <v>-9.748240699991584E-05</v>
+        <v>-1214859.847030886</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -9758,13 +9758,13 @@
         <v>2035</v>
       </c>
       <c r="C90">
-        <v>-0.0008800000068731606</v>
+        <v>-1776735.474180181</v>
       </c>
       <c r="D90">
-        <v>-0.0002098093391396105</v>
+        <v>-423608.5929406685</v>
       </c>
       <c r="E90">
-        <v>-0.0006701908423565328</v>
+        <v>-1353126.881239512</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -9778,13 +9778,13 @@
         <v>2036</v>
       </c>
       <c r="C91">
-        <v>-0.002896000049076974</v>
+        <v>-1947551.234270046</v>
       </c>
       <c r="D91">
-        <v>-0.0006904632900841534</v>
+        <v>-464334.4212000196</v>
       </c>
       <c r="E91">
-        <v>-0.002205536933615804</v>
+        <v>-1483216.813070026</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -9798,13 +9798,13 @@
         <v>2037</v>
       </c>
       <c r="C92">
-        <v>-0.003360000147949904</v>
+        <v>-2116427.999477262</v>
       </c>
       <c r="D92">
-        <v>-0.0008010900201043114</v>
+        <v>-504597.955040255</v>
       </c>
       <c r="E92">
-        <v>-0.002558910229708999</v>
+        <v>-1611830.044437007</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -9818,13 +9818,13 @@
         <v>2038</v>
       </c>
       <c r="C93">
-        <v>-0.006768000137526542</v>
+        <v>-2315860.333421328</v>
       </c>
       <c r="D93">
-        <v>-0.001613624088349752</v>
+        <v>-552146.535904776</v>
       </c>
       <c r="E93">
-        <v>-0.005154376151040196</v>
+        <v>-1763713.797516552</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -9838,13 +9838,13 @@
         <v>2039</v>
       </c>
       <c r="C94">
-        <v>-0.00627200014423579</v>
+        <v>-2506712.911195666</v>
       </c>
       <c r="D94">
-        <v>-0.001495367978350259</v>
+        <v>-597649.5345812622</v>
       </c>
       <c r="E94">
-        <v>-0.004776632355060428</v>
+        <v>-1909063.376614404</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -9858,13 +9858,13 @@
         <v>2040</v>
       </c>
       <c r="C95">
-        <v>-0.007056000118609518</v>
+        <v>-2672036.647915808</v>
       </c>
       <c r="D95">
-        <v>-0.001682288944721222</v>
+        <v>-637065.9567270672</v>
       </c>
       <c r="E95">
-        <v>-0.005373711348511279</v>
+        <v>-2034970.691188741</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -9878,13 +9878,13 @@
         <v>2041</v>
       </c>
       <c r="C96">
-        <v>-0.007728000113274902</v>
+        <v>-2877006.309176486</v>
       </c>
       <c r="D96">
-        <v>-0.001842506928369403</v>
+        <v>-685934.7450548427</v>
       </c>
       <c r="E96">
-        <v>-0.005885493417736143</v>
+        <v>-2191071.564121643</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -9898,13 +9898,13 @@
         <v>2042</v>
       </c>
       <c r="C97">
-        <v>-0.00699200015515089</v>
+        <v>-3044132.068494089</v>
       </c>
       <c r="D97">
-        <v>-0.001667030082899146</v>
+        <v>-725780.8047398599</v>
       </c>
       <c r="E97">
-        <v>-0.005324970290530473</v>
+        <v>-2318351.263754229</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -9918,13 +9918,13 @@
         <v>2043</v>
       </c>
       <c r="C98">
-        <v>-0.004992000292986631</v>
+        <v>-3226755.449528381</v>
       </c>
       <c r="D98">
-        <v>-0.001190190858324058</v>
+        <v>-769321.8014736024</v>
       </c>
       <c r="E98">
-        <v>-0.003801809623837471</v>
+        <v>-2457433.648054778</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -9938,13 +9938,13 @@
         <v>2044</v>
       </c>
       <c r="C99">
-        <v>-0.002560000284574926</v>
+        <v>-3402750.753861025</v>
       </c>
       <c r="D99">
-        <v>-0.0006103543419158086</v>
+        <v>-811282.5346924381</v>
       </c>
       <c r="E99">
-        <v>-0.001949646160937846</v>
+        <v>-2591468.219168586</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -9958,13 +9958,13 @@
         <v>2045</v>
       </c>
       <c r="C100">
-        <v>-0.001456000260077417</v>
+        <v>-3559016.516709119</v>
       </c>
       <c r="D100">
-        <v>-0.0003471390955382958</v>
+        <v>-848539.3581683274</v>
       </c>
       <c r="E100">
-        <v>-0.00110886141192168</v>
+        <v>-2710477.15854079</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -9978,13 +9978,13 @@
         <v>2046</v>
       </c>
       <c r="C101">
-        <v>0.00137599982554093</v>
+        <v>-3719135.96477867</v>
       </c>
       <c r="D101">
-        <v>0.0003280652599642053</v>
+        <v>-886714.9758023908</v>
       </c>
       <c r="E101">
-        <v>0.001047934289090335</v>
+        <v>-2832420.988976278</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -9998,13 +9998,13 @@
         <v>2047</v>
       </c>
       <c r="C102">
-        <v>0.001615999732166529</v>
+        <v>-3894013.51439266</v>
       </c>
       <c r="D102">
-        <v>0.000385285951779224</v>
+        <v>-928409.2143682506</v>
       </c>
       <c r="E102">
-        <v>0.001230713503900915</v>
+        <v>-2965604.300024409</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -10018,13 +10018,13 @@
         <v>2048</v>
       </c>
       <c r="C103">
-        <v>0.001759999722708017</v>
+        <v>-4071270.987135202</v>
       </c>
       <c r="D103">
-        <v>0.000419618358137086</v>
+        <v>-970670.8732971546</v>
       </c>
       <c r="E103">
-        <v>0.001340380986221135</v>
+        <v>-3100600.113838047</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -10038,13 +10038,13 @@
         <v>2049</v>
       </c>
       <c r="C104">
-        <v>0.004463999706786126</v>
+        <v>-4215625.997774689</v>
       </c>
       <c r="D104">
-        <v>0.00106430500454735</v>
+        <v>-1005087.939782048</v>
       </c>
       <c r="E104">
-        <v>0.003399694338440895</v>
+        <v>-3210538.057992641</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -10058,13 +10058,13 @@
         <v>2050</v>
       </c>
       <c r="C105">
-        <v>0.003583999641705304</v>
+        <v>-4385215.090940268</v>
       </c>
       <c r="D105">
-        <v>0.0008544957527192309</v>
+        <v>-1045521.306581967</v>
       </c>
       <c r="E105">
-        <v>0.002729503554292023</v>
+        <v>-3339693.7843583</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -10078,16 +10078,16 @@
         <v>2025</v>
       </c>
       <c r="C106">
-        <v>0</v>
+        <v>280902.071782</v>
       </c>
       <c r="D106">
-        <v>9.651455184211954E-05</v>
+        <v>39326.29004948001</v>
       </c>
       <c r="E106">
-        <v>-9.65145300142467E-05</v>
+        <v>241575.78173252</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>115956.3752316096</v>
       </c>
     </row>
     <row r="107" spans="1:6">
@@ -10098,16 +10098,16 @@
         <v>2026</v>
       </c>
       <c r="C107">
-        <v>0</v>
+        <v>318403.54808232</v>
       </c>
       <c r="D107">
-        <v>0.0001093996033887379</v>
+        <v>44576.49673152481</v>
       </c>
       <c r="E107">
-        <v>-0.0001093996106646955</v>
+        <v>273827.0513507952</v>
       </c>
       <c r="F107">
-        <v>0</v>
+        <v>131436.9846483817</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -10118,16 +10118,16 @@
         <v>2027</v>
       </c>
       <c r="C108">
-        <v>2.91038304567337E-11</v>
+        <v>240283.1048464</v>
       </c>
       <c r="D108">
-        <v>8.255837019532919E-05</v>
+        <v>33639.634678496</v>
       </c>
       <c r="E108">
-        <v>-8.255834109149873E-05</v>
+        <v>206643.470167904</v>
       </c>
       <c r="F108">
-        <v>0</v>
+        <v>99188.86568059392</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -10138,16 +10138,16 @@
         <v>2028</v>
       </c>
       <c r="C109">
-        <v>0</v>
+        <v>245747.808127536</v>
       </c>
       <c r="D109">
-        <v>8.443597471341491E-05</v>
+        <v>34404.69313785505</v>
       </c>
       <c r="E109">
-        <v>-8.443594560958445E-05</v>
+        <v>211343.114989681</v>
       </c>
       <c r="F109">
-        <v>0</v>
+        <v>101444.6951950469</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -10158,16 +10158,16 @@
         <v>2029</v>
       </c>
       <c r="C110">
-        <v>0</v>
+        <v>318898.161350928</v>
       </c>
       <c r="D110">
-        <v>0.0001095695479307324</v>
+        <v>44645.74258912993</v>
       </c>
       <c r="E110">
-        <v>-0.0001095695188269019</v>
+        <v>274252.4187617981</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>131641.1610056631</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -10178,16 +10178,16 @@
         <v>2030</v>
       </c>
       <c r="C111">
-        <v>0</v>
+        <v>290915.57030744</v>
       </c>
       <c r="D111">
-        <v>9.995506115956232E-05</v>
+        <v>40728.1798430416</v>
       </c>
       <c r="E111">
-        <v>-9.995503933168948E-05</v>
+        <v>250187.3904643984</v>
       </c>
       <c r="F111">
-        <v>0</v>
+        <v>120089.9474229112</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -10198,16 +10198,16 @@
         <v>2031</v>
       </c>
       <c r="C112">
-        <v>0</v>
+        <v>344068.4940382401</v>
       </c>
       <c r="D112">
-        <v>0.000118217765702866</v>
+        <v>48169.58916535361</v>
       </c>
       <c r="E112">
-        <v>-0.0001182177220471203</v>
+        <v>295898.9048728864</v>
       </c>
       <c r="F112">
-        <v>0</v>
+        <v>142031.4743389855</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -10218,16 +10218,16 @@
         <v>2032</v>
       </c>
       <c r="C113">
-        <v>0</v>
+        <v>322824.096333648</v>
       </c>
       <c r="D113">
-        <v>0.0001109184449887834</v>
+        <v>45195.37348671073</v>
       </c>
       <c r="E113">
-        <v>-0.0001109184231609106</v>
+        <v>277628.7228469373</v>
       </c>
       <c r="F113">
-        <v>0</v>
+        <v>133261.7869665299</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -10238,16 +10238,16 @@
         <v>2033</v>
       </c>
       <c r="C114">
-        <v>5.820766091346741E-11</v>
+        <v>354548.929568016</v>
       </c>
       <c r="D114">
-        <v>0.0001218187244376168</v>
+        <v>49636.85013952225</v>
       </c>
       <c r="E114">
-        <v>-0.0001218186807818711</v>
+        <v>304912.0794284938</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>146357.798125677</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -10258,16 +10258,16 @@
         <v>2034</v>
       </c>
       <c r="C115">
-        <v>0</v>
+        <v>309183.885352608</v>
       </c>
       <c r="D115">
-        <v>0.0001062318406184204</v>
+        <v>43285.74394936513</v>
       </c>
       <c r="E115">
-        <v>-0.0001062317751348019</v>
+        <v>265898.1414032429</v>
       </c>
       <c r="F115">
-        <v>0</v>
+        <v>127631.1078735566</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -10278,16 +10278,16 @@
         <v>2035</v>
       </c>
       <c r="C116">
-        <v>0</v>
+        <v>290898.77056176</v>
       </c>
       <c r="D116">
-        <v>9.994929860113189E-05</v>
+        <v>40725.82787864641</v>
       </c>
       <c r="E116">
-        <v>-9.994927677325904E-05</v>
+        <v>250172.9426831136</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>120083.0124878945</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -10298,16 +10298,16 @@
         <v>2036</v>
       </c>
       <c r="C117">
-        <v>5.820766091346741E-11</v>
+        <v>287596.670203024</v>
       </c>
       <c r="D117">
-        <v>9.881473670247942E-05</v>
+        <v>40263.53382842337</v>
       </c>
       <c r="E117">
-        <v>-9.881469304673374E-05</v>
+        <v>247333.1363746006</v>
       </c>
       <c r="F117">
-        <v>0</v>
+        <v>118719.9054598083</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -10318,16 +10318,16 @@
         <v>2037</v>
       </c>
       <c r="C118">
-        <v>0</v>
+        <v>339632.715490576</v>
       </c>
       <c r="D118">
-        <v>0.0001166936926892959</v>
+        <v>47548.58016868064</v>
       </c>
       <c r="E118">
-        <v>-0.000116693670861423</v>
+        <v>292084.1353218954</v>
       </c>
       <c r="F118">
-        <v>0</v>
+        <v>140200.3849545098</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -10338,16 +10338,16 @@
         <v>2038</v>
       </c>
       <c r="C119">
-        <v>0</v>
+        <v>325021.420760112</v>
       </c>
       <c r="D119">
-        <v>0.0001116734274546616</v>
+        <v>45502.99890641568</v>
       </c>
       <c r="E119">
-        <v>-0.0001116734347306192</v>
+        <v>279518.4218536963</v>
       </c>
       <c r="F119">
-        <v>0</v>
+        <v>134168.8424897742</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -10358,16 +10358,16 @@
         <v>2039</v>
       </c>
       <c r="C120">
-        <v>0</v>
+        <v>281545.871825856</v>
       </c>
       <c r="D120">
-        <v>9.673575550550595E-05</v>
+        <v>39416.42205561985</v>
       </c>
       <c r="E120">
-        <v>-9.673574822954834E-05</v>
+        <v>242129.4497702362</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>116222.1358897134</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -10378,16 +10378,16 @@
         <v>2040</v>
       </c>
       <c r="C121">
-        <v>5.820766091346741E-11</v>
+        <v>349062.77348208</v>
       </c>
       <c r="D121">
-        <v>0.0001199337493744679</v>
+        <v>48868.78828749121</v>
       </c>
       <c r="E121">
-        <v>-0.0001199336838908494</v>
+        <v>300193.9851945888</v>
       </c>
       <c r="F121">
-        <v>0</v>
+        <v>144093.1128934026</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -10398,16 +10398,16 @@
         <v>2041</v>
       </c>
       <c r="C122">
-        <v>0</v>
+        <v>284614.713987744</v>
       </c>
       <c r="D122">
-        <v>9.779017273103818E-05</v>
+        <v>39846.05995828417</v>
       </c>
       <c r="E122">
-        <v>-9.779015090316534E-05</v>
+        <v>244768.6540294598</v>
       </c>
       <c r="F122">
-        <v>0</v>
+        <v>117488.9539341407</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -10418,16 +10418,16 @@
         <v>2042</v>
       </c>
       <c r="C123">
-        <v>5.820766091346741E-11</v>
+        <v>311007.123696</v>
       </c>
       <c r="D123">
-        <v>0.0001068582860170864</v>
+        <v>43540.99731744001</v>
       </c>
       <c r="E123">
-        <v>-0.0001068582641892135</v>
+        <v>267466.12637856</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>128383.7406617088</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -10438,16 +10438,16 @@
         <v>2043</v>
       </c>
       <c r="C124">
-        <v>0</v>
+        <v>299719.527868944</v>
       </c>
       <c r="D124">
-        <v>0.000102980004157871</v>
+        <v>41960.73390165217</v>
       </c>
       <c r="E124">
-        <v>-0.0001029799459502101</v>
+        <v>257758.7939672919</v>
       </c>
       <c r="F124">
-        <v>0</v>
+        <v>123724.2211043001</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -10458,16 +10458,16 @@
         <v>2044</v>
       </c>
       <c r="C125">
-        <v>0</v>
+        <v>266120.170218144</v>
       </c>
       <c r="D125">
-        <v>9.14356714929454E-05</v>
+        <v>37256.82383054017</v>
       </c>
       <c r="E125">
-        <v>-9.143564966507256E-05</v>
+        <v>228863.3463876038</v>
       </c>
       <c r="F125">
-        <v>0</v>
+        <v>109854.4062660498</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -10478,16 +10478,16 @@
         <v>2045</v>
       </c>
       <c r="C126">
-        <v>0</v>
+        <v>272682.9885925601</v>
       </c>
       <c r="D126">
-        <v>9.36905707931146E-05</v>
+        <v>38175.61840295841</v>
       </c>
       <c r="E126">
-        <v>-9.369055624119937E-05</v>
+        <v>234507.3701896016</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>112563.5376910088</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -10498,16 +10498,16 @@
         <v>2046</v>
       </c>
       <c r="C127">
-        <v>0</v>
+        <v>297815.99089576</v>
       </c>
       <c r="D127">
-        <v>0.0001023259683279321</v>
+        <v>41694.23872540641</v>
       </c>
       <c r="E127">
-        <v>-0.0001023259246721864</v>
+        <v>256121.7521703536</v>
       </c>
       <c r="F127">
-        <v>0</v>
+        <v>122938.4410417697</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -10518,16 +10518,16 @@
         <v>2047</v>
       </c>
       <c r="C128">
-        <v>5.820766091346741E-11</v>
+        <v>301868.993335392</v>
       </c>
       <c r="D128">
-        <v>0.0001037185356835835</v>
+        <v>42261.65906695489</v>
       </c>
       <c r="E128">
-        <v>-0.0001037184847518802</v>
+        <v>259607.3342684371</v>
       </c>
       <c r="F128">
-        <v>0</v>
+        <v>124611.5204488498</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -10538,16 +10538,16 @@
         <v>2048</v>
       </c>
       <c r="C129">
-        <v>2.91038304567337E-11</v>
+        <v>245836.194386048</v>
       </c>
       <c r="D129">
-        <v>8.446633728453889E-05</v>
+        <v>34417.06721404673</v>
       </c>
       <c r="E129">
-        <v>-8.446633000858128E-05</v>
+        <v>211419.1271720013</v>
       </c>
       <c r="F129">
-        <v>0</v>
+        <v>101481.1810425606</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -10558,16 +10558,16 @@
         <v>2049</v>
       </c>
       <c r="C130">
-        <v>0</v>
+        <v>288809.76206672</v>
       </c>
       <c r="D130">
-        <v>9.923153265845031E-05</v>
+        <v>40433.3666893408</v>
       </c>
       <c r="E130">
-        <v>-9.923148900270462E-05</v>
+        <v>248376.3953773792</v>
       </c>
       <c r="F130">
-        <v>0</v>
+        <v>119220.669781142</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -10578,16 +10578,16 @@
         <v>2050</v>
       </c>
       <c r="C131">
-        <v>0</v>
+        <v>282500.8702428</v>
       </c>
       <c r="D131">
-        <v>9.706387936603278E-05</v>
+        <v>39550.12183399201</v>
       </c>
       <c r="E131">
-        <v>-9.706386481411755E-05</v>
+        <v>242950.748408808</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>116616.3592362279</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -10618,16 +10618,16 @@
         <v>2026</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>280902.071782</v>
       </c>
       <c r="D133">
-        <v>9.651455184211954E-05</v>
+        <v>39326.29004948001</v>
       </c>
       <c r="E133">
-        <v>-9.65145300142467E-05</v>
+        <v>241575.78173252</v>
       </c>
       <c r="F133">
-        <v>0</v>
+        <v>115956.3752316096</v>
       </c>
     </row>
     <row r="134" spans="1:6">
@@ -10638,16 +10638,16 @@
         <v>2027</v>
       </c>
       <c r="C134">
-        <v>0</v>
+        <v>599305.61986432</v>
       </c>
       <c r="D134">
-        <v>0.0002059141552308574</v>
+        <v>83902.7867810048</v>
       </c>
       <c r="E134">
-        <v>-0.0002059141406789422</v>
+        <v>515402.8330833152</v>
       </c>
       <c r="F134">
-        <v>0</v>
+        <v>247393.3598799913</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -10658,16 +10658,16 @@
         <v>2028</v>
       </c>
       <c r="C135">
-        <v>2.91038304567337E-11</v>
+        <v>839588.72471072</v>
       </c>
       <c r="D135">
-        <v>0.0002884725254261866</v>
+        <v>117542.4214595008</v>
       </c>
       <c r="E135">
-        <v>-0.0002884724817704409</v>
+        <v>722046.3032512192</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>346582.2255605853</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -10678,16 +10678,16 @@
         <v>2029</v>
       </c>
       <c r="C136">
-        <v>2.91038304567337E-11</v>
+        <v>1085336.532838256</v>
       </c>
       <c r="D136">
-        <v>0.0003729085001396015</v>
+        <v>151947.1145973559</v>
       </c>
       <c r="E136">
-        <v>-0.0003729084273800254</v>
+        <v>933389.4182409002</v>
       </c>
       <c r="F136">
-        <v>0</v>
+        <v>448026.9207556322</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -10698,16 +10698,16 @@
         <v>2030</v>
       </c>
       <c r="C137">
-        <v>2.91038304567337E-11</v>
+        <v>1404234.694189184</v>
       </c>
       <c r="D137">
-        <v>0.0004824780480703339</v>
+        <v>196592.8571864858</v>
       </c>
       <c r="E137">
-        <v>-0.0004824779462069273</v>
+        <v>1207641.837002698</v>
       </c>
       <c r="F137">
-        <v>0</v>
+        <v>579668.0817612952</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -10718,16 +10718,16 @@
         <v>2031</v>
       </c>
       <c r="C138">
-        <v>2.91038304567337E-11</v>
+        <v>1695150.264496624</v>
       </c>
       <c r="D138">
-        <v>0.0005824331092298962</v>
+        <v>237321.0370295274</v>
       </c>
       <c r="E138">
-        <v>-0.0005824329855386168</v>
+        <v>1457829.227467097</v>
       </c>
       <c r="F138">
-        <v>0</v>
+        <v>699758.0291842064</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -10738,16 +10738,16 @@
         <v>2032</v>
       </c>
       <c r="C139">
-        <v>2.91038304567337E-11</v>
+        <v>2039218.758534864</v>
       </c>
       <c r="D139">
-        <v>0.0007006508749327622</v>
+        <v>285490.626194881</v>
       </c>
       <c r="E139">
-        <v>-0.0007006507075857371</v>
+        <v>1753728.132339983</v>
       </c>
       <c r="F139">
-        <v>0</v>
+        <v>841789.5035231919</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -10758,16 +10758,16 @@
         <v>2033</v>
       </c>
       <c r="C140">
-        <v>2.91038304567337E-11</v>
+        <v>2362042.854868512</v>
       </c>
       <c r="D140">
-        <v>0.0008115693199215457</v>
+        <v>330685.9996815917</v>
       </c>
       <c r="E140">
-        <v>-0.0008115691307466477</v>
+        <v>2031356.85518692</v>
       </c>
       <c r="F140">
-        <v>0</v>
+        <v>975051.2904897218</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -10778,16 +10778,16 @@
         <v>2034</v>
       </c>
       <c r="C141">
-        <v>8.731149137020111E-11</v>
+        <v>2716591.784436528</v>
       </c>
       <c r="D141">
-        <v>0.0009333880443591624</v>
+        <v>380322.8498211139</v>
       </c>
       <c r="E141">
-        <v>-0.0009333878115285188</v>
+        <v>2336268.934615414</v>
       </c>
       <c r="F141">
-        <v>0</v>
+        <v>1121409.088615399</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -10798,16 +10798,16 @@
         <v>2035</v>
       </c>
       <c r="C142">
-        <v>8.731149137020111E-11</v>
+        <v>3025775.669789136</v>
       </c>
       <c r="D142">
-        <v>0.001039619884977583</v>
+        <v>423608.5937704791</v>
       </c>
       <c r="E142">
-        <v>-0.001039619586663321</v>
+        <v>2602167.076018657</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>1249040.196488956</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -10818,16 +10818,16 @@
         <v>2036</v>
       </c>
       <c r="C143">
-        <v>8.731149137020111E-11</v>
+        <v>3316674.440350896</v>
       </c>
       <c r="D143">
-        <v>0.001139569183578715</v>
+        <v>464334.4216491255</v>
       </c>
       <c r="E143">
-        <v>-0.00113956886343658</v>
+        <v>2852340.018701771</v>
       </c>
       <c r="F143">
-        <v>0</v>
+        <v>1369123.20897685</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -10838,16 +10838,16 @@
         <v>2037</v>
       </c>
       <c r="C144">
-        <v>1.455191522836685E-10</v>
+        <v>3604271.11055392</v>
       </c>
       <c r="D144">
-        <v>0.001238383920281194</v>
+        <v>504597.9554775489</v>
       </c>
       <c r="E144">
-        <v>-0.001238383556483313</v>
+        <v>3099673.155076372</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1487843.114436659</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -10858,16 +10858,16 @@
         <v>2038</v>
       </c>
       <c r="C145">
-        <v>1.455191522836685E-10</v>
+        <v>3943903.826044496</v>
       </c>
       <c r="D145">
-        <v>0.00135507761297049</v>
+        <v>552146.5356462295</v>
       </c>
       <c r="E145">
-        <v>-0.001355077227344736</v>
+        <v>3391757.290398267</v>
       </c>
       <c r="F145">
-        <v>0</v>
+        <v>1628043.499391168</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -10878,16 +10878,16 @@
         <v>2039</v>
       </c>
       <c r="C146">
-        <v>1.455191522836685E-10</v>
+        <v>4268925.246804608</v>
       </c>
       <c r="D146">
-        <v>0.001466751040425152</v>
+        <v>597649.5345526452</v>
       </c>
       <c r="E146">
-        <v>-0.001466750662075356</v>
+        <v>3671275.712251964</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>1762212.341880943</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -10898,16 +10898,16 @@
         <v>2040</v>
       </c>
       <c r="C147">
-        <v>1.455191522836685E-10</v>
+        <v>4550471.118630464</v>
       </c>
       <c r="D147">
-        <v>0.001563486795930658</v>
+        <v>637065.9566082651</v>
       </c>
       <c r="E147">
-        <v>-0.001563486410304904</v>
+        <v>3913405.1620222</v>
       </c>
       <c r="F147">
-        <v>0</v>
+        <v>1878434.477770656</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -10918,16 +10918,16 @@
         <v>2041</v>
       </c>
       <c r="C148">
-        <v>2.037268131971359E-10</v>
+        <v>4899533.892112544</v>
       </c>
       <c r="D148">
-        <v>0.001683420545305125</v>
+        <v>685934.7448957562</v>
       </c>
       <c r="E148">
-        <v>-0.001683420094195753</v>
+        <v>4213599.147216788</v>
       </c>
       <c r="F148">
-        <v>0</v>
+        <v>2022527.590664059</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -10938,16 +10938,16 @@
         <v>2042</v>
       </c>
       <c r="C149">
-        <v>2.037268131971359E-10</v>
+        <v>5184148.606100288</v>
       </c>
       <c r="D149">
-        <v>0.001781210718036164</v>
+        <v>725780.8048540404</v>
       </c>
       <c r="E149">
-        <v>-0.001781210245098919</v>
+        <v>4458367.801246248</v>
       </c>
       <c r="F149">
-        <v>0</v>
+        <v>2140016.544598199</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -10958,16 +10958,16 @@
         <v>2043</v>
       </c>
       <c r="C150">
-        <v>2.619344741106033E-10</v>
+        <v>5495155.729796289</v>
       </c>
       <c r="D150">
-        <v>0.00188806900405325</v>
+        <v>769321.8021714804</v>
       </c>
       <c r="E150">
-        <v>-0.001888068509288132</v>
+        <v>4725833.927624809</v>
       </c>
       <c r="F150">
-        <v>0</v>
+        <v>2268400.285259908</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -10978,16 +10978,16 @@
         <v>2044</v>
       </c>
       <c r="C151">
-        <v>2.619344741106033E-10</v>
+        <v>5794875.257665233</v>
       </c>
       <c r="D151">
-        <v>0.001991049008211121</v>
+        <v>811282.5360731325</v>
       </c>
       <c r="E151">
-        <v>-0.001991048455238342</v>
+        <v>4983592.7215921</v>
       </c>
       <c r="F151">
-        <v>0</v>
+        <v>2392124.506364208</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -10998,16 +10998,16 @@
         <v>2045</v>
       </c>
       <c r="C152">
-        <v>2.619344741106033E-10</v>
+        <v>6060995.427883376</v>
       </c>
       <c r="D152">
-        <v>0.002082484679704066</v>
+        <v>848539.3599036727</v>
       </c>
       <c r="E152">
-        <v>-0.002082484104903415</v>
+        <v>5212456.067979705</v>
       </c>
       <c r="F152">
-        <v>0</v>
+        <v>2501978.912630258</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -11018,16 +11018,16 @@
         <v>2046</v>
       </c>
       <c r="C153">
-        <v>2.619344741106033E-10</v>
+        <v>6333678.416475937</v>
       </c>
       <c r="D153">
-        <v>0.002176175250497181</v>
+        <v>886714.9783066311</v>
       </c>
       <c r="E153">
-        <v>-0.002176174661144614</v>
+        <v>5446963.438169306</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>2614542.450321267</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -11038,16 +11038,16 @@
         <v>2047</v>
       </c>
       <c r="C154">
-        <v>2.619344741106033E-10</v>
+        <v>6631494.407371697</v>
       </c>
       <c r="D154">
-        <v>0.002278501218825113</v>
+        <v>928409.2170320374</v>
       </c>
       <c r="E154">
-        <v>-0.002278500585816801</v>
+        <v>5703085.190339659</v>
       </c>
       <c r="F154">
-        <v>0</v>
+        <v>2737480.891363037</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -11058,16 +11058,16 @@
         <v>2048</v>
       </c>
       <c r="C155">
-        <v>3.201421350240707E-10</v>
+        <v>6933363.400707089</v>
       </c>
       <c r="D155">
-        <v>0.002382219754508696</v>
+        <v>970670.8760989923</v>
       </c>
       <c r="E155">
-        <v>-0.002382219070568681</v>
+        <v>5962692.524608096</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>2862092.411811887</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -11078,16 +11078,16 @@
         <v>2049</v>
       </c>
       <c r="C156">
-        <v>3.492459654808044E-10</v>
+        <v>7179199.595093138</v>
       </c>
       <c r="D156">
-        <v>0.002466686091793235</v>
+        <v>1005087.943313039</v>
       </c>
       <c r="E156">
-        <v>-0.002466685400577262</v>
+        <v>6174111.651780098</v>
       </c>
       <c r="F156">
-        <v>0</v>
+        <v>2963573.592854448</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -11098,16 +11098,16 @@
         <v>2050</v>
       </c>
       <c r="C157">
-        <v>3.492459654808044E-10</v>
+        <v>7468009.357159858</v>
       </c>
       <c r="D157">
-        <v>0.002565917624451686</v>
+        <v>1045521.31000238</v>
       </c>
       <c r="E157">
-        <v>-0.002565916889579967</v>
+        <v>6422488.047157477</v>
       </c>
       <c r="F157">
-        <v>0</v>
+        <v>3082794.26263559</v>
       </c>
     </row>
   </sheetData>

--- a/biodym_mfa_tool/data/02_output/results_scientific.xlsx
+++ b/biodym_mfa_tool/data/02_output/results_scientific.xlsx
@@ -6408,13 +6408,13 @@
         <v>2025</v>
       </c>
       <c r="C288">
-        <v>57953.8933825696</v>
+        <v>57953.89338256961</v>
       </c>
       <c r="D288">
-        <v>13817.34511860948</v>
+        <v>13817.34511860949</v>
       </c>
       <c r="E288">
-        <v>44136.54826396011</v>
+        <v>44136.54826396013</v>
       </c>
       <c r="F288">
         <v>0</v>
@@ -6428,13 +6428,13 @@
         <v>2026</v>
       </c>
       <c r="C289">
-        <v>66788.27293134169</v>
+        <v>66788.27293134171</v>
       </c>
       <c r="D289">
         <v>15923.63451539543</v>
       </c>
       <c r="E289">
-        <v>50864.63841594626</v>
+        <v>50864.63841594627</v>
       </c>
       <c r="F289">
         <v>0</v>
@@ -6448,13 +6448,13 @@
         <v>2027</v>
       </c>
       <c r="C290">
-        <v>51237.05740699392</v>
+        <v>51237.05740699393</v>
       </c>
       <c r="D290">
-        <v>12215.9196515237</v>
+        <v>12215.91965152371</v>
       </c>
       <c r="E290">
-        <v>39021.13775547021</v>
+        <v>39021.13775547023</v>
       </c>
       <c r="F290">
         <v>0</v>
@@ -6468,13 +6468,13 @@
         <v>2028</v>
       </c>
       <c r="C291">
-        <v>53264.12821275886</v>
+        <v>53264.12821275887</v>
       </c>
       <c r="D291">
-        <v>12699.21309857856</v>
+        <v>12699.21309857857</v>
       </c>
       <c r="E291">
-        <v>40564.91511418029</v>
+        <v>40564.9151141803</v>
       </c>
       <c r="F291">
         <v>0</v>
@@ -6508,13 +6508,13 @@
         <v>2030</v>
       </c>
       <c r="C293">
-        <v>65121.37004990324</v>
+        <v>65121.37004990325</v>
       </c>
       <c r="D293">
         <v>15526.21216725399</v>
       </c>
       <c r="E293">
-        <v>49595.15788264925</v>
+        <v>49595.15788264926</v>
       </c>
       <c r="F293">
         <v>0</v>
@@ -6528,13 +6528,13 @@
         <v>2031</v>
       </c>
       <c r="C294">
-        <v>78258.51262490547</v>
+        <v>78258.51262490549</v>
       </c>
       <c r="D294">
         <v>18658.36468085506</v>
       </c>
       <c r="E294">
-        <v>59600.14794405041</v>
+        <v>59600.14794405042</v>
       </c>
       <c r="F294">
         <v>0</v>
@@ -6548,13 +6548,13 @@
         <v>2032</v>
       </c>
       <c r="C295">
-        <v>74599.21427713789</v>
+        <v>74599.2142771379</v>
       </c>
       <c r="D295">
         <v>17785.9161668391</v>
       </c>
       <c r="E295">
-        <v>56813.29811029878</v>
+        <v>56813.29811029879</v>
       </c>
       <c r="F295">
         <v>0</v>
@@ -6568,13 +6568,13 @@
         <v>2033</v>
       </c>
       <c r="C296">
-        <v>83229.825223869</v>
+        <v>83229.82522386902</v>
       </c>
       <c r="D296">
         <v>19843.62313137756</v>
       </c>
       <c r="E296">
-        <v>63386.20209249144</v>
+        <v>63386.20209249145</v>
       </c>
       <c r="F296">
         <v>0</v>
@@ -6588,13 +6588,13 @@
         <v>2034</v>
       </c>
       <c r="C297">
-        <v>73723.90626539658</v>
+        <v>73723.9062653966</v>
       </c>
       <c r="D297">
         <v>17577.22556509687</v>
       </c>
       <c r="E297">
-        <v>56146.68070029971</v>
+        <v>56146.68070029972</v>
       </c>
       <c r="F297">
         <v>0</v>
@@ -6608,13 +6608,13 @@
         <v>2035</v>
       </c>
       <c r="C298">
-        <v>70449.43694571852</v>
+        <v>70449.43694571854</v>
       </c>
       <c r="D298">
         <v>16796.52784093158</v>
       </c>
       <c r="E298">
-        <v>53652.90910478694</v>
+        <v>53652.90910478695</v>
       </c>
       <c r="F298">
         <v>0</v>
@@ -6628,13 +6628,13 @@
         <v>2036</v>
       </c>
       <c r="C299">
-        <v>70732.71985272031</v>
+        <v>70732.71985272033</v>
       </c>
       <c r="D299">
-        <v>16864.06804338886</v>
+        <v>16864.06804338887</v>
       </c>
       <c r="E299">
-        <v>53868.65180933145</v>
+        <v>53868.65180933146</v>
       </c>
       <c r="F299">
         <v>0</v>
@@ -6648,13 +6648,13 @@
         <v>2037</v>
       </c>
       <c r="C300">
-        <v>84821.27627132577</v>
+        <v>84821.27627132578</v>
       </c>
       <c r="D300">
-        <v>20223.05628208795</v>
+        <v>20223.05628208796</v>
       </c>
       <c r="E300">
-        <v>64598.21998923781</v>
+        <v>64598.21998923782</v>
       </c>
       <c r="F300">
         <v>0</v>
@@ -6668,13 +6668,13 @@
         <v>2038</v>
       </c>
       <c r="C301">
-        <v>82418.58191055825</v>
+        <v>82418.58191055826</v>
       </c>
       <c r="D301">
-        <v>19650.2068105588</v>
+        <v>19650.20681055881</v>
       </c>
       <c r="E301">
-        <v>62768.37509999944</v>
+        <v>62768.37509999945</v>
       </c>
       <c r="F301">
         <v>0</v>
@@ -6688,13 +6688,13 @@
         <v>2039</v>
       </c>
       <c r="C302">
-        <v>72483.70931147336</v>
+        <v>72483.70931147337</v>
       </c>
       <c r="D302">
-        <v>17281.53828116782</v>
+        <v>17281.53828116783</v>
       </c>
       <c r="E302">
-        <v>55202.17103030553</v>
+        <v>55202.17103030554</v>
       </c>
       <c r="F302">
         <v>0</v>
@@ -6708,13 +6708,13 @@
         <v>2040</v>
       </c>
       <c r="C303">
-        <v>91229.27089785061</v>
+        <v>91229.27089785063</v>
       </c>
       <c r="D303">
         <v>21750.84791272789</v>
       </c>
       <c r="E303">
-        <v>69478.42298512271</v>
+        <v>69478.42298512273</v>
       </c>
       <c r="F303">
         <v>0</v>
@@ -6728,13 +6728,13 @@
         <v>2041</v>
       </c>
       <c r="C304">
-        <v>75507.45721353272</v>
+        <v>75507.45721353273</v>
       </c>
       <c r="D304">
         <v>18002.45910073422</v>
       </c>
       <c r="E304">
-        <v>57504.99811279849</v>
+        <v>57504.9981127985</v>
       </c>
       <c r="F304">
         <v>0</v>
@@ -6748,13 +6748,13 @@
         <v>2042</v>
       </c>
       <c r="C305">
-        <v>83746.7789177088</v>
+        <v>83746.77891770881</v>
       </c>
       <c r="D305">
-        <v>19966.87503355731</v>
+        <v>19966.87503355732</v>
       </c>
       <c r="E305">
-        <v>63779.90388415148</v>
+        <v>63779.90388415149</v>
       </c>
       <c r="F305">
         <v>0</v>
@@ -6768,13 +6768,13 @@
         <v>2043</v>
       </c>
       <c r="C306">
-        <v>81911.06305458808</v>
+        <v>81911.0630545881</v>
       </c>
       <c r="D306">
         <v>19529.20435881929</v>
       </c>
       <c r="E306">
-        <v>62381.85869576879</v>
+        <v>62381.85869576881</v>
       </c>
       <c r="F306">
         <v>0</v>
@@ -6788,13 +6788,13 @@
         <v>2044</v>
       </c>
       <c r="C307">
-        <v>73807.50452860985</v>
+        <v>73807.50452860986</v>
       </c>
       <c r="D307">
-        <v>17597.15703107291</v>
+        <v>17597.15703107292</v>
       </c>
       <c r="E307">
-        <v>56210.34749753692</v>
+        <v>56210.34749753694</v>
       </c>
       <c r="F307">
         <v>0</v>
@@ -6808,7 +6808,7 @@
         <v>2045</v>
       </c>
       <c r="C308">
-        <v>76743.64214808078</v>
+        <v>76743.64214808079</v>
       </c>
       <c r="D308">
         <v>18297.18984053666</v>
@@ -6828,10 +6828,10 @@
         <v>2046</v>
       </c>
       <c r="C309">
-        <v>85047.46479224972</v>
+        <v>85047.46479224974</v>
       </c>
       <c r="D309">
-        <v>20276.98406282984</v>
+        <v>20276.98406282985</v>
       </c>
       <c r="E309">
         <v>64770.48072941988</v>
@@ -6848,13 +6848,13 @@
         <v>2047</v>
       </c>
       <c r="C310">
-        <v>87463.96212920183</v>
+        <v>87463.96212920184</v>
       </c>
       <c r="D310">
-        <v>20853.1244346674</v>
+        <v>20853.12443466741</v>
       </c>
       <c r="E310">
-        <v>66610.83769453442</v>
+        <v>66610.83769453444</v>
       </c>
       <c r="F310">
         <v>0</v>
@@ -6868,13 +6868,13 @@
         <v>2048</v>
       </c>
       <c r="C311">
-        <v>72264.15433881662</v>
+        <v>72264.15433881663</v>
       </c>
       <c r="D311">
-        <v>17229.19206846941</v>
+        <v>17229.19206846942</v>
       </c>
       <c r="E311">
-        <v>55034.9622703472</v>
+        <v>55034.96227034721</v>
       </c>
       <c r="F311">
         <v>0</v>
@@ -6888,13 +6888,13 @@
         <v>2049</v>
       </c>
       <c r="C312">
-        <v>86124.25555154201</v>
+        <v>86124.25555154202</v>
       </c>
       <c r="D312">
-        <v>20533.71210426538</v>
+        <v>20533.71210426539</v>
       </c>
       <c r="E312">
-        <v>65590.54344727662</v>
+        <v>65590.54344727664</v>
       </c>
       <c r="F312">
         <v>0</v>
@@ -6908,13 +6908,13 @@
         <v>2050</v>
       </c>
       <c r="C313">
-        <v>85455.65718520385</v>
+        <v>85455.65718520386</v>
       </c>
       <c r="D313">
         <v>20374.3051372054</v>
       </c>
       <c r="E313">
-        <v>65081.35204799844</v>
+        <v>65081.35204799845</v>
       </c>
       <c r="F313">
         <v>0</v>
@@ -6948,16 +6948,16 @@
         <v>2026</v>
       </c>
       <c r="C315">
-        <v>0</v>
+        <v>32796.58685675026</v>
       </c>
       <c r="D315">
         <v>0</v>
       </c>
       <c r="E315">
-        <v>0</v>
+        <v>32796.58685675026</v>
       </c>
       <c r="F315">
-        <v>0</v>
+        <v>32796.58685675026</v>
       </c>
     </row>
     <row r="316" spans="1:6">
@@ -6968,16 +6968,16 @@
         <v>2027</v>
       </c>
       <c r="C316">
-        <v>0</v>
+        <v>57383.93074828545</v>
       </c>
       <c r="D316">
         <v>0</v>
       </c>
       <c r="E316">
-        <v>0</v>
+        <v>57383.93074828545</v>
       </c>
       <c r="F316">
-        <v>0</v>
+        <v>57383.93074828545</v>
       </c>
     </row>
     <row r="317" spans="1:6">
@@ -6988,16 +6988,16 @@
         <v>2028</v>
       </c>
       <c r="C317">
-        <v>0</v>
+        <v>63527.20104949955</v>
       </c>
       <c r="D317">
         <v>0</v>
       </c>
       <c r="E317">
-        <v>0</v>
+        <v>63527.20104949955</v>
       </c>
       <c r="F317">
-        <v>0</v>
+        <v>63527.20104949955</v>
       </c>
     </row>
     <row r="318" spans="1:6">
@@ -7008,16 +7008,16 @@
         <v>2029</v>
       </c>
       <c r="C318">
-        <v>0</v>
+        <v>68145.76004186686</v>
       </c>
       <c r="D318">
         <v>0</v>
       </c>
       <c r="E318">
-        <v>0</v>
+        <v>68145.76004186686</v>
       </c>
       <c r="F318">
-        <v>0</v>
+        <v>68145.76004186686</v>
       </c>
     </row>
     <row r="319" spans="1:6">
@@ -7028,16 +7028,16 @@
         <v>2030</v>
       </c>
       <c r="C319">
-        <v>0</v>
+        <v>79742.02009536952</v>
       </c>
       <c r="D319">
         <v>0</v>
       </c>
       <c r="E319">
-        <v>0</v>
+        <v>79742.02009536952</v>
       </c>
       <c r="F319">
-        <v>0</v>
+        <v>79742.02009536952</v>
       </c>
     </row>
     <row r="320" spans="1:6">
@@ -7048,16 +7048,16 @@
         <v>2031</v>
       </c>
       <c r="C320">
-        <v>0</v>
+        <v>83838.94531260688</v>
       </c>
       <c r="D320">
         <v>0</v>
       </c>
       <c r="E320">
-        <v>0</v>
+        <v>83838.94531260688</v>
       </c>
       <c r="F320">
-        <v>0</v>
+        <v>83838.94531260688</v>
       </c>
     </row>
     <row r="321" spans="1:6">
@@ -7068,16 +7068,16 @@
         <v>2032</v>
       </c>
       <c r="C321">
-        <v>0</v>
+        <v>92820.518523587</v>
       </c>
       <c r="D321">
         <v>0</v>
       </c>
       <c r="E321">
-        <v>0</v>
+        <v>92820.518523587</v>
       </c>
       <c r="F321">
-        <v>0</v>
+        <v>92820.518523587</v>
       </c>
     </row>
     <row r="322" spans="1:6">
@@ -7088,16 +7088,16 @@
         <v>2033</v>
       </c>
       <c r="C322">
-        <v>0</v>
+        <v>96131.31108837241</v>
       </c>
       <c r="D322">
         <v>0</v>
       </c>
       <c r="E322">
-        <v>0</v>
+        <v>96131.31108837241</v>
       </c>
       <c r="F322">
-        <v>0</v>
+        <v>96131.31108837241</v>
       </c>
     </row>
     <row r="323" spans="1:6">
@@ -7108,16 +7108,16 @@
         <v>2034</v>
       </c>
       <c r="C323">
-        <v>0</v>
+        <v>102154.5607737415</v>
       </c>
       <c r="D323">
         <v>0</v>
       </c>
       <c r="E323">
-        <v>0</v>
+        <v>102154.5607737415</v>
       </c>
       <c r="F323">
-        <v>0</v>
+        <v>102154.5607737415</v>
       </c>
     </row>
     <row r="324" spans="1:6">
@@ -7128,16 +7128,16 @@
         <v>2035</v>
       </c>
       <c r="C324">
-        <v>0</v>
+        <v>100850.4977098972</v>
       </c>
       <c r="D324">
         <v>0</v>
       </c>
       <c r="E324">
-        <v>0</v>
+        <v>100850.4977098972</v>
       </c>
       <c r="F324">
-        <v>0</v>
+        <v>100850.4977098972</v>
       </c>
     </row>
     <row r="325" spans="1:6">
@@ -7148,16 +7148,16 @@
         <v>2036</v>
       </c>
       <c r="C325">
-        <v>0</v>
+        <v>98204.37046313824</v>
       </c>
       <c r="D325">
         <v>0</v>
       </c>
       <c r="E325">
-        <v>0</v>
+        <v>98204.37046313824</v>
       </c>
       <c r="F325">
-        <v>0</v>
+        <v>98204.37046313824</v>
       </c>
     </row>
     <row r="326" spans="1:6">
@@ -7168,16 +7168,16 @@
         <v>2037</v>
       </c>
       <c r="C326">
-        <v>0</v>
+        <v>96466.05101983748</v>
       </c>
       <c r="D326">
         <v>0</v>
       </c>
       <c r="E326">
-        <v>0</v>
+        <v>96466.05101983748</v>
       </c>
       <c r="F326">
-        <v>0</v>
+        <v>96466.05101983748</v>
       </c>
     </row>
     <row r="327" spans="1:6">
@@ -7188,16 +7188,16 @@
         <v>2038</v>
       </c>
       <c r="C327">
-        <v>0</v>
+        <v>101729.3739547848</v>
       </c>
       <c r="D327">
         <v>0</v>
       </c>
       <c r="E327">
-        <v>0</v>
+        <v>101729.3739547848</v>
       </c>
       <c r="F327">
-        <v>0</v>
+        <v>101729.3739547848</v>
       </c>
     </row>
     <row r="328" spans="1:6">
@@ -7208,16 +7208,16 @@
         <v>2039</v>
       </c>
       <c r="C328">
-        <v>0</v>
+        <v>103510.7240469388</v>
       </c>
       <c r="D328">
         <v>0</v>
       </c>
       <c r="E328">
-        <v>0</v>
+        <v>103510.7240469388</v>
       </c>
       <c r="F328">
-        <v>0</v>
+        <v>103510.7240469388</v>
       </c>
     </row>
     <row r="329" spans="1:6">
@@ -7228,16 +7228,16 @@
         <v>2040</v>
       </c>
       <c r="C329">
-        <v>0</v>
+        <v>99786.3616189317</v>
       </c>
       <c r="D329">
         <v>0</v>
       </c>
       <c r="E329">
-        <v>0</v>
+        <v>99786.3616189317</v>
       </c>
       <c r="F329">
-        <v>0</v>
+        <v>99786.3616189317</v>
       </c>
     </row>
     <row r="330" spans="1:6">
@@ -7248,16 +7248,16 @@
         <v>2041</v>
       </c>
       <c r="C330">
-        <v>0</v>
+        <v>105625.7687010712</v>
       </c>
       <c r="D330">
         <v>0</v>
       </c>
       <c r="E330">
-        <v>0</v>
+        <v>105625.7687010712</v>
       </c>
       <c r="F330">
-        <v>0</v>
+        <v>105625.7687010712</v>
       </c>
     </row>
     <row r="331" spans="1:6">
@@ -7268,16 +7268,16 @@
         <v>2042</v>
       </c>
       <c r="C331">
-        <v>0</v>
+        <v>101929.2012371724</v>
       </c>
       <c r="D331">
         <v>0</v>
       </c>
       <c r="E331">
-        <v>0</v>
+        <v>101929.2012371724</v>
       </c>
       <c r="F331">
-        <v>0</v>
+        <v>101929.2012371724</v>
       </c>
     </row>
     <row r="332" spans="1:6">
@@ -7288,16 +7288,16 @@
         <v>2043</v>
       </c>
       <c r="C332">
-        <v>0</v>
+        <v>102975.0698501281</v>
       </c>
       <c r="D332">
         <v>0</v>
       </c>
       <c r="E332">
-        <v>0</v>
+        <v>102975.0698501281</v>
       </c>
       <c r="F332">
-        <v>0</v>
+        <v>102975.0698501281</v>
       </c>
     </row>
     <row r="333" spans="1:6">
@@ -7308,16 +7308,16 @@
         <v>2044</v>
       </c>
       <c r="C333">
-        <v>0</v>
+        <v>102522.7211616277</v>
       </c>
       <c r="D333">
         <v>0</v>
       </c>
       <c r="E333">
-        <v>0</v>
+        <v>102522.7211616277</v>
       </c>
       <c r="F333">
-        <v>0</v>
+        <v>102522.7211616277</v>
       </c>
     </row>
     <row r="334" spans="1:6">
@@ -7328,16 +7328,16 @@
         <v>2045</v>
       </c>
       <c r="C334">
-        <v>0</v>
+        <v>98538.22313310886</v>
       </c>
       <c r="D334">
         <v>0</v>
       </c>
       <c r="E334">
-        <v>0</v>
+        <v>98538.22313310886</v>
       </c>
       <c r="F334">
-        <v>0</v>
+        <v>98538.22313310886</v>
       </c>
     </row>
     <row r="335" spans="1:6">
@@ -7348,16 +7348,16 @@
         <v>2046</v>
       </c>
       <c r="C335">
-        <v>0</v>
+        <v>97057.34503861617</v>
       </c>
       <c r="D335">
         <v>0</v>
       </c>
       <c r="E335">
-        <v>0</v>
+        <v>97057.34503861617</v>
       </c>
       <c r="F335">
-        <v>0</v>
+        <v>97057.34503861617</v>
       </c>
     </row>
     <row r="336" spans="1:6">
@@ -7368,16 +7368,16 @@
         <v>2047</v>
       </c>
       <c r="C336">
-        <v>0</v>
+        <v>99266.35475068688</v>
       </c>
       <c r="D336">
         <v>0</v>
       </c>
       <c r="E336">
-        <v>0</v>
+        <v>99266.35475068688</v>
       </c>
       <c r="F336">
-        <v>0</v>
+        <v>99266.35475068688</v>
       </c>
     </row>
     <row r="337" spans="1:6">
@@ -7388,16 +7388,16 @@
         <v>2048</v>
       </c>
       <c r="C337">
-        <v>0</v>
+        <v>101276.2820638496</v>
       </c>
       <c r="D337">
         <v>0</v>
       </c>
       <c r="E337">
-        <v>0</v>
+        <v>101276.2820638496</v>
       </c>
       <c r="F337">
-        <v>0</v>
+        <v>101276.2820638496</v>
       </c>
     </row>
     <row r="338" spans="1:6">
@@ -7408,16 +7408,16 @@
         <v>2049</v>
       </c>
       <c r="C338">
-        <v>0</v>
+        <v>96149.87974452588</v>
       </c>
       <c r="D338">
         <v>0</v>
       </c>
       <c r="E338">
-        <v>0</v>
+        <v>96149.87974452588</v>
       </c>
       <c r="F338">
-        <v>0</v>
+        <v>96149.87974452588</v>
       </c>
     </row>
     <row r="339" spans="1:6">
@@ -7428,16 +7428,16 @@
         <v>2050</v>
       </c>
       <c r="C339">
-        <v>0</v>
+        <v>98186.47975212552</v>
       </c>
       <c r="D339">
         <v>0</v>
       </c>
       <c r="E339">
-        <v>0</v>
+        <v>98186.47975212552</v>
       </c>
       <c r="F339">
-        <v>0</v>
+        <v>98186.47975212552</v>
       </c>
     </row>
     <row r="340" spans="1:6">
@@ -7448,10 +7448,10 @@
         <v>2025</v>
       </c>
       <c r="C340">
-        <v>0</v>
+        <v>39326.29004948001</v>
       </c>
       <c r="D340">
-        <v>0</v>
+        <v>39326.29004948001</v>
       </c>
       <c r="E340">
         <v>0</v>
@@ -7468,13 +7468,13 @@
         <v>2026</v>
       </c>
       <c r="C341">
-        <v>0</v>
+        <v>80106.13249300426</v>
       </c>
       <c r="D341">
-        <v>0</v>
+        <v>44576.49673152481</v>
       </c>
       <c r="E341">
-        <v>0</v>
+        <v>35529.63576147945</v>
       </c>
       <c r="F341">
         <v>0</v>
@@ -7488,13 +7488,13 @@
         <v>2027</v>
       </c>
       <c r="C342">
-        <v>0</v>
+        <v>95805.55965580525</v>
       </c>
       <c r="D342">
-        <v>0</v>
+        <v>33639.634678496</v>
       </c>
       <c r="E342">
-        <v>0</v>
+        <v>62165.92497730925</v>
       </c>
       <c r="F342">
         <v>0</v>
@@ -7508,13 +7508,13 @@
         <v>2028</v>
       </c>
       <c r="C343">
-        <v>0</v>
+        <v>103225.8276081462</v>
       </c>
       <c r="D343">
-        <v>0</v>
+        <v>34404.69313785505</v>
       </c>
       <c r="E343">
-        <v>0</v>
+        <v>68821.13447029119</v>
       </c>
       <c r="F343">
         <v>0</v>
@@ -7528,13 +7528,13 @@
         <v>2029</v>
       </c>
       <c r="C344">
-        <v>0</v>
+        <v>118470.315967819</v>
       </c>
       <c r="D344">
-        <v>0</v>
+        <v>44645.74258912993</v>
       </c>
       <c r="E344">
-        <v>0</v>
+        <v>73824.57337868909</v>
       </c>
       <c r="F344">
         <v>0</v>
@@ -7548,13 +7548,13 @@
         <v>2030</v>
       </c>
       <c r="C345">
-        <v>0</v>
+        <v>127115.3682796919</v>
       </c>
       <c r="D345">
-        <v>0</v>
+        <v>40728.1798430416</v>
       </c>
       <c r="E345">
-        <v>0</v>
+        <v>86387.18843665032</v>
       </c>
       <c r="F345">
         <v>0</v>
@@ -7568,13 +7568,13 @@
         <v>2031</v>
       </c>
       <c r="C346">
-        <v>0</v>
+        <v>138995.1132540111</v>
       </c>
       <c r="D346">
-        <v>0</v>
+        <v>48169.58916535361</v>
       </c>
       <c r="E346">
-        <v>0</v>
+        <v>90825.52408865748</v>
       </c>
       <c r="F346">
         <v>0</v>
@@ -7588,13 +7588,13 @@
         <v>2032</v>
       </c>
       <c r="C347">
-        <v>0</v>
+        <v>145750.9352205967</v>
       </c>
       <c r="D347">
-        <v>0</v>
+        <v>45195.37348671073</v>
       </c>
       <c r="E347">
-        <v>0</v>
+        <v>100555.5617338859</v>
       </c>
       <c r="F347">
         <v>0</v>
@@ -7608,13 +7608,13 @@
         <v>2033</v>
       </c>
       <c r="C348">
-        <v>0</v>
+        <v>153779.1038185924</v>
       </c>
       <c r="D348">
-        <v>0</v>
+        <v>49636.85013952225</v>
       </c>
       <c r="E348">
-        <v>0</v>
+        <v>104142.2536790701</v>
       </c>
       <c r="F348">
         <v>0</v>
@@ -7628,13 +7628,13 @@
         <v>2034</v>
       </c>
       <c r="C349">
-        <v>0</v>
+        <v>153953.1847875851</v>
       </c>
       <c r="D349">
-        <v>0</v>
+        <v>43285.74394936513</v>
       </c>
       <c r="E349">
-        <v>0</v>
+        <v>110667.4408382199</v>
       </c>
       <c r="F349">
         <v>0</v>
@@ -7648,13 +7648,13 @@
         <v>2035</v>
       </c>
       <c r="C350">
-        <v>0</v>
+        <v>149980.5337310351</v>
       </c>
       <c r="D350">
-        <v>0</v>
+        <v>40725.82787864641</v>
       </c>
       <c r="E350">
-        <v>0</v>
+        <v>109254.7058523887</v>
       </c>
       <c r="F350">
         <v>0</v>
@@ -7668,13 +7668,13 @@
         <v>2036</v>
       </c>
       <c r="C351">
-        <v>0</v>
+        <v>146651.6018301565</v>
       </c>
       <c r="D351">
-        <v>0</v>
+        <v>40263.53382842337</v>
       </c>
       <c r="E351">
-        <v>0</v>
+        <v>106388.0680017331</v>
       </c>
       <c r="F351">
         <v>0</v>
@@ -7688,13 +7688,13 @@
         <v>2037</v>
       </c>
       <c r="C352">
-        <v>0</v>
+        <v>152053.4687735046</v>
       </c>
       <c r="D352">
-        <v>0</v>
+        <v>47548.58016868064</v>
       </c>
       <c r="E352">
-        <v>0</v>
+        <v>104504.888604824</v>
       </c>
       <c r="F352">
         <v>0</v>
@@ -7708,13 +7708,13 @@
         <v>2038</v>
       </c>
       <c r="C353">
-        <v>0</v>
+        <v>155709.8206907659</v>
       </c>
       <c r="D353">
-        <v>0</v>
+        <v>45502.99890641568</v>
       </c>
       <c r="E353">
-        <v>0</v>
+        <v>110206.8217843502</v>
       </c>
       <c r="F353">
         <v>0</v>
@@ -7728,13 +7728,13 @@
         <v>2039</v>
       </c>
       <c r="C354">
-        <v>0</v>
+        <v>151553.0397731369</v>
       </c>
       <c r="D354">
-        <v>0</v>
+        <v>39416.42205561985</v>
       </c>
       <c r="E354">
-        <v>0</v>
+        <v>112136.617717517</v>
       </c>
       <c r="F354">
         <v>0</v>
@@ -7748,13 +7748,13 @@
         <v>2040</v>
       </c>
       <c r="C355">
-        <v>0</v>
+        <v>156970.6800413339</v>
       </c>
       <c r="D355">
-        <v>0</v>
+        <v>48868.78828749121</v>
       </c>
       <c r="E355">
-        <v>0</v>
+        <v>108101.8917538427</v>
       </c>
       <c r="F355">
         <v>0</v>
@@ -7768,13 +7768,13 @@
         <v>2041</v>
       </c>
       <c r="C356">
-        <v>0</v>
+        <v>154273.9760511113</v>
       </c>
       <c r="D356">
-        <v>0</v>
+        <v>39846.05995828417</v>
       </c>
       <c r="E356">
-        <v>0</v>
+        <v>114427.9160928271</v>
       </c>
       <c r="F356">
         <v>0</v>
@@ -7788,13 +7788,13 @@
         <v>2042</v>
       </c>
       <c r="C357">
-        <v>0</v>
+        <v>153964.2986577101</v>
       </c>
       <c r="D357">
-        <v>0</v>
+        <v>43540.99731744001</v>
       </c>
       <c r="E357">
-        <v>0</v>
+        <v>110423.3013402701</v>
       </c>
       <c r="F357">
         <v>0</v>
@@ -7808,13 +7808,13 @@
         <v>2043</v>
       </c>
       <c r="C358">
-        <v>0</v>
+        <v>153517.0595726243</v>
       </c>
       <c r="D358">
-        <v>0</v>
+        <v>41960.73390165217</v>
       </c>
       <c r="E358">
-        <v>0</v>
+        <v>111556.3256709721</v>
       </c>
       <c r="F358">
         <v>0</v>
@@ -7828,13 +7828,13 @@
         <v>2044</v>
       </c>
       <c r="C359">
-        <v>0</v>
+        <v>148323.1050889702</v>
       </c>
       <c r="D359">
-        <v>0</v>
+        <v>37256.82383054017</v>
       </c>
       <c r="E359">
-        <v>0</v>
+        <v>111066.28125843</v>
       </c>
       <c r="F359">
         <v>0</v>
@@ -7848,13 +7848,13 @@
         <v>2045</v>
       </c>
       <c r="C360">
-        <v>0</v>
+        <v>144925.360130493</v>
       </c>
       <c r="D360">
-        <v>0</v>
+        <v>38175.61840295841</v>
       </c>
       <c r="E360">
-        <v>0</v>
+        <v>106749.7417275346</v>
       </c>
       <c r="F360">
         <v>0</v>
@@ -7868,13 +7868,13 @@
         <v>2046</v>
       </c>
       <c r="C361">
-        <v>0</v>
+        <v>146839.6958505739</v>
       </c>
       <c r="D361">
-        <v>0</v>
+        <v>41694.23872540641</v>
       </c>
       <c r="E361">
-        <v>0</v>
+        <v>105145.4571251675</v>
       </c>
       <c r="F361">
         <v>0</v>
@@ -7888,13 +7888,13 @@
         <v>2047</v>
       </c>
       <c r="C362">
-        <v>0</v>
+        <v>149800.2100468657</v>
       </c>
       <c r="D362">
-        <v>0</v>
+        <v>42261.65906695489</v>
       </c>
       <c r="E362">
-        <v>0</v>
+        <v>107538.5509799108</v>
       </c>
       <c r="F362">
         <v>0</v>
@@ -7908,13 +7908,13 @@
         <v>2048</v>
       </c>
       <c r="C363">
-        <v>0</v>
+        <v>144133.0394498838</v>
       </c>
       <c r="D363">
-        <v>0</v>
+        <v>34417.06721404673</v>
       </c>
       <c r="E363">
-        <v>0</v>
+        <v>109715.9722358371</v>
       </c>
       <c r="F363">
         <v>0</v>
@@ -7928,13 +7928,13 @@
         <v>2049</v>
       </c>
       <c r="C364">
-        <v>0</v>
+        <v>144595.7364125772</v>
       </c>
       <c r="D364">
-        <v>0</v>
+        <v>40433.3666893408</v>
       </c>
       <c r="E364">
-        <v>0</v>
+        <v>104162.3697232364</v>
       </c>
       <c r="F364">
         <v>0</v>
@@ -7948,13 +7948,13 @@
         <v>2050</v>
       </c>
       <c r="C365">
-        <v>0</v>
+        <v>145918.808232128</v>
       </c>
       <c r="D365">
-        <v>0</v>
+        <v>39550.12183399201</v>
       </c>
       <c r="E365">
-        <v>0</v>
+        <v>106368.686398136</v>
       </c>
       <c r="F365">
         <v>0</v>
@@ -8018,16 +8018,16 @@
         <v>2026</v>
       </c>
       <c r="C3">
-        <v>-131436.9879283817</v>
+        <v>-98640.40107163147</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>-131436.9879283817</v>
+        <v>-98640.40107163147</v>
       </c>
       <c r="F3">
-        <v>-131436.9879283817</v>
+        <v>-98640.40107163147</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8038,16 +8038,16 @@
         <v>2027</v>
       </c>
       <c r="C4">
-        <v>-99188.8684805939</v>
+        <v>-41804.93773230843</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>-99188.8684805939</v>
+        <v>-41804.93773230843</v>
       </c>
       <c r="F4">
-        <v>-99188.8684805939</v>
+        <v>-41804.93773230843</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8058,16 +8058,16 @@
         <v>2028</v>
       </c>
       <c r="C5">
-        <v>-101444.6952430469</v>
+        <v>-37917.49419354729</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>-101444.6952430469</v>
+        <v>-37917.49419354729</v>
       </c>
       <c r="F5">
-        <v>-101444.6952430469</v>
+        <v>-37917.49419354729</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8078,16 +8078,16 @@
         <v>2029</v>
       </c>
       <c r="C6">
-        <v>-131641.1611336631</v>
+        <v>-63495.40109179623</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>-131641.1611336631</v>
+        <v>-63495.40109179623</v>
       </c>
       <c r="F6">
-        <v>-131641.1611336631</v>
+        <v>-63495.40109179623</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8098,16 +8098,16 @@
         <v>2030</v>
       </c>
       <c r="C7">
-        <v>-120089.9450549113</v>
+        <v>-40347.92495954176</v>
       </c>
       <c r="D7">
         <v>0</v>
       </c>
       <c r="E7">
-        <v>-120089.9450549113</v>
+        <v>-40347.92495954176</v>
       </c>
       <c r="F7">
-        <v>-120089.9450549113</v>
+        <v>-40347.92495954176</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8118,16 +8118,16 @@
         <v>2031</v>
       </c>
       <c r="C8">
-        <v>-142031.4744989855</v>
+        <v>-58192.52918637858</v>
       </c>
       <c r="D8">
         <v>0</v>
       </c>
       <c r="E8">
-        <v>-142031.4744989855</v>
+        <v>-58192.52918637858</v>
       </c>
       <c r="F8">
-        <v>-142031.4744989855</v>
+        <v>-58192.52918637858</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8138,16 +8138,16 @@
         <v>2032</v>
       </c>
       <c r="C9">
-        <v>-133261.7868225299</v>
+        <v>-40441.26829894294</v>
       </c>
       <c r="D9">
         <v>0</v>
       </c>
       <c r="E9">
-        <v>-133261.7868225299</v>
+        <v>-40441.26829894294</v>
       </c>
       <c r="F9">
-        <v>-133261.7868225299</v>
+        <v>-40441.26829894294</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8158,16 +8158,16 @@
         <v>2033</v>
       </c>
       <c r="C10">
-        <v>-146357.795133677</v>
+        <v>-50226.48404530459</v>
       </c>
       <c r="D10">
         <v>0</v>
       </c>
       <c r="E10">
-        <v>-146357.795133677</v>
+        <v>-50226.48404530459</v>
       </c>
       <c r="F10">
-        <v>-146357.795133677</v>
+        <v>-50226.48404530459</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -8178,16 +8178,16 @@
         <v>2034</v>
       </c>
       <c r="C11">
-        <v>-127631.1071215566</v>
+        <v>-25476.54634781508</v>
       </c>
       <c r="D11">
         <v>0</v>
       </c>
       <c r="E11">
-        <v>-127631.1071215566</v>
+        <v>-25476.54634781508</v>
       </c>
       <c r="F11">
-        <v>-127631.1071215566</v>
+        <v>-25476.54634781508</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -8198,16 +8198,16 @@
         <v>2035</v>
       </c>
       <c r="C12">
-        <v>-120083.0104718946</v>
+        <v>-19232.51276199729</v>
       </c>
       <c r="D12">
         <v>0</v>
       </c>
       <c r="E12">
-        <v>-120083.0104718946</v>
+        <v>-19232.51276199729</v>
       </c>
       <c r="F12">
-        <v>-120083.0104718946</v>
+        <v>-19232.51276199729</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -8218,16 +8218,16 @@
         <v>2036</v>
       </c>
       <c r="C13">
-        <v>-118719.9049958083</v>
+        <v>-20515.53453267011</v>
       </c>
       <c r="D13">
         <v>0</v>
       </c>
       <c r="E13">
-        <v>-118719.9049958083</v>
+        <v>-20515.53453267011</v>
       </c>
       <c r="F13">
-        <v>-118719.9049958083</v>
+        <v>-20515.53453267011</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -8238,16 +8238,16 @@
         <v>2037</v>
       </c>
       <c r="C14">
-        <v>-140200.3815465098</v>
+        <v>-43734.3305266723</v>
       </c>
       <c r="D14">
         <v>0</v>
       </c>
       <c r="E14">
-        <v>-140200.3815465098</v>
+        <v>-43734.3305266723</v>
       </c>
       <c r="F14">
-        <v>-140200.3815465098</v>
+        <v>-43734.3305266723</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -8258,16 +8258,16 @@
         <v>2038</v>
       </c>
       <c r="C15">
-        <v>-134168.8429857742</v>
+        <v>-32439.46903098945</v>
       </c>
       <c r="D15">
         <v>0</v>
       </c>
       <c r="E15">
-        <v>-134168.8429857742</v>
+        <v>-32439.46903098945</v>
       </c>
       <c r="F15">
-        <v>-134168.8429857742</v>
+        <v>-32439.46903098945</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -8278,16 +8278,16 @@
         <v>2039</v>
       </c>
       <c r="C16">
-        <v>-116222.1351057133</v>
+        <v>-12711.41105877457</v>
       </c>
       <c r="D16">
         <v>0</v>
       </c>
       <c r="E16">
-        <v>-116222.1351057133</v>
+        <v>-12711.41105877457</v>
       </c>
       <c r="F16">
-        <v>-116222.1351057133</v>
+        <v>-12711.41105877457</v>
       </c>
     </row>
     <row r="17" spans="1:6">
@@ -8298,16 +8298,16 @@
         <v>2040</v>
       </c>
       <c r="C17">
-        <v>-144093.1122214027</v>
+        <v>-44306.75060247094</v>
       </c>
       <c r="D17">
         <v>0</v>
       </c>
       <c r="E17">
-        <v>-144093.1122214027</v>
+        <v>-44306.75060247094</v>
       </c>
       <c r="F17">
-        <v>-144093.1122214027</v>
+        <v>-44306.75060247094</v>
       </c>
     </row>
     <row r="18" spans="1:6">
@@ -8318,16 +8318,16 @@
         <v>2041</v>
       </c>
       <c r="C18">
-        <v>-117488.9546701407</v>
+        <v>-11863.18596906948</v>
       </c>
       <c r="D18">
         <v>0</v>
       </c>
       <c r="E18">
-        <v>-117488.9546701407</v>
+        <v>-11863.18596906948</v>
       </c>
       <c r="F18">
-        <v>-117488.9546701407</v>
+        <v>-11863.18596906948</v>
       </c>
     </row>
     <row r="19" spans="1:6">
@@ -8338,16 +8338,16 @@
         <v>2042</v>
       </c>
       <c r="C19">
-        <v>-128383.7426617088</v>
+        <v>-26454.54142453638</v>
       </c>
       <c r="D19">
         <v>0</v>
       </c>
       <c r="E19">
-        <v>-128383.7426617088</v>
+        <v>-26454.54142453638</v>
       </c>
       <c r="F19">
-        <v>-128383.7426617088</v>
+        <v>-26454.54142453638</v>
       </c>
     </row>
     <row r="20" spans="1:6">
@@ -8358,16 +8358,16 @@
         <v>2043</v>
       </c>
       <c r="C20">
-        <v>-123724.2235363001</v>
+        <v>-20749.15368617198</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>-123724.2235363001</v>
+        <v>-20749.15368617198</v>
       </c>
       <c r="F20">
-        <v>-123724.2235363001</v>
+        <v>-20749.15368617198</v>
       </c>
     </row>
     <row r="21" spans="1:6">
@@ -8378,16 +8378,16 @@
         <v>2044</v>
       </c>
       <c r="C21">
-        <v>-109854.4073700498</v>
+        <v>-7331.686208422121</v>
       </c>
       <c r="D21">
         <v>0</v>
       </c>
       <c r="E21">
-        <v>-109854.4073700498</v>
+        <v>-7331.686208422121</v>
       </c>
       <c r="F21">
-        <v>-109854.4073700498</v>
+        <v>-7331.686208422121</v>
       </c>
     </row>
     <row r="22" spans="1:6">
@@ -8398,16 +8398,16 @@
         <v>2045</v>
       </c>
       <c r="C22">
-        <v>-112563.5405230088</v>
+        <v>-14025.31738989992</v>
       </c>
       <c r="D22">
         <v>0</v>
       </c>
       <c r="E22">
-        <v>-112563.5405230088</v>
+        <v>-14025.31738989992</v>
       </c>
       <c r="F22">
-        <v>-112563.5405230088</v>
+        <v>-14025.31738989992</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -8418,16 +8418,16 @@
         <v>2046</v>
       </c>
       <c r="C23">
-        <v>-122938.4412817697</v>
+        <v>-25881.09624315356</v>
       </c>
       <c r="D23">
         <v>0</v>
       </c>
       <c r="E23">
-        <v>-122938.4412817697</v>
+        <v>-25881.09624315356</v>
       </c>
       <c r="F23">
-        <v>-122938.4412817697</v>
+        <v>-25881.09624315356</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -8438,16 +8438,16 @@
         <v>2047</v>
       </c>
       <c r="C24">
-        <v>-124611.5205928498</v>
+        <v>-25345.16584216297</v>
       </c>
       <c r="D24">
         <v>0</v>
       </c>
       <c r="E24">
-        <v>-124611.5205928498</v>
+        <v>-25345.16584216297</v>
       </c>
       <c r="F24">
-        <v>-124611.5205928498</v>
+        <v>-25345.16584216297</v>
       </c>
     </row>
     <row r="25" spans="1:6">
@@ -8458,16 +8458,16 @@
         <v>2048</v>
       </c>
       <c r="C25">
-        <v>-101481.1837465606</v>
+        <v>-204.9016827109735</v>
       </c>
       <c r="D25">
         <v>0</v>
       </c>
       <c r="E25">
-        <v>-101481.1837465606</v>
+        <v>-204.9016827109735</v>
       </c>
       <c r="F25">
-        <v>-101481.1837465606</v>
+        <v>-204.9016827109735</v>
       </c>
     </row>
     <row r="26" spans="1:6">
@@ -8478,16 +8478,16 @@
         <v>2049</v>
       </c>
       <c r="C26">
-        <v>-119220.668901142</v>
+        <v>-23070.78915661614</v>
       </c>
       <c r="D26">
         <v>0</v>
       </c>
       <c r="E26">
-        <v>-119220.668901142</v>
+        <v>-23070.78915661614</v>
       </c>
       <c r="F26">
-        <v>-119220.668901142</v>
+        <v>-23070.78915661614</v>
       </c>
     </row>
     <row r="27" spans="1:6">
@@ -8498,16 +8498,16 @@
         <v>2050</v>
       </c>
       <c r="C27">
-        <v>-116616.3586122278</v>
+        <v>-18429.87886010227</v>
       </c>
       <c r="D27">
         <v>0</v>
       </c>
       <c r="E27">
-        <v>-116616.3586122278</v>
+        <v>-18429.87886010227</v>
       </c>
       <c r="F27">
-        <v>-116616.3586122278</v>
+        <v>-18429.87886010227</v>
       </c>
     </row>
     <row r="28" spans="1:6">
@@ -8558,16 +8558,16 @@
         <v>2027</v>
       </c>
       <c r="C30">
-        <v>-247393.3621199913</v>
+        <v>-214596.7752632411</v>
       </c>
       <c r="D30">
         <v>0</v>
       </c>
       <c r="E30">
-        <v>-247393.3621199913</v>
+        <v>-214596.7752632411</v>
       </c>
       <c r="F30">
-        <v>-247393.3621199913</v>
+        <v>-214596.7752632411</v>
       </c>
     </row>
     <row r="31" spans="1:6">
@@ -8578,16 +8578,16 @@
         <v>2028</v>
       </c>
       <c r="C31">
-        <v>-346582.2306005852</v>
+        <v>-256401.7129955495</v>
       </c>
       <c r="D31">
         <v>0</v>
       </c>
       <c r="E31">
-        <v>-346582.2306005852</v>
+        <v>-256401.7129955495</v>
       </c>
       <c r="F31">
-        <v>-346582.2306005852</v>
+        <v>-256401.7129955495</v>
       </c>
     </row>
     <row r="32" spans="1:6">
@@ -8598,16 +8598,16 @@
         <v>2029</v>
       </c>
       <c r="C32">
-        <v>-448026.9258436321</v>
+        <v>-294319.2071890968</v>
       </c>
       <c r="D32">
         <v>0</v>
       </c>
       <c r="E32">
-        <v>-448026.9258436321</v>
+        <v>-294319.2071890968</v>
       </c>
       <c r="F32">
-        <v>-448026.9258436321</v>
+        <v>-294319.2071890968</v>
       </c>
     </row>
     <row r="33" spans="1:6">
@@ -8618,16 +8618,16 @@
         <v>2030</v>
       </c>
       <c r="C33">
-        <v>-579668.0869772951</v>
+        <v>-357814.6082808931</v>
       </c>
       <c r="D33">
         <v>0</v>
       </c>
       <c r="E33">
-        <v>-579668.0869772951</v>
+        <v>-357814.6082808931</v>
       </c>
       <c r="F33">
-        <v>-579668.0869772951</v>
+        <v>-357814.6082808931</v>
       </c>
     </row>
     <row r="34" spans="1:6">
@@ -8638,16 +8638,16 @@
         <v>2031</v>
       </c>
       <c r="C34">
-        <v>-699758.0320322064</v>
+        <v>-398162.5332404348</v>
       </c>
       <c r="D34">
         <v>0</v>
       </c>
       <c r="E34">
-        <v>-699758.0320322064</v>
+        <v>-398162.5332404348</v>
       </c>
       <c r="F34">
-        <v>-699758.0320322064</v>
+        <v>-398162.5332404348</v>
       </c>
     </row>
     <row r="35" spans="1:6">
@@ -8658,16 +8658,16 @@
         <v>2032</v>
       </c>
       <c r="C35">
-        <v>-841789.5065311919</v>
+        <v>-456355.0624268134</v>
       </c>
       <c r="D35">
         <v>0</v>
       </c>
       <c r="E35">
-        <v>-841789.5065311919</v>
+        <v>-456355.0624268134</v>
       </c>
       <c r="F35">
-        <v>-841789.5065311919</v>
+        <v>-456355.0624268134</v>
       </c>
     </row>
     <row r="36" spans="1:6">
@@ -8678,16 +8678,16 @@
         <v>2033</v>
       </c>
       <c r="C36">
-        <v>-975051.2933537217</v>
+        <v>-496796.3307257564</v>
       </c>
       <c r="D36">
         <v>0</v>
       </c>
       <c r="E36">
-        <v>-975051.2933537217</v>
+        <v>-496796.3307257564</v>
       </c>
       <c r="F36">
-        <v>-975051.2933537217</v>
+        <v>-496796.3307257564</v>
       </c>
     </row>
     <row r="37" spans="1:6">
@@ -8698,16 +8698,16 @@
         <v>2034</v>
       </c>
       <c r="C37">
-        <v>-1121409.088487399</v>
+        <v>-547022.8147710609</v>
       </c>
       <c r="D37">
         <v>0</v>
       </c>
       <c r="E37">
-        <v>-1121409.088487399</v>
+        <v>-547022.8147710609</v>
       </c>
       <c r="F37">
-        <v>-1121409.088487399</v>
+        <v>-547022.8147710609</v>
       </c>
     </row>
     <row r="38" spans="1:6">
@@ -8718,16 +8718,16 @@
         <v>2035</v>
       </c>
       <c r="C38">
-        <v>-1249040.195608955</v>
+        <v>-572499.361118876</v>
       </c>
       <c r="D38">
         <v>0</v>
       </c>
       <c r="E38">
-        <v>-1249040.195608955</v>
+        <v>-572499.361118876</v>
       </c>
       <c r="F38">
-        <v>-1249040.195608955</v>
+        <v>-572499.361118876</v>
       </c>
     </row>
     <row r="39" spans="1:6">
@@ -8738,16 +8738,16 @@
         <v>2036</v>
       </c>
       <c r="C39">
-        <v>-1369123.20608085</v>
+        <v>-591731.8738808733</v>
       </c>
       <c r="D39">
         <v>0</v>
       </c>
       <c r="E39">
-        <v>-1369123.20608085</v>
+        <v>-591731.8738808733</v>
       </c>
       <c r="F39">
-        <v>-1369123.20608085</v>
+        <v>-591731.8738808733</v>
       </c>
     </row>
     <row r="40" spans="1:6">
@@ -8758,16 +8758,16 @@
         <v>2037</v>
       </c>
       <c r="C40">
-        <v>-1487843.111076658</v>
+        <v>-612247.4084135434</v>
       </c>
       <c r="D40">
         <v>0</v>
       </c>
       <c r="E40">
-        <v>-1487843.111076658</v>
+        <v>-612247.4084135434</v>
       </c>
       <c r="F40">
-        <v>-1487843.111076658</v>
+        <v>-612247.4084135434</v>
       </c>
     </row>
     <row r="41" spans="1:6">
@@ -8778,16 +8778,16 @@
         <v>2038</v>
       </c>
       <c r="C41">
-        <v>-1628043.492623168</v>
+        <v>-655981.7389402157</v>
       </c>
       <c r="D41">
         <v>0</v>
       </c>
       <c r="E41">
-        <v>-1628043.492623168</v>
+        <v>-655981.7389402157</v>
       </c>
       <c r="F41">
-        <v>-1628043.492623168</v>
+        <v>-655981.7389402157</v>
       </c>
     </row>
     <row r="42" spans="1:6">
@@ -8798,16 +8798,16 @@
         <v>2039</v>
       </c>
       <c r="C42">
-        <v>-1762212.335608942</v>
+        <v>-688421.2079712051</v>
       </c>
       <c r="D42">
         <v>0</v>
       </c>
       <c r="E42">
-        <v>-1762212.335608942</v>
+        <v>-688421.2079712051</v>
       </c>
       <c r="F42">
-        <v>-1762212.335608942</v>
+        <v>-688421.2079712051</v>
       </c>
     </row>
     <row r="43" spans="1:6">
@@ -8818,16 +8818,16 @@
         <v>2040</v>
       </c>
       <c r="C43">
-        <v>-1878434.470714655</v>
+        <v>-701132.6190299797</v>
       </c>
       <c r="D43">
         <v>0</v>
       </c>
       <c r="E43">
-        <v>-1878434.470714655</v>
+        <v>-701132.6190299797</v>
       </c>
       <c r="F43">
-        <v>-1878434.470714655</v>
+        <v>-701132.6190299797</v>
       </c>
     </row>
     <row r="44" spans="1:6">
@@ -8838,16 +8838,16 @@
         <v>2041</v>
       </c>
       <c r="C44">
-        <v>-2022527.582936058</v>
+        <v>-745439.3696324506</v>
       </c>
       <c r="D44">
         <v>0</v>
       </c>
       <c r="E44">
-        <v>-2022527.582936058</v>
+        <v>-745439.3696324506</v>
       </c>
       <c r="F44">
-        <v>-2022527.582936058</v>
+        <v>-745439.3696324506</v>
       </c>
     </row>
     <row r="45" spans="1:6">
@@ -8858,16 +8858,16 @@
         <v>2042</v>
       </c>
       <c r="C45">
-        <v>-2140016.537606199</v>
+        <v>-757302.5556015201</v>
       </c>
       <c r="D45">
         <v>0</v>
       </c>
       <c r="E45">
-        <v>-2140016.537606199</v>
+        <v>-757302.5556015201</v>
       </c>
       <c r="F45">
-        <v>-2140016.537606199</v>
+        <v>-757302.5556015201</v>
       </c>
     </row>
     <row r="46" spans="1:6">
@@ -8878,16 +8878,16 @@
         <v>2043</v>
       </c>
       <c r="C46">
-        <v>-2268400.280267908</v>
+        <v>-783757.0970260565</v>
       </c>
       <c r="D46">
         <v>0</v>
       </c>
       <c r="E46">
-        <v>-2268400.280267908</v>
+        <v>-783757.0970260565</v>
       </c>
       <c r="F46">
-        <v>-2268400.280267908</v>
+        <v>-783757.0970260565</v>
       </c>
     </row>
     <row r="47" spans="1:6">
@@ -8898,16 +8898,16 @@
         <v>2044</v>
       </c>
       <c r="C47">
-        <v>-2392124.503804208</v>
+        <v>-804506.2507122285</v>
       </c>
       <c r="D47">
         <v>0</v>
       </c>
       <c r="E47">
-        <v>-2392124.503804208</v>
+        <v>-804506.2507122285</v>
       </c>
       <c r="F47">
-        <v>-2392124.503804208</v>
+        <v>-804506.2507122285</v>
       </c>
     </row>
     <row r="48" spans="1:6">
@@ -8918,16 +8918,16 @@
         <v>2045</v>
       </c>
       <c r="C48">
-        <v>-2501978.911174258</v>
+        <v>-811837.9369206505</v>
       </c>
       <c r="D48">
         <v>0</v>
       </c>
       <c r="E48">
-        <v>-2501978.911174258</v>
+        <v>-811837.9369206505</v>
       </c>
       <c r="F48">
-        <v>-2501978.911174258</v>
+        <v>-811837.9369206505</v>
       </c>
     </row>
     <row r="49" spans="1:6">
@@ -8938,16 +8938,16 @@
         <v>2046</v>
       </c>
       <c r="C49">
-        <v>-2614542.451697267</v>
+        <v>-825863.2543105504</v>
       </c>
       <c r="D49">
         <v>0</v>
       </c>
       <c r="E49">
-        <v>-2614542.451697267</v>
+        <v>-825863.2543105504</v>
       </c>
       <c r="F49">
-        <v>-2614542.451697267</v>
+        <v>-825863.2543105504</v>
       </c>
     </row>
     <row r="50" spans="1:6">
@@ -8958,16 +8958,16 @@
         <v>2047</v>
       </c>
       <c r="C50">
-        <v>-2737480.892979037</v>
+        <v>-851744.350553704</v>
       </c>
       <c r="D50">
         <v>0</v>
       </c>
       <c r="E50">
-        <v>-2737480.892979037</v>
+        <v>-851744.350553704</v>
       </c>
       <c r="F50">
-        <v>-2737480.892979037</v>
+        <v>-851744.350553704</v>
       </c>
     </row>
     <row r="51" spans="1:6">
@@ -8978,16 +8978,16 @@
         <v>2048</v>
       </c>
       <c r="C51">
-        <v>-2862092.413571886</v>
+        <v>-877089.5163958669</v>
       </c>
       <c r="D51">
         <v>0</v>
       </c>
       <c r="E51">
-        <v>-2862092.413571886</v>
+        <v>-877089.5163958669</v>
       </c>
       <c r="F51">
-        <v>-2862092.413571886</v>
+        <v>-877089.5163958669</v>
       </c>
     </row>
     <row r="52" spans="1:6">
@@ -8998,16 +8998,16 @@
         <v>2049</v>
       </c>
       <c r="C52">
-        <v>-2963573.597318447</v>
+        <v>-877294.4180785778</v>
       </c>
       <c r="D52">
         <v>0</v>
       </c>
       <c r="E52">
-        <v>-2963573.597318447</v>
+        <v>-877294.4180785778</v>
       </c>
       <c r="F52">
-        <v>-2963573.597318447</v>
+        <v>-877294.4180785778</v>
       </c>
     </row>
     <row r="53" spans="1:6">
@@ -9018,16 +9018,16 @@
         <v>2050</v>
       </c>
       <c r="C53">
-        <v>-3082794.266219589</v>
+        <v>-900365.207235194</v>
       </c>
       <c r="D53">
         <v>0</v>
       </c>
       <c r="E53">
-        <v>-3082794.266219589</v>
+        <v>-900365.207235194</v>
       </c>
       <c r="F53">
-        <v>-3082794.266219589</v>
+        <v>-900365.207235194</v>
       </c>
     </row>
     <row r="54" spans="1:6">
@@ -9038,10 +9038,10 @@
         <v>2025</v>
       </c>
       <c r="C54">
-        <v>-164945.6975903904</v>
+        <v>-125619.4075409104</v>
       </c>
       <c r="D54">
-        <v>-39326.29020092187</v>
+        <v>-0.00015144185454119</v>
       </c>
       <c r="E54">
         <v>-125619.4073894685</v>
@@ -9058,13 +9058,13 @@
         <v>2026</v>
       </c>
       <c r="C55">
-        <v>-186966.5601539384</v>
+        <v>-106860.4276609341</v>
       </c>
       <c r="D55">
-        <v>-44576.49584010887</v>
+        <v>0.0008914159407140687</v>
       </c>
       <c r="E55">
-        <v>-142390.0643138295</v>
+        <v>-106860.42855235</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -9078,13 +9078,13 @@
         <v>2027</v>
       </c>
       <c r="C56">
-        <v>-141094.2363658061</v>
+        <v>-45288.67671000079</v>
       </c>
       <c r="D56">
-        <v>-33639.63392836272</v>
+        <v>0.0007501333020627499</v>
       </c>
       <c r="E56">
-        <v>-107454.6024374434</v>
+        <v>-45288.67746013409</v>
       </c>
       <c r="F56">
         <v>0</v>
@@ -9098,13 +9098,13 @@
         <v>2028</v>
       </c>
       <c r="C57">
-        <v>-144303.1128844892</v>
+        <v>-41077.28527634294</v>
       </c>
       <c r="D57">
-        <v>-34404.69304197494</v>
+        <v>9.588011016603559E-05</v>
       </c>
       <c r="E57">
-        <v>-109898.4198425142</v>
+        <v>-41077.28537222301</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -9118,13 +9118,13 @@
         <v>2029</v>
       </c>
       <c r="C58">
-        <v>-187257.000217265</v>
+        <v>-68786.68424944597</v>
       </c>
       <c r="D58">
-        <v>-44645.74244904269</v>
+        <v>0.0001400872424710542</v>
       </c>
       <c r="E58">
-        <v>-142611.2577682223</v>
+        <v>-68786.68438953318</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -9138,13 +9138,13 @@
         <v>2030</v>
       </c>
       <c r="C59">
-        <v>-170825.6252525288</v>
+        <v>-43710.25697283685</v>
       </c>
       <c r="D59">
-        <v>-40728.1803076642</v>
+        <v>-0.0004646225861506537</v>
       </c>
       <c r="E59">
-        <v>-130097.4449448646</v>
+        <v>-43710.25650821428</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -9158,13 +9158,13 @@
         <v>2031</v>
       </c>
       <c r="C60">
-        <v>-202037.0195392545</v>
+        <v>-63041.90628524346</v>
       </c>
       <c r="D60">
-        <v>-48169.58900898871</v>
+        <v>0.0001563648984301835</v>
       </c>
       <c r="E60">
-        <v>-153867.4305302658</v>
+        <v>-63041.90644160839</v>
       </c>
       <c r="F60">
         <v>0</v>
@@ -9178,13 +9178,13 @@
         <v>2032</v>
       </c>
       <c r="C61">
-        <v>-189562.3095111181</v>
+        <v>-43811.37429052143</v>
       </c>
       <c r="D61">
-        <v>-45195.37341012471</v>
+        <v>7.658601680304855E-05</v>
       </c>
       <c r="E61">
-        <v>-144366.9361009934</v>
+        <v>-43811.37436710746</v>
       </c>
       <c r="F61">
         <v>0</v>
@@ -9198,13 +9198,13 @@
         <v>2033</v>
       </c>
       <c r="C62">
-        <v>-208191.134434339</v>
+        <v>-54412.03061574663</v>
       </c>
       <c r="D62">
-        <v>-49636.85073105502</v>
+        <v>-0.0005915327637922019</v>
       </c>
       <c r="E62">
-        <v>-158554.283703284</v>
+        <v>-54412.03002421389</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -9218,13 +9218,13 @@
         <v>2034</v>
       </c>
       <c r="C63">
-        <v>-181552.7782310514</v>
+        <v>-27599.59344346635</v>
       </c>
       <c r="D63">
-        <v>-43285.74402242484</v>
+        <v>-7.305970939341933E-05</v>
       </c>
       <c r="E63">
-        <v>-138267.0342086266</v>
+        <v>-27599.59337040666</v>
       </c>
       <c r="F63">
         <v>0</v>
@@ -9238,13 +9238,13 @@
         <v>2035</v>
       </c>
       <c r="C64">
-        <v>-170815.7600898655</v>
+        <v>-20835.2263588304</v>
       </c>
       <c r="D64">
-        <v>-40725.82825935107</v>
+        <v>-0.0003807046596193686</v>
       </c>
       <c r="E64">
-        <v>-130089.9318305145</v>
+        <v>-20835.22597812576</v>
       </c>
       <c r="F64">
         <v>0</v>
@@ -9258,13 +9258,13 @@
         <v>2036</v>
       </c>
       <c r="C65">
-        <v>-168876.7652072157</v>
+        <v>-22225.16337705927</v>
       </c>
       <c r="D65">
-        <v>-40263.53384023535</v>
+        <v>-1.181197876576334E-05</v>
       </c>
       <c r="E65">
-        <v>-128613.2313669804</v>
+        <v>-22225.16336524725</v>
       </c>
       <c r="F65">
         <v>0</v>
@@ -9278,13 +9278,13 @@
         <v>2037</v>
       </c>
       <c r="C66">
-        <v>-199432.3339440663</v>
+        <v>-47378.86517056165</v>
       </c>
       <c r="D66">
-        <v>-47548.58086452102</v>
+        <v>-0.0006958403828321025</v>
       </c>
       <c r="E66">
-        <v>-151883.7530795452</v>
+        <v>-47378.86447472125</v>
       </c>
       <c r="F66">
         <v>0</v>
@@ -9298,13 +9298,13 @@
         <v>2038</v>
       </c>
       <c r="C67">
-        <v>-190852.5777743378</v>
+        <v>-35142.75708357192</v>
       </c>
       <c r="D67">
-        <v>-45502.99867648614</v>
+        <v>0.000229929544730112</v>
       </c>
       <c r="E67">
-        <v>-145349.5790978516</v>
+        <v>-35142.75731350138</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -9318,13 +9318,13 @@
         <v>2039</v>
       </c>
       <c r="C68">
-        <v>-165323.7367201426</v>
+        <v>-13770.69694700575</v>
       </c>
       <c r="D68">
-        <v>-39416.42214580506</v>
+        <v>-9.018521814141423E-05</v>
       </c>
       <c r="E68">
-        <v>-125907.3145743376</v>
+        <v>-13770.69685682055</v>
       </c>
       <c r="F68">
         <v>0</v>
@@ -9338,13 +9338,13 @@
         <v>2040</v>
       </c>
       <c r="C69">
-        <v>-204969.6612606774</v>
+        <v>-47998.98121934349</v>
       </c>
       <c r="D69">
-        <v>-48868.78832777544</v>
+        <v>-4.028421244584024E-05</v>
       </c>
       <c r="E69">
-        <v>-156100.872932902</v>
+        <v>-47998.98117905925</v>
       </c>
       <c r="F69">
         <v>0</v>
@@ -9358,13 +9358,13 @@
         <v>2041</v>
       </c>
       <c r="C70">
-        <v>-167125.7593176033</v>
+        <v>-12851.78326649201</v>
       </c>
       <c r="D70">
-        <v>-39846.05968501716</v>
+        <v>0.0002732670109253377</v>
       </c>
       <c r="E70">
-        <v>-127279.6996325861</v>
+        <v>-12851.783539759</v>
       </c>
       <c r="F70">
         <v>0</v>
@@ -9378,13 +9378,13 @@
         <v>2042</v>
       </c>
       <c r="C71">
-        <v>-182623.3810342913</v>
+        <v>-28659.08237658109</v>
       </c>
       <c r="D71">
-        <v>-43540.9967337425</v>
+        <v>0.0005836975033162162</v>
       </c>
       <c r="E71">
-        <v>-139082.3843005488</v>
+        <v>-28659.08296027867</v>
       </c>
       <c r="F71">
         <v>0</v>
@@ -9398,13 +9398,13 @@
         <v>2043</v>
       </c>
       <c r="C72">
-        <v>-175995.3043326439</v>
+        <v>-22478.24476001959</v>
       </c>
       <c r="D72">
-        <v>-41960.73321883565</v>
+        <v>0.0006828165205661207</v>
       </c>
       <c r="E72">
-        <v>-134034.5711138083</v>
+        <v>-22478.24544283608</v>
       </c>
       <c r="F72">
         <v>0</v>
@@ -9418,13 +9418,13 @@
         <v>2044</v>
       </c>
       <c r="C73">
-        <v>-156265.7628480942</v>
+        <v>-7942.657759124006</v>
       </c>
       <c r="D73">
-        <v>-37256.82347588925</v>
+        <v>0.0003546509105945006</v>
       </c>
       <c r="E73">
-        <v>-119008.9393722049</v>
+        <v>-7942.658113774902</v>
       </c>
       <c r="F73">
         <v>0</v>
@@ -9438,13 +9438,13 @@
         <v>2045</v>
       </c>
       <c r="C74">
-        <v>-160119.4480695512</v>
+        <v>-15194.0879390582</v>
       </c>
       <c r="D74">
-        <v>-38175.61763406348</v>
+        <v>0.000768894940847531</v>
       </c>
       <c r="E74">
-        <v>-121943.8304354877</v>
+        <v>-15194.08870795311</v>
       </c>
       <c r="F74">
         <v>0</v>
@@ -9458,13 +9458,13 @@
         <v>2046</v>
       </c>
       <c r="C75">
-        <v>-174877.5496139904</v>
+        <v>-28037.85376341635</v>
       </c>
       <c r="D75">
-        <v>-41694.23856585975</v>
+        <v>0.0001595466746948659</v>
       </c>
       <c r="E75">
-        <v>-133183.3110481306</v>
+        <v>-28037.85392296308</v>
       </c>
       <c r="F75">
         <v>0</v>
@@ -9478,13 +9478,13 @@
         <v>2047</v>
       </c>
       <c r="C76">
-        <v>-177257.4727425422</v>
+        <v>-27457.26269567653</v>
       </c>
       <c r="D76">
-        <v>-42261.65892890394</v>
+        <v>0.0001380509493174031</v>
       </c>
       <c r="E76">
-        <v>-134995.8138136383</v>
+        <v>-27457.26283372747</v>
       </c>
       <c r="F76">
         <v>0</v>
@@ -9498,13 +9498,13 @@
         <v>2048</v>
       </c>
       <c r="C77">
-        <v>-144355.0106394874</v>
+        <v>-221.9711896035587</v>
       </c>
       <c r="D77">
-        <v>-34417.06648489375</v>
+        <v>0.0007291529764188454</v>
       </c>
       <c r="E77">
-        <v>-109937.9441545937</v>
+        <v>-221.9719187565497</v>
       </c>
       <c r="F77">
         <v>0</v>
@@ -9518,13 +9518,13 @@
         <v>2049</v>
       </c>
       <c r="C78">
-        <v>-169589.093165578</v>
+        <v>-24993.35675300081</v>
       </c>
       <c r="D78">
-        <v>-40433.36679991853</v>
+        <v>-0.0001105777337215841</v>
       </c>
       <c r="E78">
-        <v>-129155.7263656595</v>
+        <v>-24993.35664242308</v>
       </c>
       <c r="F78">
         <v>0</v>
@@ -9538,13 +9538,13 @@
         <v>2050</v>
       </c>
       <c r="C79">
-        <v>-165884.5116305721</v>
+        <v>-19965.70339844417</v>
       </c>
       <c r="D79">
-        <v>-39550.12188570197</v>
+        <v>-5.170995427761227E-05</v>
       </c>
       <c r="E79">
-        <v>-126334.3897448702</v>
+        <v>-19965.70334673417</v>
       </c>
       <c r="F79">
         <v>0</v>
@@ -9578,10 +9578,10 @@
         <v>2026</v>
       </c>
       <c r="C81">
-        <v>-164945.6975903904</v>
+        <v>-125619.4075409104</v>
       </c>
       <c r="D81">
-        <v>-39326.29020092187</v>
+        <v>-0.00015144185454119</v>
       </c>
       <c r="E81">
         <v>-125619.4073894685</v>
@@ -9598,13 +9598,13 @@
         <v>2027</v>
       </c>
       <c r="C82">
-        <v>-351912.2577443288</v>
+        <v>-232479.8352018445</v>
       </c>
       <c r="D82">
-        <v>-83902.78604103073</v>
+        <v>0.0007399740861728787</v>
       </c>
       <c r="E82">
-        <v>-268009.471703298</v>
+        <v>-232479.8359418185</v>
       </c>
       <c r="F82">
         <v>0</v>
@@ -9618,13 +9618,13 @@
         <v>2028</v>
       </c>
       <c r="C83">
-        <v>-493006.4941101348</v>
+        <v>-277768.5119118453</v>
       </c>
       <c r="D83">
-        <v>-117542.4199693934</v>
+        <v>0.001490107388235629</v>
       </c>
       <c r="E83">
-        <v>-375464.0741407414</v>
+        <v>-277768.5134019526</v>
       </c>
       <c r="F83">
         <v>0</v>
@@ -9638,13 +9638,13 @@
         <v>2029</v>
       </c>
       <c r="C84">
-        <v>-637309.606994624</v>
+        <v>-318845.7971881882</v>
       </c>
       <c r="D84">
-        <v>-151947.1130113684</v>
+        <v>0.001585987498401664</v>
       </c>
       <c r="E84">
-        <v>-485362.4939832556</v>
+        <v>-318845.7987741756</v>
       </c>
       <c r="F84">
         <v>0</v>
@@ -9658,13 +9658,13 @@
         <v>2030</v>
       </c>
       <c r="C85">
-        <v>-824566.607211889</v>
+        <v>-387632.4814376342</v>
       </c>
       <c r="D85">
-        <v>-196592.8554604111</v>
+        <v>0.001726074740872718</v>
       </c>
       <c r="E85">
-        <v>-627973.7517514778</v>
+        <v>-387632.4831637088</v>
       </c>
       <c r="F85">
         <v>0</v>
@@ -9678,13 +9678,13 @@
         <v>2031</v>
       </c>
       <c r="C86">
-        <v>-995392.2324644178</v>
+        <v>-431342.7384104711</v>
       </c>
       <c r="D86">
-        <v>-237321.0357680753</v>
+        <v>0.001261452154722065</v>
       </c>
       <c r="E86">
-        <v>-758071.1966963424</v>
+        <v>-431342.739671923</v>
       </c>
       <c r="F86">
         <v>0</v>
@@ -9698,13 +9698,13 @@
         <v>2032</v>
       </c>
       <c r="C87">
-        <v>-1197429.252003672</v>
+        <v>-494384.6446957145</v>
       </c>
       <c r="D87">
-        <v>-285490.624777064</v>
+        <v>0.001417817053152248</v>
       </c>
       <c r="E87">
-        <v>-911938.6272266083</v>
+        <v>-494384.6461135314</v>
       </c>
       <c r="F87">
         <v>0</v>
@@ -9718,13 +9718,13 @@
         <v>2033</v>
       </c>
       <c r="C88">
-        <v>-1386991.56151479</v>
+        <v>-538196.018986236</v>
       </c>
       <c r="D88">
-        <v>-330685.9981871886</v>
+        <v>0.001494403069955297</v>
       </c>
       <c r="E88">
-        <v>-1056305.563327602</v>
+        <v>-538196.0204806388</v>
       </c>
       <c r="F88">
         <v>0</v>
@@ -9738,13 +9738,13 @@
         <v>2034</v>
       </c>
       <c r="C89">
-        <v>-1595182.695949129</v>
+        <v>-592608.0496019826</v>
       </c>
       <c r="D89">
-        <v>-380322.8489182437</v>
+        <v>0.0009028703061630949</v>
       </c>
       <c r="E89">
-        <v>-1214859.847030886</v>
+        <v>-592608.0505048528</v>
       </c>
       <c r="F89">
         <v>0</v>
@@ -9758,13 +9758,13 @@
         <v>2035</v>
       </c>
       <c r="C90">
-        <v>-1776735.474180181</v>
+        <v>-620207.6430454489</v>
       </c>
       <c r="D90">
-        <v>-423608.5929406685</v>
+        <v>0.0008298105967696756</v>
       </c>
       <c r="E90">
-        <v>-1353126.881239512</v>
+        <v>-620207.6438752594</v>
       </c>
       <c r="F90">
         <v>0</v>
@@ -9778,13 +9778,13 @@
         <v>2036</v>
       </c>
       <c r="C91">
-        <v>-1947551.234270046</v>
+        <v>-641042.8694042794</v>
       </c>
       <c r="D91">
-        <v>-464334.4212000196</v>
+        <v>0.000449105937150307</v>
       </c>
       <c r="E91">
-        <v>-1483216.813070026</v>
+        <v>-641042.8698533853</v>
       </c>
       <c r="F91">
         <v>0</v>
@@ -9798,13 +9798,13 @@
         <v>2037</v>
       </c>
       <c r="C92">
-        <v>-2116427.999477262</v>
+        <v>-663268.0327813387</v>
       </c>
       <c r="D92">
-        <v>-504597.955040255</v>
+        <v>0.0004372939583845437</v>
       </c>
       <c r="E92">
-        <v>-1611830.044437007</v>
+        <v>-663268.0332186325</v>
       </c>
       <c r="F92">
         <v>0</v>
@@ -9818,13 +9818,13 @@
         <v>2038</v>
       </c>
       <c r="C93">
-        <v>-2315860.333421328</v>
+        <v>-710646.8979519003</v>
       </c>
       <c r="D93">
-        <v>-552146.535904776</v>
+        <v>-0.0002585464244475588</v>
       </c>
       <c r="E93">
-        <v>-1763713.797516552</v>
+        <v>-710646.8976933537</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -9838,13 +9838,13 @@
         <v>2039</v>
       </c>
       <c r="C94">
-        <v>-2506712.911195666</v>
+        <v>-745789.6550354722</v>
       </c>
       <c r="D94">
-        <v>-597649.5345812622</v>
+        <v>-2.861687971744686E-05</v>
       </c>
       <c r="E94">
-        <v>-1909063.376614404</v>
+        <v>-745789.655006855</v>
       </c>
       <c r="F94">
         <v>0</v>
@@ -9858,13 +9858,13 @@
         <v>2040</v>
       </c>
       <c r="C95">
-        <v>-2672036.647915808</v>
+        <v>-759560.3519824781</v>
       </c>
       <c r="D95">
-        <v>-637065.9567270672</v>
+        <v>-0.0001188020978588611</v>
       </c>
       <c r="E95">
-        <v>-2034970.691188741</v>
+        <v>-759560.3518636755</v>
       </c>
       <c r="F95">
         <v>0</v>
@@ -9878,13 +9878,13 @@
         <v>2041</v>
       </c>
       <c r="C96">
-        <v>-2877006.309176486</v>
+        <v>-807559.3332018215</v>
       </c>
       <c r="D96">
-        <v>-685934.7450548427</v>
+        <v>-0.0001590863103047013</v>
       </c>
       <c r="E96">
-        <v>-2191071.564121643</v>
+        <v>-807559.3330427348</v>
       </c>
       <c r="F96">
         <v>0</v>
@@ -9898,13 +9898,13 @@
         <v>2042</v>
       </c>
       <c r="C97">
-        <v>-3044132.068494089</v>
+        <v>-820411.1164683136</v>
       </c>
       <c r="D97">
-        <v>-725780.8047398599</v>
+        <v>0.0001141807006206363</v>
       </c>
       <c r="E97">
-        <v>-2318351.263754229</v>
+        <v>-820411.1165824938</v>
       </c>
       <c r="F97">
         <v>0</v>
@@ -9918,13 +9918,13 @@
         <v>2043</v>
       </c>
       <c r="C98">
-        <v>-3226755.449528381</v>
+        <v>-849070.1988448948</v>
       </c>
       <c r="D98">
-        <v>-769321.8014736024</v>
+        <v>0.0006978782039368525</v>
       </c>
       <c r="E98">
-        <v>-2457433.648054778</v>
+        <v>-849070.1995427725</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -9938,13 +9938,13 @@
         <v>2044</v>
       </c>
       <c r="C99">
-        <v>-3402750.753861025</v>
+        <v>-871548.4436049144</v>
       </c>
       <c r="D99">
-        <v>-811282.5346924381</v>
+        <v>0.001380694724502973</v>
       </c>
       <c r="E99">
-        <v>-2591468.219168586</v>
+        <v>-871548.4449856086</v>
       </c>
       <c r="F99">
         <v>0</v>
@@ -9958,13 +9958,13 @@
         <v>2045</v>
       </c>
       <c r="C100">
-        <v>-3559016.516709119</v>
+        <v>-879491.1013640384</v>
       </c>
       <c r="D100">
-        <v>-848539.3581683274</v>
+        <v>0.001735345635097474</v>
       </c>
       <c r="E100">
-        <v>-2710477.15854079</v>
+        <v>-879491.1030993834</v>
       </c>
       <c r="F100">
         <v>0</v>
@@ -9978,13 +9978,13 @@
         <v>2046</v>
       </c>
       <c r="C101">
-        <v>-3719135.96477867</v>
+        <v>-894685.1893030966</v>
       </c>
       <c r="D101">
-        <v>-886714.9758023908</v>
+        <v>0.002504240575945005</v>
       </c>
       <c r="E101">
-        <v>-2832420.988976278</v>
+        <v>-894685.1918073365</v>
       </c>
       <c r="F101">
         <v>0</v>
@@ -9998,13 +9998,13 @@
         <v>2047</v>
       </c>
       <c r="C102">
-        <v>-3894013.51439266</v>
+        <v>-922723.043066513</v>
       </c>
       <c r="D102">
-        <v>-928409.2143682506</v>
+        <v>0.002663787250639871</v>
       </c>
       <c r="E102">
-        <v>-2965604.300024409</v>
+        <v>-922723.0457302995</v>
       </c>
       <c r="F102">
         <v>0</v>
@@ -10018,13 +10018,13 @@
         <v>2048</v>
       </c>
       <c r="C103">
-        <v>-4071270.987135202</v>
+        <v>-950180.3057621896</v>
       </c>
       <c r="D103">
-        <v>-970670.8732971546</v>
+        <v>0.002801838199957274</v>
       </c>
       <c r="E103">
-        <v>-3100600.113838047</v>
+        <v>-950180.3085640271</v>
       </c>
       <c r="F103">
         <v>0</v>
@@ -10038,13 +10038,13 @@
         <v>2049</v>
       </c>
       <c r="C104">
-        <v>-4215625.997774689</v>
+        <v>-950402.2769517931</v>
       </c>
       <c r="D104">
-        <v>-1005087.939782048</v>
+        <v>0.003530991176376119</v>
       </c>
       <c r="E104">
-        <v>-3210538.057992641</v>
+        <v>-950402.2804827837</v>
       </c>
       <c r="F104">
         <v>0</v>
@@ -10058,13 +10058,13 @@
         <v>2050</v>
       </c>
       <c r="C105">
-        <v>-4385215.090940268</v>
+        <v>-975395.6337047939</v>
       </c>
       <c r="D105">
-        <v>-1045521.306581967</v>
+        <v>0.003420413442654535</v>
       </c>
       <c r="E105">
-        <v>-3339693.7843583</v>
+        <v>-975395.6371252068</v>
       </c>
       <c r="F105">
         <v>0</v>
@@ -10078,10 +10078,10 @@
         <v>2025</v>
       </c>
       <c r="C106">
-        <v>280902.071782</v>
+        <v>241575.78173252</v>
       </c>
       <c r="D106">
-        <v>39326.29004948001</v>
+        <v>0</v>
       </c>
       <c r="E106">
         <v>241575.78173252</v>
@@ -10098,16 +10098,16 @@
         <v>2026</v>
       </c>
       <c r="C107">
-        <v>318403.54808232</v>
+        <v>205500.8287325655</v>
       </c>
       <c r="D107">
-        <v>44576.49673152481</v>
+        <v>0</v>
       </c>
       <c r="E107">
-        <v>273827.0513507952</v>
+        <v>205500.8287325655</v>
       </c>
       <c r="F107">
-        <v>131436.9846483817</v>
+        <v>98640.39779163145</v>
       </c>
     </row>
     <row r="108" spans="1:6">
@@ -10118,16 +10118,16 @@
         <v>2027</v>
       </c>
       <c r="C108">
-        <v>240283.1048464</v>
+        <v>87093.61444230931</v>
       </c>
       <c r="D108">
-        <v>33639.634678496</v>
+        <v>0</v>
       </c>
       <c r="E108">
-        <v>206643.470167904</v>
+        <v>87093.61444230932</v>
       </c>
       <c r="F108">
-        <v>99188.86568059392</v>
+        <v>41804.93493230848</v>
       </c>
     </row>
     <row r="109" spans="1:6">
@@ -10138,16 +10138,16 @@
         <v>2028</v>
       </c>
       <c r="C109">
-        <v>245747.808127536</v>
+        <v>78994.77946989023</v>
       </c>
       <c r="D109">
-        <v>34404.69313785505</v>
+        <v>0</v>
       </c>
       <c r="E109">
-        <v>211343.114989681</v>
+        <v>78994.77946989026</v>
       </c>
       <c r="F109">
-        <v>101444.6951950469</v>
+        <v>37917.49414554733</v>
       </c>
     </row>
     <row r="110" spans="1:6">
@@ -10158,16 +10158,16 @@
         <v>2029</v>
       </c>
       <c r="C110">
-        <v>318898.161350928</v>
+        <v>132282.0853412421</v>
       </c>
       <c r="D110">
-        <v>44645.74258912993</v>
+        <v>0</v>
       </c>
       <c r="E110">
-        <v>274252.4187617981</v>
+        <v>132282.0853412421</v>
       </c>
       <c r="F110">
-        <v>131641.1610056631</v>
+        <v>63495.40096379622</v>
       </c>
     </row>
     <row r="111" spans="1:6">
@@ -10178,16 +10178,16 @@
         <v>2030</v>
       </c>
       <c r="C111">
-        <v>290915.57030744</v>
+        <v>84058.18193237856</v>
       </c>
       <c r="D111">
-        <v>40728.1798430416</v>
+        <v>0</v>
       </c>
       <c r="E111">
-        <v>250187.3904643984</v>
+        <v>84058.18193237856</v>
       </c>
       <c r="F111">
-        <v>120089.9474229112</v>
+        <v>40347.92732754172</v>
       </c>
     </row>
     <row r="112" spans="1:6">
@@ -10198,16 +10198,16 @@
         <v>2031</v>
       </c>
       <c r="C112">
-        <v>344068.4940382401</v>
+        <v>121234.4354716221</v>
       </c>
       <c r="D112">
-        <v>48169.58916535361</v>
+        <v>0</v>
       </c>
       <c r="E112">
-        <v>295898.9048728864</v>
+        <v>121234.4354716221</v>
       </c>
       <c r="F112">
-        <v>142031.4743389855</v>
+        <v>58192.5290263786</v>
       </c>
     </row>
     <row r="113" spans="1:6">
@@ -10218,16 +10218,16 @@
         <v>2032</v>
       </c>
       <c r="C113">
-        <v>322824.096333648</v>
+        <v>84252.64258946435</v>
       </c>
       <c r="D113">
-        <v>45195.37348671073</v>
+        <v>0</v>
       </c>
       <c r="E113">
-        <v>277628.7228469373</v>
+        <v>84252.64258946438</v>
       </c>
       <c r="F113">
-        <v>133261.7869665299</v>
+        <v>40441.26844294291</v>
       </c>
     </row>
     <row r="114" spans="1:6">
@@ -10238,16 +10238,16 @@
         <v>2033</v>
       </c>
       <c r="C114">
-        <v>354548.929568016</v>
+        <v>104638.5146610513</v>
       </c>
       <c r="D114">
-        <v>49636.85013952225</v>
+        <v>0</v>
       </c>
       <c r="E114">
-        <v>304912.0794284938</v>
+        <v>104638.5146610513</v>
       </c>
       <c r="F114">
-        <v>146357.798125677</v>
+        <v>50226.4870373046</v>
       </c>
     </row>
     <row r="115" spans="1:6">
@@ -10258,16 +10258,16 @@
         <v>2034</v>
       </c>
       <c r="C115">
-        <v>309183.885352608</v>
+        <v>53076.13979128154</v>
       </c>
       <c r="D115">
-        <v>43285.74394936513</v>
+        <v>0</v>
       </c>
       <c r="E115">
-        <v>265898.1414032429</v>
+        <v>53076.13979128154</v>
       </c>
       <c r="F115">
-        <v>127631.1078735566</v>
+        <v>25476.54709981513</v>
       </c>
     </row>
     <row r="116" spans="1:6">
@@ -10278,16 +10278,16 @@
         <v>2035</v>
       </c>
       <c r="C116">
-        <v>290898.77056176</v>
+        <v>40067.7391208277</v>
       </c>
       <c r="D116">
-        <v>40725.82787864641</v>
+        <v>0</v>
       </c>
       <c r="E116">
-        <v>250172.9426831136</v>
+        <v>40067.7391208277</v>
       </c>
       <c r="F116">
-        <v>120083.0124878945</v>
+        <v>19232.5147779973</v>
       </c>
     </row>
     <row r="117" spans="1:6">
@@ -10298,16 +10298,16 @@
         <v>2036</v>
       </c>
       <c r="C117">
-        <v>287596.670203024</v>
+        <v>42740.69790972929</v>
       </c>
       <c r="D117">
-        <v>40263.53382842337</v>
+        <v>0</v>
       </c>
       <c r="E117">
-        <v>247333.1363746006</v>
+        <v>42740.69790972929</v>
       </c>
       <c r="F117">
-        <v>118719.9054598083</v>
+        <v>20515.53499667006</v>
       </c>
     </row>
     <row r="118" spans="1:6">
@@ -10318,16 +10318,16 @@
         <v>2037</v>
       </c>
       <c r="C118">
-        <v>339632.715490576</v>
+        <v>91113.1956972339</v>
       </c>
       <c r="D118">
-        <v>47548.58016868064</v>
+        <v>0</v>
       </c>
       <c r="E118">
-        <v>292084.1353218954</v>
+        <v>91113.19569723392</v>
       </c>
       <c r="F118">
-        <v>140200.3849545098</v>
+        <v>43734.33393467228</v>
       </c>
     </row>
     <row r="119" spans="1:6">
@@ -10338,16 +10338,16 @@
         <v>2038</v>
       </c>
       <c r="C119">
-        <v>325021.420760112</v>
+        <v>67582.22611456132</v>
       </c>
       <c r="D119">
-        <v>45502.99890641568</v>
+        <v>0</v>
       </c>
       <c r="E119">
-        <v>279518.4218536963</v>
+        <v>67582.22611456129</v>
       </c>
       <c r="F119">
-        <v>134168.8424897742</v>
+        <v>32439.46853498943</v>
       </c>
     </row>
     <row r="120" spans="1:6">
@@ -10358,16 +10358,16 @@
         <v>2039</v>
       </c>
       <c r="C120">
-        <v>281545.871825856</v>
+        <v>26482.10800578038</v>
       </c>
       <c r="D120">
-        <v>39416.42205561985</v>
+        <v>0</v>
       </c>
       <c r="E120">
-        <v>242129.4497702362</v>
+        <v>26482.10800578038</v>
       </c>
       <c r="F120">
-        <v>116222.1358897134</v>
+        <v>12711.4118427746</v>
       </c>
     </row>
     <row r="121" spans="1:6">
@@ -10378,16 +10378,16 @@
         <v>2040</v>
       </c>
       <c r="C121">
-        <v>349062.77348208</v>
+        <v>92305.73182181444</v>
       </c>
       <c r="D121">
-        <v>48868.78828749121</v>
+        <v>0</v>
       </c>
       <c r="E121">
-        <v>300193.9851945888</v>
+        <v>92305.73182181446</v>
       </c>
       <c r="F121">
-        <v>144093.1128934026</v>
+        <v>44306.75127447094</v>
       </c>
     </row>
     <row r="122" spans="1:6">
@@ -10398,16 +10398,16 @@
         <v>2041</v>
       </c>
       <c r="C122">
-        <v>284614.713987744</v>
+        <v>24714.9692355615</v>
       </c>
       <c r="D122">
-        <v>39846.05995828417</v>
+        <v>0</v>
       </c>
       <c r="E122">
-        <v>244768.6540294598</v>
+        <v>24714.9692355615</v>
       </c>
       <c r="F122">
-        <v>117488.9539341407</v>
+        <v>11863.18523306953</v>
       </c>
     </row>
     <row r="123" spans="1:6">
@@ -10418,16 +10418,16 @@
         <v>2042</v>
       </c>
       <c r="C123">
-        <v>311007.123696</v>
+        <v>55113.62380111747</v>
       </c>
       <c r="D123">
-        <v>43540.99731744001</v>
+        <v>0</v>
       </c>
       <c r="E123">
-        <v>267466.12637856</v>
+        <v>55113.62380111747</v>
       </c>
       <c r="F123">
-        <v>128383.7406617088</v>
+        <v>26454.53942453639</v>
       </c>
     </row>
     <row r="124" spans="1:6">
@@ -10438,16 +10438,16 @@
         <v>2043</v>
       </c>
       <c r="C124">
-        <v>299719.527868944</v>
+        <v>43227.3984461916</v>
       </c>
       <c r="D124">
-        <v>41960.73390165217</v>
+        <v>0</v>
       </c>
       <c r="E124">
-        <v>257758.7939672919</v>
+        <v>43227.39844619163</v>
       </c>
       <c r="F124">
-        <v>123724.2211043001</v>
+        <v>20749.15125417199</v>
       </c>
     </row>
     <row r="125" spans="1:6">
@@ -10458,16 +10458,16 @@
         <v>2044</v>
       </c>
       <c r="C125">
-        <v>266120.170218144</v>
+        <v>15274.34396754619</v>
       </c>
       <c r="D125">
-        <v>37256.82383054017</v>
+        <v>0</v>
       </c>
       <c r="E125">
-        <v>228863.3463876038</v>
+        <v>15274.34396754616</v>
       </c>
       <c r="F125">
-        <v>109854.4062660498</v>
+        <v>7331.685104422155</v>
       </c>
     </row>
     <row r="126" spans="1:6">
@@ -10478,16 +10478,16 @@
         <v>2045</v>
       </c>
       <c r="C126">
-        <v>272682.9885925601</v>
+        <v>29219.40532895818</v>
       </c>
       <c r="D126">
-        <v>38175.61840295841</v>
+        <v>0</v>
       </c>
       <c r="E126">
-        <v>234507.3701896016</v>
+        <v>29219.40532895818</v>
       </c>
       <c r="F126">
-        <v>112563.5376910088</v>
+        <v>14025.31455789994</v>
       </c>
     </row>
     <row r="127" spans="1:6">
@@ -10498,16 +10498,16 @@
         <v>2046</v>
       </c>
       <c r="C127">
-        <v>297815.99089576</v>
+        <v>53918.95000656991</v>
       </c>
       <c r="D127">
-        <v>41694.23872540641</v>
+        <v>0</v>
       </c>
       <c r="E127">
-        <v>256121.7521703536</v>
+        <v>53918.95000656991</v>
       </c>
       <c r="F127">
-        <v>122938.4410417697</v>
+        <v>25881.09600315357</v>
       </c>
     </row>
     <row r="128" spans="1:6">
@@ -10518,16 +10518,16 @@
         <v>2047</v>
       </c>
       <c r="C128">
-        <v>301868.993335392</v>
+        <v>52802.42853783947</v>
       </c>
       <c r="D128">
-        <v>42261.65906695489</v>
+        <v>0</v>
       </c>
       <c r="E128">
-        <v>259607.3342684371</v>
+        <v>52802.42853783947</v>
       </c>
       <c r="F128">
-        <v>124611.5204488498</v>
+        <v>25345.16569816295</v>
       </c>
     </row>
     <row r="129" spans="1:6">
@@ -10538,16 +10538,16 @@
         <v>2048</v>
       </c>
       <c r="C129">
-        <v>245836.194386048</v>
+        <v>426.8728723146196</v>
       </c>
       <c r="D129">
-        <v>34417.06721404673</v>
+        <v>0</v>
       </c>
       <c r="E129">
-        <v>211419.1271720013</v>
+        <v>426.8728723146196</v>
       </c>
       <c r="F129">
-        <v>101481.1810425606</v>
+        <v>204.8989787110186</v>
       </c>
     </row>
     <row r="130" spans="1:6">
@@ -10558,16 +10558,16 @@
         <v>2049</v>
       </c>
       <c r="C130">
-        <v>288809.76206672</v>
+        <v>48064.14590961693</v>
       </c>
       <c r="D130">
-        <v>40433.3666893408</v>
+        <v>0</v>
       </c>
       <c r="E130">
-        <v>248376.3953773792</v>
+        <v>48064.14590961693</v>
       </c>
       <c r="F130">
-        <v>119220.669781142</v>
+        <v>23070.79003661613</v>
       </c>
     </row>
     <row r="131" spans="1:6">
@@ -10578,16 +10578,16 @@
         <v>2050</v>
       </c>
       <c r="C131">
-        <v>282500.8702428</v>
+        <v>38395.58225854655</v>
       </c>
       <c r="D131">
-        <v>39550.12183399201</v>
+        <v>0</v>
       </c>
       <c r="E131">
-        <v>242950.748408808</v>
+        <v>38395.58225854652</v>
       </c>
       <c r="F131">
-        <v>116616.3592362279</v>
+        <v>18429.87948410233</v>
       </c>
     </row>
     <row r="132" spans="1:6">
@@ -10618,10 +10618,10 @@
         <v>2026</v>
       </c>
       <c r="C133">
-        <v>280902.071782</v>
+        <v>241575.78173252</v>
       </c>
       <c r="D133">
-        <v>39326.29004948001</v>
+        <v>0</v>
       </c>
       <c r="E133">
         <v>241575.78173252</v>
@@ -10638,16 +10638,16 @@
         <v>2027</v>
       </c>
       <c r="C134">
-        <v>599305.61986432</v>
+        <v>447076.6104650855</v>
       </c>
       <c r="D134">
-        <v>83902.7867810048</v>
+        <v>0</v>
       </c>
       <c r="E134">
-        <v>515402.8330833152</v>
+        <v>447076.6104650855</v>
       </c>
       <c r="F134">
-        <v>247393.3598799913</v>
+        <v>214596.7730232411</v>
       </c>
     </row>
     <row r="135" spans="1:6">
@@ -10658,16 +10658,16 @@
         <v>2028</v>
       </c>
       <c r="C135">
-        <v>839588.72471072</v>
+        <v>534170.2249073947</v>
       </c>
       <c r="D135">
-        <v>117542.4214595008</v>
+        <v>0</v>
       </c>
       <c r="E135">
-        <v>722046.3032512192</v>
+        <v>534170.2249073948</v>
       </c>
       <c r="F135">
-        <v>346582.2255605853</v>
+        <v>256401.7079555495</v>
       </c>
     </row>
     <row r="136" spans="1:6">
@@ -10678,16 +10678,16 @@
         <v>2029</v>
       </c>
       <c r="C136">
-        <v>1085336.532838256</v>
+        <v>613165.004377285</v>
       </c>
       <c r="D136">
-        <v>151947.1145973559</v>
+        <v>0</v>
       </c>
       <c r="E136">
-        <v>933389.4182409002</v>
+        <v>613165.0043772851</v>
       </c>
       <c r="F136">
-        <v>448026.9207556322</v>
+        <v>294319.2021010969</v>
       </c>
     </row>
     <row r="137" spans="1:6">
@@ -10698,16 +10698,16 @@
         <v>2030</v>
       </c>
       <c r="C137">
-        <v>1404234.694189184</v>
+        <v>745447.0897185272</v>
       </c>
       <c r="D137">
-        <v>196592.8571864858</v>
+        <v>0</v>
       </c>
       <c r="E137">
-        <v>1207641.837002698</v>
+        <v>745447.0897185273</v>
       </c>
       <c r="F137">
-        <v>579668.0817612952</v>
+        <v>357814.603064893</v>
       </c>
     </row>
     <row r="138" spans="1:6">
@@ -10718,16 +10718,16 @@
         <v>2031</v>
       </c>
       <c r="C138">
-        <v>1695150.264496624</v>
+        <v>829505.2716509057</v>
       </c>
       <c r="D138">
-        <v>237321.0370295274</v>
+        <v>0</v>
       </c>
       <c r="E138">
-        <v>1457829.227467097</v>
+        <v>829505.2716509058</v>
       </c>
       <c r="F138">
-        <v>699758.0291842064</v>
+        <v>398162.5303924348</v>
       </c>
     </row>
     <row r="139" spans="1:6">
@@ -10738,16 +10738,16 @@
         <v>2032</v>
       </c>
       <c r="C139">
-        <v>2039218.758534864</v>
+        <v>950739.7071225278</v>
       </c>
       <c r="D139">
-        <v>285490.626194881</v>
+        <v>0</v>
       </c>
       <c r="E139">
-        <v>1753728.132339983</v>
+        <v>950739.7071225279</v>
       </c>
       <c r="F139">
-        <v>841789.5035231919</v>
+        <v>456355.0594188134</v>
       </c>
     </row>
     <row r="140" spans="1:6">
@@ -10758,16 +10758,16 @@
         <v>2033</v>
       </c>
       <c r="C140">
-        <v>2362042.854868512</v>
+        <v>1034992.349711992</v>
       </c>
       <c r="D140">
-        <v>330685.9996815917</v>
+        <v>0</v>
       </c>
       <c r="E140">
-        <v>2031356.85518692</v>
+        <v>1034992.349711992</v>
       </c>
       <c r="F140">
-        <v>975051.2904897218</v>
+        <v>496796.3278617563</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -10778,16 +10778,16 @@
         <v>2034</v>
       </c>
       <c r="C141">
-        <v>2716591.784436528</v>
+        <v>1139630.864373043</v>
       </c>
       <c r="D141">
-        <v>380322.8498211139</v>
+        <v>0</v>
       </c>
       <c r="E141">
-        <v>2336268.934615414</v>
+        <v>1139630.864373044</v>
       </c>
       <c r="F141">
-        <v>1121409.088615399</v>
+        <v>547022.8148990609</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -10798,16 +10798,16 @@
         <v>2035</v>
       </c>
       <c r="C142">
-        <v>3025775.669789136</v>
+        <v>1192707.004164325</v>
       </c>
       <c r="D142">
-        <v>423608.5937704791</v>
+        <v>0</v>
       </c>
       <c r="E142">
-        <v>2602167.076018657</v>
+        <v>1192707.004164325</v>
       </c>
       <c r="F142">
-        <v>1249040.196488956</v>
+        <v>572499.361998876</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -10818,16 +10818,16 @@
         <v>2036</v>
       </c>
       <c r="C143">
-        <v>3316674.440350896</v>
+        <v>1232774.743285153</v>
       </c>
       <c r="D143">
-        <v>464334.4216491255</v>
+        <v>0</v>
       </c>
       <c r="E143">
-        <v>2852340.018701771</v>
+        <v>1232774.743285153</v>
       </c>
       <c r="F143">
-        <v>1369123.20897685</v>
+        <v>591731.8767768733</v>
       </c>
     </row>
     <row r="144" spans="1:6">
@@ -10838,16 +10838,16 @@
         <v>2037</v>
       </c>
       <c r="C144">
-        <v>3604271.11055392</v>
+        <v>1275515.441194882</v>
       </c>
       <c r="D144">
-        <v>504597.9554775489</v>
+        <v>0</v>
       </c>
       <c r="E144">
-        <v>3099673.155076372</v>
+        <v>1275515.441194882</v>
       </c>
       <c r="F144">
-        <v>1487843.114436659</v>
+        <v>612247.4117735433</v>
       </c>
     </row>
     <row r="145" spans="1:6">
@@ -10858,16 +10858,16 @@
         <v>2038</v>
       </c>
       <c r="C145">
-        <v>3943903.826044496</v>
+        <v>1366628.636892116</v>
       </c>
       <c r="D145">
-        <v>552146.5356462295</v>
+        <v>0</v>
       </c>
       <c r="E145">
-        <v>3391757.290398267</v>
+        <v>1366628.636892116</v>
       </c>
       <c r="F145">
-        <v>1628043.499391168</v>
+        <v>655981.7457082156</v>
       </c>
     </row>
     <row r="146" spans="1:6">
@@ -10878,16 +10878,16 @@
         <v>2039</v>
       </c>
       <c r="C146">
-        <v>4268925.246804608</v>
+        <v>1434210.863006677</v>
       </c>
       <c r="D146">
-        <v>597649.5345526452</v>
+        <v>0</v>
       </c>
       <c r="E146">
-        <v>3671275.712251964</v>
+        <v>1434210.863006677</v>
       </c>
       <c r="F146">
-        <v>1762212.341880943</v>
+        <v>688421.214243205</v>
       </c>
     </row>
     <row r="147" spans="1:6">
@@ -10898,16 +10898,16 @@
         <v>2040</v>
       </c>
       <c r="C147">
-        <v>4550471.118630464</v>
+        <v>1460692.971012458</v>
       </c>
       <c r="D147">
-        <v>637065.9566082651</v>
+        <v>0</v>
       </c>
       <c r="E147">
-        <v>3913405.1620222</v>
+        <v>1460692.971012458</v>
       </c>
       <c r="F147">
-        <v>1878434.477770656</v>
+        <v>701132.6260859796</v>
       </c>
     </row>
     <row r="148" spans="1:6">
@@ -10918,16 +10918,16 @@
         <v>2041</v>
       </c>
       <c r="C148">
-        <v>4899533.892112544</v>
+        <v>1552998.702834272</v>
       </c>
       <c r="D148">
-        <v>685934.7448957562</v>
+        <v>0</v>
       </c>
       <c r="E148">
-        <v>4213599.147216788</v>
+        <v>1552998.702834272</v>
       </c>
       <c r="F148">
-        <v>2022527.590664059</v>
+        <v>745439.3773604506</v>
       </c>
     </row>
     <row r="149" spans="1:6">
@@ -10938,16 +10938,16 @@
         <v>2042</v>
       </c>
       <c r="C149">
-        <v>5184148.606100288</v>
+        <v>1577713.672069834</v>
       </c>
       <c r="D149">
-        <v>725780.8048540404</v>
+        <v>0</v>
       </c>
       <c r="E149">
-        <v>4458367.801246248</v>
+        <v>1577713.672069834</v>
       </c>
       <c r="F149">
-        <v>2140016.544598199</v>
+        <v>757302.5625935202</v>
       </c>
     </row>
     <row r="150" spans="1:6">
@@ -10958,16 +10958,16 @@
         <v>2043</v>
       </c>
       <c r="C150">
-        <v>5495155.729796289</v>
+        <v>1632827.295870951</v>
       </c>
       <c r="D150">
-        <v>769321.8021714804</v>
+        <v>0</v>
       </c>
       <c r="E150">
-        <v>4725833.927624809</v>
+        <v>1632827.295870951</v>
       </c>
       <c r="F150">
-        <v>2268400.285259908</v>
+        <v>783757.1020180566</v>
       </c>
     </row>
     <row r="151" spans="1:6">
@@ -10978,16 +10978,16 @@
         <v>2044</v>
       </c>
       <c r="C151">
-        <v>5794875.257665233</v>
+        <v>1676054.694317143</v>
       </c>
       <c r="D151">
-        <v>811282.5360731325</v>
+        <v>0</v>
       </c>
       <c r="E151">
-        <v>4983592.7215921</v>
+        <v>1676054.694317143</v>
       </c>
       <c r="F151">
-        <v>2392124.506364208</v>
+        <v>804506.2532722285</v>
       </c>
     </row>
     <row r="152" spans="1:6">
@@ -10998,16 +10998,16 @@
         <v>2045</v>
       </c>
       <c r="C152">
-        <v>6060995.427883376</v>
+        <v>1691329.038284689</v>
       </c>
       <c r="D152">
-        <v>848539.3599036727</v>
+        <v>0</v>
       </c>
       <c r="E152">
-        <v>5212456.067979705</v>
+        <v>1691329.038284689</v>
       </c>
       <c r="F152">
-        <v>2501978.912630258</v>
+        <v>811837.9383766507</v>
       </c>
     </row>
     <row r="153" spans="1:6">
@@ -11018,16 +11018,16 @@
         <v>2046</v>
       </c>
       <c r="C153">
-        <v>6333678.416475937</v>
+        <v>1720548.443613647</v>
       </c>
       <c r="D153">
-        <v>886714.9783066311</v>
+        <v>0</v>
       </c>
       <c r="E153">
-        <v>5446963.438169306</v>
+        <v>1720548.443613647</v>
       </c>
       <c r="F153">
-        <v>2614542.450321267</v>
+        <v>825863.2529345506</v>
       </c>
     </row>
     <row r="154" spans="1:6">
@@ -11038,16 +11038,16 @@
         <v>2047</v>
       </c>
       <c r="C154">
-        <v>6631494.407371697</v>
+        <v>1774467.393620217</v>
       </c>
       <c r="D154">
-        <v>928409.2170320374</v>
+        <v>0</v>
       </c>
       <c r="E154">
-        <v>5703085.190339659</v>
+        <v>1774467.393620217</v>
       </c>
       <c r="F154">
-        <v>2737480.891363037</v>
+        <v>851744.3489377042</v>
       </c>
     </row>
     <row r="155" spans="1:6">
@@ -11058,16 +11058,16 @@
         <v>2048</v>
       </c>
       <c r="C155">
-        <v>6933363.400707089</v>
+        <v>1827269.822158057</v>
       </c>
       <c r="D155">
-        <v>970670.8760989923</v>
+        <v>0</v>
       </c>
       <c r="E155">
-        <v>5962692.524608096</v>
+        <v>1827269.822158057</v>
       </c>
       <c r="F155">
-        <v>2862092.411811887</v>
+        <v>877089.5146358672</v>
       </c>
     </row>
     <row r="156" spans="1:6">
@@ -11078,16 +11078,16 @@
         <v>2049</v>
       </c>
       <c r="C156">
-        <v>7179199.595093138</v>
+        <v>1827696.695030372</v>
       </c>
       <c r="D156">
-        <v>1005087.943313039</v>
+        <v>0</v>
       </c>
       <c r="E156">
-        <v>6174111.651780098</v>
+        <v>1827696.695030372</v>
       </c>
       <c r="F156">
-        <v>2963573.592854448</v>
+        <v>877294.4136145782</v>
       </c>
     </row>
     <row r="157" spans="1:6">
@@ -11098,16 +11098,16 @@
         <v>2050</v>
       </c>
       <c r="C157">
-        <v>7468009.357159858</v>
+        <v>1875760.840939989</v>
       </c>
       <c r="D157">
-        <v>1045521.31000238</v>
+        <v>0</v>
       </c>
       <c r="E157">
-        <v>6422488.047157477</v>
+        <v>1875760.840939989</v>
       </c>
       <c r="F157">
-        <v>3082794.26263559</v>
+        <v>900365.2036511943</v>
       </c>
     </row>
   </sheetData>
@@ -11197,7 +11197,7 @@
         <v>37</v>
       </c>
       <c r="B10">
-        <v>0.5871999999999999</v>
+        <v>0.5872000000000001</v>
       </c>
     </row>
     <row r="11" spans="1:2">
